--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Data da Coleta</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Região</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Cidade</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Nome do Negócio</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Telefone</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Score de Conformidade</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Nível de Risco</t>
         </is>
@@ -874,6 +862,198 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Clínica Simoneti</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://clinicasimoneti.com.br/</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Clínica Rubi</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.clinicarubi.com.br/</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>76</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Smile Clínica Odontológica</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://smilebh.com.br/</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>75</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ClinBelo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://clinbelo.com.br/</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>80</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,6 +1054,246 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Médico em Maceió</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://agenda.app.br</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>67</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Clínica Inside Mind Jatiúca Maceió AL - Telefone...</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.benditoguia.com.br</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>70</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Monica Brasil</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://cebes.com.br</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>69</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dra. Ana Maria Monteiro Menezes,- Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://agendaconvenio.com</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>62</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mix Clínica Ponta Verde Reviews</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.top-rated.online</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>33</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1294,6 +1294,990 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Clínica Médica Multi-Especialidades</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://nubeclinic.com.br</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5582993999600</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>87</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Clínica ATEND JÁ</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://vizisaude.com.br</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>82</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vagas de Clínica em Maceió, AL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://br.indeed.com</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>33</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Clínica Guri</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>http://www.clinicaguri.com.br</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>558232016100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>75</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diagnose</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://diagnose.com.br</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>44</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Laboratório Sabin</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.labsabin.com.br</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5582999095311</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>65</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Encontre um Médico em Maceió</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.rededorsaoluiz.com.br</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>552121012658</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>70</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vagas de Emprego de Médico em Maceió/AL</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.trabalhabrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>73</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>5 Vagas de Emprego para Médico em Maceió/Al</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.bne.com.br</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>64</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Parque Shopping Maceió</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.maceioparqueshopping.com.br</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>70</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rede Credenciada SulAmérica Alagoas 2026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://saudesulamericasa.com.br</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5512981915070</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>22</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>A consulta</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://endouromedicina.site.med.br</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>56</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Os 10 Dentistas mais indicados em Maceió/AL</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.catalogo.med.br</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>62</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dentistas em Maceió, Brasil</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://seniorbemestar.com</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>56</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dentista em Maceió, AL — 401 resultados</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://saudecidade.com</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>69</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Oral Unic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.oralunic.com.br</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>73</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dentistas em Maceió (AL)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.medicosbrasil.com</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>50</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Clínica Integrar</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://integrarodontologiaestetica.com</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5582999010230</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>73</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica Sorrifácil Maceió na cidade de Maceió</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://sorrifacil.com.br</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>53</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Adelmo de Abreu Neto</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.adelmonetopsi.com</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>73</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1331,10 +1331,8 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5582993999600</t>
-        </is>
+      <c r="I19" t="n">
+        <v>5582993999600</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
@@ -1479,10 +1477,8 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>558232016100</t>
-        </is>
+      <c r="I22" t="n">
+        <v>558232016100</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
@@ -1579,10 +1575,8 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5582999095311</t>
-        </is>
+      <c r="I24" t="n">
+        <v>5582999095311</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
@@ -1631,10 +1625,8 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>552121012658</t>
-        </is>
+      <c r="I25" t="n">
+        <v>552121012658</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
@@ -1827,10 +1819,8 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5512981915070</t>
-        </is>
+      <c r="I29" t="n">
+        <v>5512981915070</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
@@ -2167,10 +2157,8 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5582999010230</t>
-        </is>
+      <c r="I36" t="n">
+        <v>5582999010230</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
@@ -2278,6 +2266,4654 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Clinialagoas Medicina Integrada</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://clinialagoas.com.br</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5582999450266</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>69</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Atend Já Maceió</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://maceio.atendja.com.br</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>90</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Climecor</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.climecor.com</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5582993112942</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>69</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Maceió / AL</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.clinicaconsulta.com.br</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>69</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gastroclinica</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://gastroclinicamaceio.com.br</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>75</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Bioclínica</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.bioclinicaal.com.br</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>88</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Especialistas em Maceió</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.medguias.com.br</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>94</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Médicos clínicos em Maceio</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://agendarconsulta.com</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>73</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Médico de Dor em Maceió-AL</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.drpedroferro.com.br</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>69</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Busca por médicos</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://cremal.org.br</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>76</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dr. Daniel Moreira</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://dentistamaceio.com</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="n">
+        <v>67</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Odontologia Especializada</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.clinicaenova.com</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>558232418220</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>80</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Profissionais em Maceió</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www2.uniodonto.coop.br</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="n">
+        <v>56</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Dentista em Maceió</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://nucleoodontomcz.com.br</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5582999851965</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>69</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dentista SulAmérica Odonto em Maceió</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://odontologicosulamerica.com.br</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="n">
+        <v>56</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dentista/Clínica Odontológica OdontoCompany em Maceió</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://odontocompany.com</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5511932799505</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>81</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Os Mais Recomendados Psicólogos em Maceió</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://facilconsulta.com.br</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>22</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Psicólogo, Maceió, AL</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://redepsicologos.com.br</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>81</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Psicólogo, Maceió, AL</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://centralterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>88</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Psicólogos Maceió (Alagoas)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://br.mundopsicologos.com</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>88</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Psicólogo em Maceió - AL</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://medprev.online</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="n">
+        <v>87</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Psicólogos em Maceió</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.cronoshare.com.br</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>82</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vanessa Dâmaso Psicóloga Clínica em Maceió</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://vanessadamaso.com.br</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5582999161318</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>67</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Psicólogo, Conselheiro, Terapeuta perto de mim em Maceió ...</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://mentalzon.com</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>47</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Psicanalistas em Maceió</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://euterapeuta.com.br</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="n">
+        <v>80</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>10 melhores terapeutas para Maceió</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.starofservice.com.br</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>64</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Advogados</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.tenoriomeloadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5582981318059</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>73</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Advogados e Escritórios de Advocacia em Maceió</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.encontramaceio.com.br</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="n">
+        <v>55</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ALNPP</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.alnpp.com.br</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>45</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Cavalcanti Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://cavalcantiassociados.com</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5582993710121</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>73</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>10 Melhores Escritórios de Advocacia em Maceió AL</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://ddireito.com.br</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>73</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Advocacia de excelência em Maceió e Alagoas</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://neripachecoadvogados.com</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="n">
+        <v>64</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Advogado em Maceió e Região</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://joseneto.adv.br</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>558299179336</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="n">
+        <v>82</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Faculdades de Educação Física em Maceió - AL</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://querobolsa.com.br</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>558001232222</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="n">
+        <v>69</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mestrados e cursos de Educação Física no Maceió</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.educaedu-brasil.com</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="n">
+        <v>62</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Faculdades de Educação Física a distância em Maceió - AL</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.ead.com.br</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>558009423474</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>69</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Cursos de Educação Física em Maceió - AL</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.guiadacarreira.com.br</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>558009427777</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>69</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.uncisal.edu.br</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="n">
+        <v>71</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>EDUCAÇÃO FÍSICA NA IBESA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://carreiras.stoodi.com.br</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="n">
+        <v>22</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Instituto de Educação Física e Esporte</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://iefe.ufal.br</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="n">
+        <v>67</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Academias em Maceió, AL, Brasil</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://wellhub.com</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>551124241451</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="n">
+        <v>60</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://allpfit.com.br</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="n">
+        <v>40</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Academia Smart Fit</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.smartfit.com.br</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="n">
+        <v>90</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>PARQUE SHOPPING MACEIÓ</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.selfitacademias.com.br</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="n">
+        <v>90</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>GO Training Center</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://gorgonoid.com</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5531998385296</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="n">
+        <v>70</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Academias em Maceió, AL</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.gurupass.com.br</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>551141182773</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="n">
+        <v>50</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Academia Smart Fit</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.waze.com</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="n">
+        <v>56</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Fisioterapia Pilates RPG</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.clinicafipi.com</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>5582991107444</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="n">
+        <v>69</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Dr. André Oliveira</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://drandreoliveirafisio.com.br</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>5582996460786</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="n">
+        <v>73</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Fisiocoop</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://fisiocoop.coop.br</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Espaço Saúde Unimed</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.unimed.coop.br</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="n">
+        <v>71</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Os 10 melhores centros de Fisioterapia em Maceió</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://maceio.infoisinfo-br.com</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="n">
+        <v>64</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Clinica Vida: Clínica Vida</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://clinicavida.com.br</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>5571981784780</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="n">
+        <v>69</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Clinicas Clivale</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://clinicasclivale.com.br</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>5571999697064</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="n">
+        <v>65</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Clínica Santa Helena</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.gruposhbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>5571999667555</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="n">
+        <v>56</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Clínica Ibis</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.clinicaibis.com.br</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>5571984105500</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="n">
+        <v>76</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Clínica médica</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.fjs.org.br</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>557135045240</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="n">
+        <v>65</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Clínica Humana</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.clinicahumana.com.br</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="n">
+        <v>50</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Clínica-escola oferece atendimento médico gratuito em Salvador</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://g1.globo.com</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="n">
+        <v>64</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Centro Médico Hospital da Bahia</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.centromedicohba.com.br</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="n">
+        <v>69</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Melhor médicos em Salvador por avaliações</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.avaliamed.com.br</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="n">
+        <v>81</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Home • Bem Centro Médico</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://bemcentromedico.com.br</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>557131900499</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="n">
+        <v>67</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>O Dentista Clínica Odontológica</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.odentistabrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>557132427486</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="n">
+        <v>67</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Dentista Salvador</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://dentistasalvador.ac.gd</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="n">
+        <v>53</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Dentista Salvador</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://dentistasalvador.com.br</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Clínica Apollo Odontologia Integrada</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://clinicaapollo.com.br</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>5571981251568</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="n">
+        <v>73</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Núcleo Odontológico de Salvador</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.nosodontosalvador.com.br</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>5571991562088</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="n">
+        <v>69</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Dentistas em Salvador - BA</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://dentmap.com.br</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="n">
+        <v>75</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Implante Dentário em Salvador</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.hospitalodontologico.com.br</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>69</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Antônia Carolina de Souza Paim</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.psicologasalvador.com.br</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>5571997056073</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="n">
+        <v>73</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Gestar Psi</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://clinicagestarpsi.com.br</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>557193733334</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>94</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Psicólogos em Salvador - Bahia</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.psicologapopular.com</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5537999773676</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="n">
+        <v>93</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Vagas de Psicólogo em Salvador, BA (Urgente!)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://br.jooble.org</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="n">
+        <v>33</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Terapeuta perto de mim em Salvador</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.locaisdobrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="n">
+        <v>78</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Terapias em Salvador</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.terapyas.com.br</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="n">
+        <v>94</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Sandra Valéria Coelho</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://terapia.salvador.br</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="n">
+        <v>62</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Advogados e Correspondentes Jurídicos em Salvador, BA</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://juridicocerto.com</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="n">
+        <v>64</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Salvador advogados em salvador BA advogado salvador BA</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.advogadosaqui.com.br</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="n">
+        <v>64</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Isabella Magalhães</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://especialistadefamilia.com.br</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="n">
+        <v>33</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>31 avaliações sobre Borges &amp; Queiroz Advogados...</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://avaliacoesbrasil.com</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="n">
+        <v>73</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Faculdades de Educação Física em Salvador</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.faculdadesja.com.br</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>CURSO SUPERIOR LICENCIATURA EM FÍSICA — IFBA</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://portal.ifba.edu.br</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.bahiana.edu.br</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="n">
+        <v>33</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>297 Academias em Salvador/BA (2026)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://acharacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="n">
+        <v>60</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Academias em Salvador</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.akademias.com.br</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="n">
+        <v>90</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Hammer Fitness Club</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.hammeracademia.com</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="n">
+        <v>90</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Fisioterapeutas em Salvador - BA</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.listamais.com.br</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Fisioterapeutas em Salvador (2026) — Agendar Consulta</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://clinic.medilifeapp.com</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="n">
+        <v>73</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Rosimeire Passos Fisioterapeuta em Salvador</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.rosipassosfisio.com.br</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="n">
+        <v>73</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Profisio</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.clinicaprofisio.com</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>5571999926164</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="n">
+        <v>73</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>HomeCalm Fisioterapia e Pilates</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://homecalm.com.br</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>5571991272568</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="n">
+        <v>75</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Clínica de Fisioterapia na Pituba</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://pitubafisio.com.br</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>5571988103288</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="n">
+        <v>73</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Clínica Nova</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://clinicanova.med.br</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>558530480500</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="n">
+        <v>67</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Clínica SantaMed: Página Principal</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://clinicasantamed.com.br</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>5585981077070</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="n">
+        <v>69</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L132"/>
+  <dimension ref="A1:L208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2303,10 +2303,8 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5582999450266</t>
-        </is>
+      <c r="I39" t="n">
+        <v>5582999450266</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
@@ -2403,10 +2401,8 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5582993112942</t>
-        </is>
+      <c r="I41" t="n">
+        <v>5582993112942</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
@@ -2839,10 +2835,8 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>558232418220</t>
-        </is>
+      <c r="I50" t="n">
+        <v>558232418220</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="n">
@@ -2939,10 +2933,8 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5582999851965</t>
-        </is>
+      <c r="I52" t="n">
+        <v>5582999851965</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="n">
@@ -3039,10 +3031,8 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5511932799505</t>
-        </is>
+      <c r="I54" t="n">
+        <v>5511932799505</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="n">
@@ -3379,10 +3369,8 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5582999161318</t>
-        </is>
+      <c r="I61" t="n">
+        <v>5582999161318</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
@@ -3575,10 +3563,8 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>5582981318059</t>
-        </is>
+      <c r="I65" t="n">
+        <v>5582981318059</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
@@ -3723,10 +3709,8 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>5582993710121</t>
-        </is>
+      <c r="I68" t="n">
+        <v>5582993710121</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
@@ -3871,10 +3855,8 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>558299179336</t>
-        </is>
+      <c r="I71" t="n">
+        <v>558299179336</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="n">
@@ -3923,10 +3905,8 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>558001232222</t>
-        </is>
+      <c r="I72" t="n">
+        <v>558001232222</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
@@ -4023,10 +4003,8 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>558009423474</t>
-        </is>
+      <c r="I74" t="n">
+        <v>558009423474</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
@@ -4075,10 +4053,8 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>558009427777</t>
-        </is>
+      <c r="I75" t="n">
+        <v>558009427777</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="n">
@@ -4271,10 +4247,8 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>551124241451</t>
-        </is>
+      <c r="I79" t="n">
+        <v>551124241451</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
@@ -4467,10 +4441,8 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>5531998385296</t>
-        </is>
+      <c r="I83" t="n">
+        <v>5531998385296</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="n">
@@ -4519,10 +4491,8 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>551141182773</t>
-        </is>
+      <c r="I84" t="n">
+        <v>551141182773</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="n">
@@ -4619,10 +4589,8 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>5582991107444</t>
-        </is>
+      <c r="I86" t="n">
+        <v>5582991107444</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="n">
@@ -4671,10 +4639,8 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>5582996460786</t>
-        </is>
+      <c r="I87" t="n">
+        <v>5582996460786</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="n">
@@ -4867,10 +4833,8 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>5571981784780</t>
-        </is>
+      <c r="I91" t="n">
+        <v>5571981784780</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
@@ -4919,10 +4883,8 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>5571999697064</t>
-        </is>
+      <c r="I92" t="n">
+        <v>5571999697064</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="n">
@@ -4971,10 +4933,8 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>5571999667555</t>
-        </is>
+      <c r="I93" t="n">
+        <v>5571999667555</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="n">
@@ -5023,10 +4983,8 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>5571984105500</t>
-        </is>
+      <c r="I94" t="n">
+        <v>5571984105500</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="n">
@@ -5075,10 +5033,8 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>557135045240</t>
-        </is>
+      <c r="I95" t="n">
+        <v>557135045240</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="n">
@@ -5319,10 +5275,8 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>557131900499</t>
-        </is>
+      <c r="I100" t="n">
+        <v>557131900499</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
@@ -5371,10 +5325,8 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>557132427486</t>
-        </is>
+      <c r="I101" t="n">
+        <v>557132427486</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
@@ -5519,10 +5471,8 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>5571981251568</t>
-        </is>
+      <c r="I104" t="n">
+        <v>5571981251568</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
@@ -5571,10 +5521,8 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>5571991562088</t>
-        </is>
+      <c r="I105" t="n">
+        <v>5571991562088</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="n">
@@ -5719,10 +5667,8 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>5571997056073</t>
-        </is>
+      <c r="I108" t="n">
+        <v>5571997056073</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
@@ -5771,10 +5717,8 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>557193733334</t>
-        </is>
+      <c r="I109" t="n">
+        <v>557193733334</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="n">
@@ -5823,10 +5767,8 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>5537999773676</t>
-        </is>
+      <c r="I110" t="n">
+        <v>5537999773676</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
@@ -6691,10 +6633,8 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>5571999926164</t>
-        </is>
+      <c r="I128" t="n">
+        <v>5571999926164</v>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="n">
@@ -6743,10 +6683,8 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>5571991272568</t>
-        </is>
+      <c r="I129" t="n">
+        <v>5571991272568</v>
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="n">
@@ -6795,10 +6733,8 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>5571988103288</t>
-        </is>
+      <c r="I130" t="n">
+        <v>5571988103288</v>
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="n">
@@ -6847,10 +6783,8 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>558530480500</t>
-        </is>
+      <c r="I131" t="n">
+        <v>558530480500</v>
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="n">
@@ -6899,16 +6833,3806 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>5585981077070</t>
-        </is>
+      <c r="I132" t="n">
+        <v>5585981077070</v>
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="n">
         <v>69</v>
       </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>clinicasbrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://clinicasbrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>556134681068</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="n">
+        <v>64</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Centro Clínico A+ Saúde</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://velora.tech</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="n">
+        <v>44</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Brasília com Somos Popular</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.somospopular.com.br</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="n">
+        <v>33</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Centro Clínico Humana Recanto das Emas Brasília DF...</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://guiamania.com.br</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="n">
+        <v>33</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Dr. André Luís Wambier — Cardio DF</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://cardiodf.com.br</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="n">
+        <v>59</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>medicoperto.com.br</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://medicoperto.com.br</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>5561982863837</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="n">
+        <v>80</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Dental Brasil</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://dentalbrasildf.com.br</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>556130112356</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="n">
+        <v>75</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Clínica de Odontologia</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.unip.br</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>5511943035000</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="n">
+        <v>88</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>ZR Odonto</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://zrodonto.com.br</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>5561998375118</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="n">
+        <v>88</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Trida Odontologia Especializada</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://tridaodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>5561981850318</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="n">
+        <v>80</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Clínica-Escola de Odontologia</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://ucb2.catolica.edu.br</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>556133569075</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="n">
+        <v>69</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Odontologia</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://sescdf.com.br</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>556132189101</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="n">
+        <v>69</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Psicólogos em Brasília: Agende sua terapia online agora mesmo</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.psitto.com.br</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>5511968632121</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="n">
+        <v>81</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Psiquiatra Brasilia DF</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://med-br.com</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="n">
+        <v>75</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Psicólogo Brasília</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.singularpsicologiadf.com.br</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>5561999511258</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="n">
+        <v>73</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>IBAC</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://ibac.com.br</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="n">
+        <v>62</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Psicoterapia em Brasília</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.fisioemov.com.br</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>556198782133</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="n">
+        <v>69</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Clínica Diálogo</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://clinicadialogo.com.br</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="n">
+        <v>50</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Terapia de Casal em Brasília</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.ressignificarpsicologia.com</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>5561998634538</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="n">
+        <v>80</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Psicologia e Psicoterapia</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://incb.com.br</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>5561996060635</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="n">
+        <v>22</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Reflexões e Orientações sobre a Prática da Psicoterapia</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://site.cfp.org.br</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="n">
+        <v>88</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Distrito Federal</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.traumaclinic.com.br</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="n">
+        <v>81</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Carneiros Advogados: Home</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://carneiros.adv.br</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="n">
+        <v>64</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Ibaneis Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.ibaneis.adv.br</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="n">
+        <v>73</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Torres e Corrêa Advocacia</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://tco.adv.br</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="n">
+        <v>89</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Eliana Calmon</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://elianacalmon.adv.br</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>556139631262</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="n">
+        <v>64</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Paixão Côrtes Advogados</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.paixaocortes.com.br</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>5561981536149</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="n">
+        <v>64</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Dinamarco Advogados: Home</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.dinamarco.com.br</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="n">
+        <v>55</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Vagas De Emprego De Professor Educaçao Fisica Brasilia</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://vagas.mitula.com.br</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="n">
+        <v>22</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Vagas de emprego : Professor de Educação Física em Brasília</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.careerjet.com.br</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Ensino médio noturno: as dispensas nas aulas de Educação Física</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://efdeportes.com</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="n">
+        <v>65</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Como chegar até CREF</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://moovitapp.com</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="n">
+        <v>44</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Horário de Brasília</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.horariodebrasilia.org</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="n">
+        <v>56</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Vaga de Estagiário</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://cadernonacional.com.br</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="n">
+        <v>81</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Dimensões motivacionais dos conteúdos da educação física no...</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://ojs.revistadelos.com</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="n">
+        <v>33</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>29 academias em Brasília (Distrito Federal) + trainers</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://conecta.fitness</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="n">
+        <v>40</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Runway</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://runway.com.br</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>556195844771</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="n">
+        <v>90</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Academia Unique</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.academiaunique.com.br</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>5561993140270</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="n">
+        <v>70</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Ultra Academia</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://ultraacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>5511974139514</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="n">
+        <v>70</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Academia Body Action</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://foursquare.com</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="n">
+        <v>44</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>13 vagas de fisioterapeuta – Brasília, Distrito Federal</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com.br</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="n">
+        <v>33</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Encontre um profissional Certificado</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://mckenzie.com.br</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="n">
+        <v>33</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Clínica Brasil: Tudo o que sua saúde precisa!</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://clinicabrasilgoiania.com.br</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>556235454000</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="n">
+        <v>94</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Clínica Goiana Medicina &amp; Diagnóstico</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://clinicagoiana.med.br</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>5564984390766</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="n">
+        <v>88</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Clínica Popular em Goiânia, Consultas Médicas, Exames Médicos</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.clinicavittagoiania.com.br</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>556239960505</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="n">
+        <v>62</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Clínica em Goiânia</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://clinicagedda.com.br</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>5562998256655</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="n">
+        <v>22</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Clínica Médica Goiás Saúde e Odontologia</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.clinicamedicagoias.com.br</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Atend Já Goiânia</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://goiania.atendja.com.br</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="n">
+        <v>90</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Goiânia Médica</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.goianiamedica.com.br</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Clínica de Diagnóstico por Imagem Avançado</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://clinicadia.net.br</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>556232512898</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="n">
+        <v>88</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>CREMEGO, Busca médico</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://crmvirtual.cfm.org.br</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="n">
+        <v>62</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Vagas de emprego Médico em Goiânia, GO</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.jobijoba.com.br</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="n">
+        <v>73</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>CREDENCIADOS GOIANIA</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://assets.marinha.mil.br</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Dentista em Goiânia</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://dentistagoiania.com.br</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>5511912062131</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="n">
+        <v>56</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Implantes Dentários em Goiânia</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://odontogaravelo.com.br</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>5562996304831</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="n">
+        <v>60</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Centro Goiano de Odontologia</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.centrogoianodeodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>5562995531882</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="n">
+        <v>56</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Psicólogo Goiânia: Encontre os melhores psicólogos em Goiânia</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://psicologogoiania.com</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>5562982663416</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="n">
+        <v>75</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Instituto Suassuna</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://institutosuassuna.com.br</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>5562981426789</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="n">
+        <v>81</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>A função do psicólogo no pronto-socorro: a visão da equipe</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>http://pepsic.bvsalud.org</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="n">
+        <v>60</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Psicólogo em Goiânia</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.clinicamedprime.com.br</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>556239960508</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="n">
+        <v>62</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Dr Humberto Psicanalista Terapeuta</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.humbertopsicanalista.com</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>5562999234619</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="n">
+        <v>62</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>TERAPEUTA LUCIANA OFICIAL</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.terapeutalucianarocha.com.br</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Clínica Veredas</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://veredaspsicologia.com.br</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>5562992899057</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="n">
+        <v>80</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>EMBN Advogados</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.edmommoraesadv.com</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>5562984796876</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="n">
+        <v>73</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Advogado Goiânia Escritório de Advocacia Rodolfo Pimenta</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://rodolfopimenta.com.br</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="n">
+        <v>82</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Rocha Advogados</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://rochadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>5562992347835</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="n">
+        <v>73</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Advogado Goiania</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://advogadogoiania.com.br</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="n">
+        <v>64</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Advogado Trabalhista - Dr. Arthur Morais</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://viatapida.com</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="n">
+        <v>45</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.uniaraguaia.edu.br</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="n">
+        <v>33</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Faça Educação Física Bacharelado na PUC Goiás (Bolsa de 50%)</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.pucgoias.edu.br</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="n">
+        <v>33</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Curso de Faculdades de Educação Física em Goiás</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.educabras.com</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="n">
+        <v>59</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.academiagavioes.com.br</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>5511940747584</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="n">
+        <v>73</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Flex Fitness Center</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.flexfitnesscenter.com.br</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="n">
+        <v>22</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Academia da Fáscia</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.academiadafascia.com</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>5562994359484</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="n">
+        <v>70</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Melhores Academias de Goiânia - GO</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://rudders.com.br</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="n">
+        <v>80</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Principais fisioterapeutas e profissionais da saúde em Goiânia</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://buscafisio.com.br</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>551141183034</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="n">
+        <v>69</v>
+      </c>
+      <c r="L208" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:L279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6883,10 +6883,8 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>556134681068</t>
-        </is>
+      <c r="I133" t="n">
+        <v>556134681068</v>
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="n">
@@ -7127,10 +7125,8 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>5561982863837</t>
-        </is>
+      <c r="I138" t="n">
+        <v>5561982863837</v>
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="n">
@@ -7179,10 +7175,8 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>556130112356</t>
-        </is>
+      <c r="I139" t="n">
+        <v>556130112356</v>
       </c>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="n">
@@ -7231,10 +7225,8 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>5511943035000</t>
-        </is>
+      <c r="I140" t="n">
+        <v>5511943035000</v>
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="n">
@@ -7283,10 +7275,8 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>5561998375118</t>
-        </is>
+      <c r="I141" t="n">
+        <v>5561998375118</v>
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="n">
@@ -7335,10 +7325,8 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>5561981850318</t>
-        </is>
+      <c r="I142" t="n">
+        <v>5561981850318</v>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="n">
@@ -7387,10 +7375,8 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>556133569075</t>
-        </is>
+      <c r="I143" t="n">
+        <v>556133569075</v>
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="n">
@@ -7439,10 +7425,8 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>556132189101</t>
-        </is>
+      <c r="I144" t="n">
+        <v>556132189101</v>
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="n">
@@ -7491,10 +7475,8 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>5511968632121</t>
-        </is>
+      <c r="I145" t="n">
+        <v>5511968632121</v>
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="n">
@@ -7591,10 +7573,8 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>5561999511258</t>
-        </is>
+      <c r="I147" t="n">
+        <v>5561999511258</v>
       </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="n">
@@ -7691,10 +7671,8 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>556198782133</t>
-        </is>
+      <c r="I149" t="n">
+        <v>556198782133</v>
       </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="n">
@@ -7791,10 +7769,8 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>5561998634538</t>
-        </is>
+      <c r="I151" t="n">
+        <v>5561998634538</v>
       </c>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="n">
@@ -7843,10 +7819,8 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>5561996060635</t>
-        </is>
+      <c r="I152" t="n">
+        <v>5561996060635</v>
       </c>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="n">
@@ -8135,10 +8109,8 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>556139631262</t>
-        </is>
+      <c r="I158" t="n">
+        <v>556139631262</v>
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="n">
@@ -8187,10 +8159,8 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>5561981536149</t>
-        </is>
+      <c r="I159" t="n">
+        <v>5561981536149</v>
       </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="n">
@@ -8671,10 +8641,8 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>556195844771</t>
-        </is>
+      <c r="I169" t="n">
+        <v>556195844771</v>
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="n">
@@ -8723,10 +8691,8 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>5561993140270</t>
-        </is>
+      <c r="I170" t="n">
+        <v>5561993140270</v>
       </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="n">
@@ -8775,10 +8741,8 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>5511974139514</t>
-        </is>
+      <c r="I171" t="n">
+        <v>5511974139514</v>
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="n">
@@ -8971,10 +8935,8 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>556235454000</t>
-        </is>
+      <c r="I175" t="n">
+        <v>556235454000</v>
       </c>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="n">
@@ -9023,10 +8985,8 @@
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>5564984390766</t>
-        </is>
+      <c r="I176" t="n">
+        <v>5564984390766</v>
       </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="n">
@@ -9075,10 +9035,8 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>556239960505</t>
-        </is>
+      <c r="I177" t="n">
+        <v>556239960505</v>
       </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="n">
@@ -9127,10 +9085,8 @@
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>5562998256655</t>
-        </is>
+      <c r="I178" t="n">
+        <v>5562998256655</v>
       </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="n">
@@ -9323,10 +9279,8 @@
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>556232512898</t>
-        </is>
+      <c r="I182" t="n">
+        <v>556232512898</v>
       </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="n">
@@ -9519,10 +9473,8 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>5511912062131</t>
-        </is>
+      <c r="I186" t="n">
+        <v>5511912062131</v>
       </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="n">
@@ -9571,10 +9523,8 @@
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>5562996304831</t>
-        </is>
+      <c r="I187" t="n">
+        <v>5562996304831</v>
       </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="n">
@@ -9623,10 +9573,8 @@
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>5562995531882</t>
-        </is>
+      <c r="I188" t="n">
+        <v>5562995531882</v>
       </c>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="n">
@@ -9675,10 +9623,8 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>5562982663416</t>
-        </is>
+      <c r="I189" t="n">
+        <v>5562982663416</v>
       </c>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="n">
@@ -9727,10 +9673,8 @@
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>5562981426789</t>
-        </is>
+      <c r="I190" t="n">
+        <v>5562981426789</v>
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="n">
@@ -9827,10 +9771,8 @@
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>556239960508</t>
-        </is>
+      <c r="I192" t="n">
+        <v>556239960508</v>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="n">
@@ -9879,10 +9821,8 @@
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>5562999234619</t>
-        </is>
+      <c r="I193" t="n">
+        <v>5562999234619</v>
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="n">
@@ -9979,10 +9919,8 @@
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>5562992899057</t>
-        </is>
+      <c r="I195" t="n">
+        <v>5562992899057</v>
       </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="n">
@@ -10031,10 +9969,8 @@
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>5562984796876</t>
-        </is>
+      <c r="I196" t="n">
+        <v>5562984796876</v>
       </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="n">
@@ -10131,10 +10067,8 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>5562992347835</t>
-        </is>
+      <c r="I198" t="n">
+        <v>5562992347835</v>
       </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="n">
@@ -10423,10 +10357,8 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>5511940747584</t>
-        </is>
+      <c r="I204" t="n">
+        <v>5511940747584</v>
       </c>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="n">
@@ -10523,10 +10455,8 @@
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>5562994359484</t>
-        </is>
+      <c r="I206" t="n">
+        <v>5562994359484</v>
       </c>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="n">
@@ -10623,16 +10553,3510 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>551141183034</t>
-        </is>
+      <c r="I208" t="n">
+        <v>551141183034</v>
       </c>
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="n">
         <v>69</v>
       </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Moda feminina</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://br.shein.com</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="n">
+        <v>60</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Os melhores médicos de Espírito Santo (ES)</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.doctoranytime.com.br</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="n">
+        <v>56</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Prepaga</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.swissmedical.com.ar</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="n">
+        <v>53</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>CBF</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.cbf.com.br</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Verano Joven</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://veranojoven.transportes.gob.es</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="n">
+        <v>33</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Marcadores en Vivo, Calendarios, Resultados y Tablas</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://es.soccerway.com</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="n">
+        <v>50</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Victoria's Secret: sujetadores, bañadores, lencería, deporte y belleza</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://es.victoriassecret.com</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="n">
+        <v>33</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Dra. Letícia Ribeiro Meirelles</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.leticiarm.com.br</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="n">
+        <v>73</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Carminate Odontologia</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://carminateodontologia.com</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>5527992716293</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="n">
+        <v>73</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Centro de Estética Dental</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.centrodeesteticadental.com.br</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>5527997209784</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="n">
+        <v>67</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Dentista em Jardim Camburi</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://renoveodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>5527992799432</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="n">
+        <v>88</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Psicólogo em Vitória - ES</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://mail.lorenagomes.com.br</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="n">
+        <v>22</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Maialen Fernández Psicólogos Vitoria</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.maialenfernandezpsicologia.com</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="n">
+        <v>62</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Localizador de envíos de Correos</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.correos.es</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="n">
+        <v>50</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Massagens, terapias corporais, estética e bem-estar no Brasil</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.pamot.com.br</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="n">
+        <v>33</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Terapeuta Sol / Realização no toque! em Vitoria</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://topmassagens.com.br</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="n">
+        <v>62</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Maria Alice Lamego de Moraes em Vitória, ES</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.econodata.com.br</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="n">
+        <v>22</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Charming apartment-Jdim da Penha- Vitória, ES -Brazil...</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.airbnb.com</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="n">
+        <v>44</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Barroso Advogados</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.barrosoadvogados.etc.br</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="n">
+        <v>73</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Advogado - Vitória</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://vlvadvogados.com</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="n">
+        <v>64</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Victor Vittore Advogados</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://victorvittoreadvogados.adv.br</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>5527999045444</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="n">
+        <v>64</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Advogado em Vitória ES</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://lopesecampos.adv.br</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>5527996901700</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="n">
+        <v>100</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Advogado, Vitória - ES</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://villeladamotta.com.br</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>5527999489898</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="n">
+        <v>73</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>CJAR</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://cjar.com.br</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="n">
+        <v>82</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Vagas abertas em Educação Física em Vitória / ES</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://www.superestagios.com.br</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="n">
+        <v>67</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>CREF22/ES</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://cref22.org.br</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>5527998114107</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="n">
+        <v>78</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Vagas de Emprego de educação fisica em Vitória - ES</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://www.infojobs.com.br</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="n">
+        <v>73</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>CETEFE</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://cetefe.org</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="n">
+        <v>78</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Dra. Flávia Brito</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://draflaviabrito.com.br</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>5527981229670</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="n">
+        <v>73</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Guia Médico</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://guiamedico.unimedvitoria.com.br</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="n">
+        <v>44</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Vitória (ES) - Faculdade Inspirar</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://www.inspirar.com.br</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="n">
+        <v>33</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Crefito 15</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://www.crefito15.org.br</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="n">
+        <v>75</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Belo Horizonte: Dados 2026</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://ondeabrir.com</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="n">
+        <v>90</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Médicos Online em Belo Horizonte (MG)</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://whatsmed.com.br</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="n">
+        <v>88</v>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Dental Free</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://www.dentalfree.com.br</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="n">
+        <v>81</v>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Uniodonto Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://uniodontobh.com.br</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>5531993287918</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="n">
+        <v>80</v>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>LeDeux Odontologia · Clínica Premium em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://ledeuxodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="n">
+        <v>67</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>PromoDental</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://promodental.com.br</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>553132533400</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="n">
+        <v>75</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Dr Alysson Resende</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://www.alyssonresende.com.br</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="n">
+        <v>56</v>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://slmandic.edu.br</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>5519992288781</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="n">
+        <v>80</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Psicólogo BH - Atendimento Psicológico em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://www.psicologobelohorizonte.com.br</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="n">
+        <v>73</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Psicólogos em Belo Horizonte, MG</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://terappy.com.br</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>5592984020249</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="n">
+        <v>73</v>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Psicólogos em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://www.pratimed.com.br</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>5521967662304</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="n">
+        <v>80</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Auxiliadora Crepaldi</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://www.auxiliadoracrepaldi.com.br</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="n">
+        <v>73</v>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Erika Neves</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://www.erikaneves.com.br</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="n">
+        <v>75</v>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Advogado em Belo Horizonte (BH)</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://www.oliveiramiranda.adv.br</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>5531998440357</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="n">
+        <v>73</v>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Rafael Vieira</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://advrafael.com.br</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>553190726984</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="n">
+        <v>73</v>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>André Beliene</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://andrebelieneadvogado.com.br</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>5531995356105</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="n">
+        <v>73</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Escritório de Advocacia em BH</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://settemadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>5531981062500</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="n">
+        <v>73</v>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Túlio Vianna Advocacia Criminal</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://tuliovianna.adv.br</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>5531998551641</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="n">
+        <v>73</v>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Rômulo Brasil Advogados</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://romulobrasil.adv.br</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>553181016517</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="n">
+        <v>73</v>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Josimar Bezerra Advogados</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://www.josimarbezerraadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="n">
+        <v>45</v>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://www.defisd.cefetmg.br</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Bacharelado em Educação Física</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://www.unibh.br</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="n">
+        <v>62</v>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Educação Física (Bacharelado)</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://www.ufmg.br</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="n">
+        <v>67</v>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Faculdade de EDUCAÇÃO FÍSICA em BELO HORIZONTE</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://www.educamaisbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="n">
+        <v>44</v>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>EEFFTO</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://www.eeffto.ufmg.br</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Apartamentos com academia para alugar perto de...</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://www.quintoandar.com.br</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="n">
+        <v>80</v>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>De Belo Horizonte, MG para Timóteo, MG de ônibus</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://www.checkmybus.com.br</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="n">
+        <v>67</v>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>ONEFIT ACADEMIA, Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://br.polomap.com</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="n">
+        <v>33</v>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta em Belo Horizonte-MG</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>https://cliniguia.com</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="n">
+        <v>56</v>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>A Clínica Biophysical</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>https://www.clinicadefisioterapiabh.com.br</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="n">
+        <v>67</v>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>médico Rio de Janeiro em Rio de Janeiro (RJ)</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>https://zapvida.com</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>554792174808</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="n">
+        <v>75</v>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Centro Médico Rio Barra: Consultas, Centro Médico...</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>https://portaljpa.com</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>5521980769543</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="n">
+        <v>64</v>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Dr. Carlos Henrique Ferreira Cruz, Médico - Perfil completo</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>https://www.medstream.com.br</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="n">
+        <v>53</v>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Anúncio: Propagandista médico (rio de janeiro) #950703</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://www.netvagas.com.br</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="n">
+        <v>56</v>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>https://ufrj.br</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="n">
+        <v>76</v>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Dr. Bruno Abrantes, Cirurgião-Dentista - Perfil completo</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>https://www.ident.com.br</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="n">
+        <v>62</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Melhores Dentista Do Rio De Janeiro Rj em Rio de Janeiro RJ...</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://portaljpa.com.br</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>5521980769543</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="n">
+        <v>64</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Reservas e descontos nos motéis da Zona Norte do Rio de Janeiro...</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://www.guiademoteis.com.br</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="n">
+        <v>33</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Scenic Aerial View of Rio de Janeiro Coastline · Free Stock Photo</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>https://www.pexels.com</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="n">
+        <v>33</v>
+      </c>
+      <c r="L279" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L279"/>
+  <dimension ref="A1:L349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10987,10 +10987,8 @@
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>5527992716293</t>
-        </is>
+      <c r="I217" t="n">
+        <v>5527992716293</v>
       </c>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="n">
@@ -11039,10 +11037,8 @@
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>5527997209784</t>
-        </is>
+      <c r="I218" t="n">
+        <v>5527997209784</v>
       </c>
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="n">
@@ -11091,10 +11087,8 @@
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>5527992799432</t>
-        </is>
+      <c r="I219" t="n">
+        <v>5527992799432</v>
       </c>
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="n">
@@ -11575,10 +11569,8 @@
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>5527999045444</t>
-        </is>
+      <c r="I229" t="n">
+        <v>5527999045444</v>
       </c>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="n">
@@ -11627,10 +11619,8 @@
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>5527996901700</t>
-        </is>
+      <c r="I230" t="n">
+        <v>5527996901700</v>
       </c>
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="n">
@@ -11679,10 +11669,8 @@
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>5527999489898</t>
-        </is>
+      <c r="I231" t="n">
+        <v>5527999489898</v>
       </c>
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="n">
@@ -11827,10 +11815,8 @@
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>5527998114107</t>
-        </is>
+      <c r="I234" t="n">
+        <v>5527998114107</v>
       </c>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="n">
@@ -11975,10 +11961,8 @@
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>5527981229670</t>
-        </is>
+      <c r="I237" t="n">
+        <v>5527981229670</v>
       </c>
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="n">
@@ -12315,10 +12299,8 @@
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>5531993287918</t>
-        </is>
+      <c r="I244" t="n">
+        <v>5531993287918</v>
       </c>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="n">
@@ -12415,10 +12397,8 @@
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>553132533400</t>
-        </is>
+      <c r="I246" t="n">
+        <v>553132533400</v>
       </c>
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="n">
@@ -12515,10 +12495,8 @@
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>5519992288781</t>
-        </is>
+      <c r="I248" t="n">
+        <v>5519992288781</v>
       </c>
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="n">
@@ -12615,10 +12593,8 @@
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>5592984020249</t>
-        </is>
+      <c r="I250" t="n">
+        <v>5592984020249</v>
       </c>
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="n">
@@ -12667,10 +12643,8 @@
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>5521967662304</t>
-        </is>
+      <c r="I251" t="n">
+        <v>5521967662304</v>
       </c>
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="n">
@@ -12815,10 +12789,8 @@
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>5531998440357</t>
-        </is>
+      <c r="I254" t="n">
+        <v>5531998440357</v>
       </c>
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="n">
@@ -12867,10 +12839,8 @@
         </is>
       </c>
       <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>553190726984</t>
-        </is>
+      <c r="I255" t="n">
+        <v>553190726984</v>
       </c>
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="n">
@@ -12919,10 +12889,8 @@
         </is>
       </c>
       <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>5531995356105</t>
-        </is>
+      <c r="I256" t="n">
+        <v>5531995356105</v>
       </c>
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="n">
@@ -12971,10 +12939,8 @@
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>5531981062500</t>
-        </is>
+      <c r="I257" t="n">
+        <v>5531981062500</v>
       </c>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="n">
@@ -13023,10 +12989,8 @@
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>5531998551641</t>
-        </is>
+      <c r="I258" t="n">
+        <v>5531998551641</v>
       </c>
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="n">
@@ -13075,10 +13039,8 @@
         </is>
       </c>
       <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>553181016517</t>
-        </is>
+      <c r="I259" t="n">
+        <v>553181016517</v>
       </c>
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="n">
@@ -13655,10 +13617,8 @@
         </is>
       </c>
       <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>554792174808</t>
-        </is>
+      <c r="I271" t="n">
+        <v>554792174808</v>
       </c>
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="n">
@@ -13707,10 +13667,8 @@
         </is>
       </c>
       <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>5521980769543</t>
-        </is>
+      <c r="I272" t="n">
+        <v>5521980769543</v>
       </c>
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="n">
@@ -13951,10 +13909,8 @@
         </is>
       </c>
       <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>5521980769543</t>
-        </is>
+      <c r="I277" t="n">
+        <v>5521980769543</v>
       </c>
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="n">
@@ -14062,6 +14018,3490 @@
         </is>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Centro Médico Adventista</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://curitiba.clinicaadventista.org.br</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="n">
+        <v>22</v>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Centro Médico em Curitiba</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://incorporecentromedico.com.br</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>5541998281051</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="n">
+        <v>88</v>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Paraná Clínicas</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://paranaclinicas.com.br</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="n">
+        <v>71</v>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>https://santacasacuritiba.com.br</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="n">
+        <v>76</v>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>CMI - Centro Médico Integrado Curitiba</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>https://cmicentromedicointegrado.com.br</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>5541991980029</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="n">
+        <v>87</v>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Policlínica Capão Raso</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>https://policlinicacapaoraso.com.br</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>5541985084617</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="n">
+        <v>64</v>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Ventura Clínica</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>https://venturaclinica.com.br</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr"/>
+      <c r="K286" t="n">
+        <v>65</v>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Médicos Curitiba</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>https://medicos.curitiba.br</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="n">
+        <v>0</v>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Dr. Shadi Abdulla</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>https://www.shadiabdulla.com.br</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>5541995181395</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="n">
+        <v>69</v>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Dentistas Curitiba</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>https://dentistas.curitiba.br</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>5541991447326</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="n">
+        <v>87</v>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Curitiba Dental Office</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>https://www.curitibadentaloffice.com.br</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="n">
+        <v>75</v>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Clínica de Odontologia em Curitiba, PR: Serviços</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://www.up.edu.br</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="n">
+        <v>44</v>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>You Odonto</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://youodonto.com.br</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>5541991457638</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr"/>
+      <c r="K292" t="n">
+        <v>69</v>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>ILAPEO: Home</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://www.ilapeo.com.br</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="n">
+        <v>75</v>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Gross Odontologia</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>https://www.grossodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="n">
+        <v>69</v>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Psicólogo Curitiba — Agendar Consulta</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://www.psiqdoctor.com.br</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
+      <c r="K295" t="n">
+        <v>56</v>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Os 7 Psicólogos em Curitiba</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://terappio.com</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="n">
+        <v>67</v>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Giovana Tessaro</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://giovanatessaro.com.br</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>5541999954585</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr"/>
+      <c r="K297" t="n">
+        <v>73</v>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Nutty Ramos Terapeuta</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://www.nuttyramosterapeuta.com</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+      <c r="J298" t="inlineStr"/>
+      <c r="K298" t="n">
+        <v>73</v>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Psicoterapias Curitiba</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>https://www.psicoterapiascuritiba.com</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="n">
+        <v>33</v>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Os 10 Psicoterapeutas mais indicados em Curitiba PR</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://www.boaconsulta.com</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
+      <c r="K300" t="n">
+        <v>80</v>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Advogado de Direito Civil e Contratos em Curitiba</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>https://moraistavares.adv.br</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>5532999999999</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr"/>
+      <c r="K301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Pacheco Advocacia: Advogado em Curitiba</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>https://pachecoadvocacia.adv.br</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>554196201718</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr"/>
+      <c r="K302" t="n">
+        <v>73</v>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Hapner Kroetz Advogados</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>https://www.hapnerkroetz.com.br</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+      <c r="J303" t="inlineStr"/>
+      <c r="K303" t="n">
+        <v>82</v>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Advogado de Familia em Curitiba: Página Inicial</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>https://fladvogadocuritiba.com.br</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>5541988652670</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="n">
+        <v>73</v>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Melo Advogados</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>https://meloadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>5541991567228</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr"/>
+      <c r="K305" t="n">
+        <v>64</v>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>HOME NOVO FSA</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>https://nfernandes.com.br</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>5541995009977</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr"/>
+      <c r="K306" t="n">
+        <v>82</v>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Andersen Ballão Advocacia: Home</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>http://andersenballao.com.br</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
+      <c r="J307" t="inlineStr"/>
+      <c r="K307" t="n">
+        <v>89</v>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Faculdade de Educação Física em Curitiba - PR</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>https://cursos.up.edu.br</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
+      <c r="J308" t="inlineStr"/>
+      <c r="K308" t="n">
+        <v>44</v>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>https://feiradecursos.ufpr.br</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr"/>
+      <c r="K309" t="n">
+        <v>33</v>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>https://www.pucpr.br</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>554132711555</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr"/>
+      <c r="K310" t="n">
+        <v>75</v>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Educação Física (Bacharelado) na PUCPR</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>https://especiais.gazetadopovo.com.br</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
+      <c r="J311" t="inlineStr"/>
+      <c r="K311" t="n">
+        <v>56</v>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>CURVES ACADEMIA - Academias</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>https://qualotelefone.com</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
+      <c r="J312" t="inlineStr"/>
+      <c r="K312" t="n">
+        <v>44</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>https://forceoneacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr"/>
+      <c r="K313" t="n">
+        <v>80</v>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta do HC de Curitiba lança materiais informativos sobre ...</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>https://unidospelavida.org.br</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>5541996300022</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr"/>
+      <c r="K314" t="n">
+        <v>62</v>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Congresso Internacional Inspirar de Fisioterapia Pélvica</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>https://congressopelvica.com.br</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
+      <c r="J315" t="inlineStr"/>
+      <c r="K315" t="n">
+        <v>67</v>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Salary: Recepcionista Clinica Medica in Porto Alegre, Brazil 2026</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
+      <c r="J316" t="inlineStr"/>
+      <c r="K316" t="n">
+        <v>33</v>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Derma Roller Manchas</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>https://clinicabergmann.com.br</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+      <c r="J317" t="inlineStr"/>
+      <c r="K317" t="n">
+        <v>65</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Ortopedia Mariland em Porto Alegre - RS</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>https://spotway.com.br</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>5512991730887</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr"/>
+      <c r="K318" t="n">
+        <v>81</v>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Anestesiologista em Rio Branco - Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>https://www.conveniosocial.com.br</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+      <c r="J319" t="inlineStr"/>
+      <c r="K319" t="n">
+        <v>33</v>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Clínica Popular em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>https://blog.amorsaude.com.br</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+      <c r="J320" t="inlineStr"/>
+      <c r="K320" t="n">
+        <v>62</v>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Rede de Clínicas Médicas, Grande Porto Alegre - RS</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>https://www.clinicasalute.com.br</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>555130141111</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="n">
+        <v>75</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>https://instamedsaude.com.br</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>5551995914372</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="n">
+        <v>59</v>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Teleconsulta com médicos de Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>https://telemedicinamorsch.com.br</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
+      <c r="J323" t="inlineStr"/>
+      <c r="K323" t="n">
+        <v>75</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Clinicentro</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>https://www.clinicentro.com.br</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>555195560177</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr"/>
+      <c r="K324" t="n">
+        <v>67</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>https://www.sorridere.net</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>555133463277</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr"/>
+      <c r="K325" t="n">
+        <v>73</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>WK•R</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>https://www.wkrodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>5551986648451</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr"/>
+      <c r="K326" t="n">
+        <v>73</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Clínica Dental Center</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>https://clinicadentalcenter.com.br</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
+      <c r="J327" t="inlineStr"/>
+      <c r="K327" t="n">
+        <v>47</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Dentista na Zona Sul de Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>https://www.integrareodontologia.com</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
+      <c r="J328" t="inlineStr"/>
+      <c r="K328" t="n">
+        <v>56</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Centro Odontológico R8</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>https://centroodontologicor8.com.br</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
+      <c r="J329" t="inlineStr"/>
+      <c r="K329" t="n">
+        <v>53</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Núcleo de Psicologia Porto Alegrense (NPPA)</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>https://www.nucleodepsicologiapoa.com</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="n">
+        <v>73</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Psicobreve</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>https://www.psicobreve.com.br</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>555132262225</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr"/>
+      <c r="K331" t="n">
+        <v>80</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Psicóloga em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>https://psicologaportoalegre.com</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="n">
+        <v>80</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Psicologia Viva: Consulte com um psicólogo online de qualquer lugar</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>https://www.psicologiaviva.com.br</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>5521966964821</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr"/>
+      <c r="K333" t="n">
+        <v>80</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Clínica de psicologia de Porto Alegre proporciona atendimento ...</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>https://gauchazh.clicrbs.com.br</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>5551996674125</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr"/>
+      <c r="K334" t="n">
+        <v>56</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Psicoterapia Online Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>https://clinicarpsicologiaonline.com.br</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>5551996786184</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr"/>
+      <c r="K335" t="n">
+        <v>80</v>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Boa Terapia: Psicólogo Em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>https://boaterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>555193922723</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr"/>
+      <c r="K336" t="n">
+        <v>80</v>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Psicóloga em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>https://www.rosangelapsicologa.com</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>5551983374242</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr"/>
+      <c r="K337" t="n">
+        <v>80</v>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Terapeuta Cognitivo Comportamental</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>https://www.psicologocognitivoemportoalegre.com</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
+      <c r="J338" t="inlineStr"/>
+      <c r="K338" t="n">
+        <v>67</v>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Advogados e Escritórios de Advocacia em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>https://guia.poa.br</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
+      <c r="J339" t="inlineStr"/>
+      <c r="K339" t="n">
+        <v>82</v>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>106 Advogados em Porto Alegre/RS (2026)</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>https://acharadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
+      <c r="J340" t="inlineStr"/>
+      <c r="K340" t="n">
+        <v>64</v>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>CG Advogados</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>https://www.cgadvogados.com</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
+      <c r="J341" t="inlineStr"/>
+      <c r="K341" t="n">
+        <v>73</v>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Portanova</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>https://www.portanova.adv.br</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="n">
+        <v>73</v>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Carpena Advogados</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>https://carpena.com.br</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>555132333588</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr"/>
+      <c r="K343" t="n">
+        <v>82</v>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Advogado Especialista Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>https://dihladvogados.adv.br</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>5551999882013</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr"/>
+      <c r="K344" t="n">
+        <v>100</v>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Alves Nunes Advogados</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>https://advogadosemportoalegre.adv.br</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>555135745063</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr"/>
+      <c r="K345" t="n">
+        <v>73</v>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Rama Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>https://www.ramaadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr"/>
+      <c r="J346" t="inlineStr"/>
+      <c r="K346" t="n">
+        <v>36</v>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>https://prefeitura.poa.br</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>555134330156</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr"/>
+      <c r="K347" t="n">
+        <v>67</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>https://www.ulbra.br</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>555192741192</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr"/>
+      <c r="K348" t="n">
+        <v>71</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>As 20 melhores academias em Porto Alegre (RS) · AvataReel</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>https://avatareel.com</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr"/>
+      <c r="K349" t="n">
+        <v>44</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L349"/>
+  <dimension ref="A1:L411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14103,10 +14103,8 @@
         </is>
       </c>
       <c r="H281" t="inlineStr"/>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>5541998281051</t>
-        </is>
+      <c r="I281" t="n">
+        <v>5541998281051</v>
       </c>
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="n">
@@ -14251,10 +14249,8 @@
         </is>
       </c>
       <c r="H284" t="inlineStr"/>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>5541991980029</t>
-        </is>
+      <c r="I284" t="n">
+        <v>5541991980029</v>
       </c>
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="n">
@@ -14303,10 +14299,8 @@
         </is>
       </c>
       <c r="H285" t="inlineStr"/>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>5541985084617</t>
-        </is>
+      <c r="I285" t="n">
+        <v>5541985084617</v>
       </c>
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="n">
@@ -14451,10 +14445,8 @@
         </is>
       </c>
       <c r="H288" t="inlineStr"/>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>5541995181395</t>
-        </is>
+      <c r="I288" t="n">
+        <v>5541995181395</v>
       </c>
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="n">
@@ -14503,10 +14495,8 @@
         </is>
       </c>
       <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>5541991447326</t>
-        </is>
+      <c r="I289" t="n">
+        <v>5541991447326</v>
       </c>
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="n">
@@ -14651,10 +14641,8 @@
         </is>
       </c>
       <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>5541991457638</t>
-        </is>
+      <c r="I292" t="n">
+        <v>5541991457638</v>
       </c>
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="n">
@@ -14895,10 +14883,8 @@
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>5541999954585</t>
-        </is>
+      <c r="I297" t="n">
+        <v>5541999954585</v>
       </c>
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="n">
@@ -15091,10 +15077,8 @@
         </is>
       </c>
       <c r="H301" t="inlineStr"/>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>5532999999999</t>
-        </is>
+      <c r="I301" t="n">
+        <v>5532999999999</v>
       </c>
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="n">
@@ -15143,10 +15127,8 @@
         </is>
       </c>
       <c r="H302" t="inlineStr"/>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>554196201718</t>
-        </is>
+      <c r="I302" t="n">
+        <v>554196201718</v>
       </c>
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="n">
@@ -15243,10 +15225,8 @@
         </is>
       </c>
       <c r="H304" t="inlineStr"/>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>5541988652670</t>
-        </is>
+      <c r="I304" t="n">
+        <v>5541988652670</v>
       </c>
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="n">
@@ -15295,10 +15275,8 @@
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>5541991567228</t>
-        </is>
+      <c r="I305" t="n">
+        <v>5541991567228</v>
       </c>
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="n">
@@ -15347,10 +15325,8 @@
         </is>
       </c>
       <c r="H306" t="inlineStr"/>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>5541995009977</t>
-        </is>
+      <c r="I306" t="n">
+        <v>5541995009977</v>
       </c>
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="n">
@@ -15543,10 +15519,8 @@
         </is>
       </c>
       <c r="H310" t="inlineStr"/>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>554132711555</t>
-        </is>
+      <c r="I310" t="n">
+        <v>554132711555</v>
       </c>
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="n">
@@ -15739,10 +15713,8 @@
         </is>
       </c>
       <c r="H314" t="inlineStr"/>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>5541996300022</t>
-        </is>
+      <c r="I314" t="n">
+        <v>5541996300022</v>
       </c>
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="n">
@@ -15935,10 +15907,8 @@
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>5512991730887</t>
-        </is>
+      <c r="I318" t="n">
+        <v>5512991730887</v>
       </c>
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="n">
@@ -16083,10 +16053,8 @@
         </is>
       </c>
       <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>555130141111</t>
-        </is>
+      <c r="I321" t="n">
+        <v>555130141111</v>
       </c>
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="n">
@@ -16135,10 +16103,8 @@
         </is>
       </c>
       <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr">
-        <is>
-          <t>5551995914372</t>
-        </is>
+      <c r="I322" t="n">
+        <v>5551995914372</v>
       </c>
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="n">
@@ -16235,10 +16201,8 @@
         </is>
       </c>
       <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>555195560177</t>
-        </is>
+      <c r="I324" t="n">
+        <v>555195560177</v>
       </c>
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="n">
@@ -16287,10 +16251,8 @@
         </is>
       </c>
       <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>555133463277</t>
-        </is>
+      <c r="I325" t="n">
+        <v>555133463277</v>
       </c>
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="n">
@@ -16339,10 +16301,8 @@
         </is>
       </c>
       <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>5551986648451</t>
-        </is>
+      <c r="I326" t="n">
+        <v>5551986648451</v>
       </c>
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="n">
@@ -16583,10 +16543,8 @@
         </is>
       </c>
       <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>555132262225</t>
-        </is>
+      <c r="I331" t="n">
+        <v>555132262225</v>
       </c>
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="n">
@@ -16683,10 +16641,8 @@
         </is>
       </c>
       <c r="H333" t="inlineStr"/>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>5521966964821</t>
-        </is>
+      <c r="I333" t="n">
+        <v>5521966964821</v>
       </c>
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="n">
@@ -16735,10 +16691,8 @@
         </is>
       </c>
       <c r="H334" t="inlineStr"/>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>5551996674125</t>
-        </is>
+      <c r="I334" t="n">
+        <v>5551996674125</v>
       </c>
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="n">
@@ -16787,10 +16741,8 @@
         </is>
       </c>
       <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>5551996786184</t>
-        </is>
+      <c r="I335" t="n">
+        <v>5551996786184</v>
       </c>
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="n">
@@ -16839,10 +16791,8 @@
         </is>
       </c>
       <c r="H336" t="inlineStr"/>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>555193922723</t>
-        </is>
+      <c r="I336" t="n">
+        <v>555193922723</v>
       </c>
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="n">
@@ -16891,10 +16841,8 @@
         </is>
       </c>
       <c r="H337" t="inlineStr"/>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>5551983374242</t>
-        </is>
+      <c r="I337" t="n">
+        <v>5551983374242</v>
       </c>
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="n">
@@ -17183,10 +17131,8 @@
         </is>
       </c>
       <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>555132333588</t>
-        </is>
+      <c r="I343" t="n">
+        <v>555132333588</v>
       </c>
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="n">
@@ -17235,10 +17181,8 @@
         </is>
       </c>
       <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>5551999882013</t>
-        </is>
+      <c r="I344" t="n">
+        <v>5551999882013</v>
       </c>
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="n">
@@ -17287,10 +17231,8 @@
         </is>
       </c>
       <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>555135745063</t>
-        </is>
+      <c r="I345" t="n">
+        <v>555135745063</v>
       </c>
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="n">
@@ -17387,10 +17329,8 @@
         </is>
       </c>
       <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>555134330156</t>
-        </is>
+      <c r="I347" t="n">
+        <v>555134330156</v>
       </c>
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="n">
@@ -17439,10 +17379,8 @@
         </is>
       </c>
       <c r="H348" t="inlineStr"/>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>555192741192</t>
-        </is>
+      <c r="I348" t="n">
+        <v>555192741192</v>
       </c>
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="n">
@@ -17502,6 +17440,3058 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>https://riobrancocentromedico.com.br</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>5512974026261</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="n">
+        <v>69</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Clinica Medicos</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>https://www.clinicamedicos.com.br</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>5521972416496</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr"/>
+      <c r="K351" t="n">
+        <v>62</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Clínica Popular Vital Brasil</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>https://www.clinicapopularvitalbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
+      <c r="K352" t="n">
+        <v>0</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Henrique Representante Médico</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>https://henrique-representante-medico.ueniweb.com</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="n">
+        <v>93</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>10 MELHORES Clínicas Médicas Gerais em Rio Branco, AC</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>https://www.guiatelefone.com</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="n">
+        <v>81</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Guia de Saúde</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>https://realconvenios.com.br</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>5568999847320</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="n">
+        <v>69</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Dentista - Implante dentário</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>https://clinicaodontorio.com.br</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>5568999876708</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="n">
+        <v>80</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Dentistas em Rio Branco</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>https://www.encontrariobranco.com.br</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="inlineStr"/>
+      <c r="K357" t="n">
+        <v>55</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Psicoclean</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>https://www.psicoclean.com.br</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>5568999897343</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr"/>
+      <c r="K358" t="n">
+        <v>73</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Psicólogos em Rio Branco</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>https://mindee.me</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr"/>
+      <c r="K359" t="n">
+        <v>87</v>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>1 GUIA MÉDICO LOCAL UNIMED RIO BRANCO</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>https://unimedrb.com.br</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
+      <c r="J360" t="inlineStr"/>
+      <c r="K360" t="n">
+        <v>44</v>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Rio Branco /AC</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>https://tehabilitar.com</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="n">
+        <v>53</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Kelly Cristina Costa Albuquerque</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>https://www.escavador.com</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
+      <c r="J362" t="inlineStr"/>
+      <c r="K362" t="n">
+        <v>33</v>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Arteterapia como estratégia de cuidado em saúde mental no âmbito ...</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>https://www.jmphc.com.br</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
+      <c r="J363" t="inlineStr"/>
+      <c r="K363" t="n">
+        <v>60</v>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Grupo Terapêutico em Centro de Referência para Mulheres em ...</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>https://periodicos.ufac.br</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
+      <c r="J364" t="inlineStr"/>
+      <c r="K364" t="n">
+        <v>67</v>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Rodrigo Aiache Advogados</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>https://www.aiache.adv.br</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>556832246324</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr"/>
+      <c r="K365" t="n">
+        <v>64</v>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Advogados Rio Branco (Acre)</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>https://www.mundoadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr"/>
+      <c r="K366" t="n">
+        <v>0</v>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Advogado correspondente em Rio Branco</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>https://correspondentesnaweb.com.br</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
+      <c r="J367" t="inlineStr"/>
+      <c r="K367" t="n">
+        <v>73</v>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Efeito da atividade física programada sobre a aptidão</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>https://www.scielo.br</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
+      <c r="J368" t="inlineStr"/>
+      <c r="K368" t="n">
+        <v>22</v>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>https://www.openstreetmap.org</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
+      <c r="J369" t="inlineStr"/>
+      <c r="K369" t="n">
+        <v>33</v>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Academias em Rio Branco, AC, Brasil</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>https://brfirmas.org</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
+      <c r="J370" t="inlineStr"/>
+      <c r="K370" t="n">
+        <v>33</v>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Ac. Atitude - Acre — BJJ in Rio Branco</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>https://rollmap.co</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr"/>
+      <c r="J371" t="inlineStr"/>
+      <c r="K371" t="n">
+        <v>33</v>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Link to applocal.com.br</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>https://applocal.com.br</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
+      <c r="J372" t="inlineStr"/>
+      <c r="K372" t="n">
+        <v>33</v>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Fisioclin - Reabilitação - Fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>https://fisioclin-centro-de-reabilitacao.ueniweb.com</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
+      <c r="J373" t="inlineStr"/>
+      <c r="K373" t="n">
+        <v>93</v>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Fisiocentro - Fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>https://fisiocentro.ueniweb.com</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
+      <c r="J374" t="inlineStr"/>
+      <c r="K374" t="n">
+        <v>93</v>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Clínica Promed</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>https://www.clinicapromed.com</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>5596991864319</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr"/>
+      <c r="K375" t="n">
+        <v>76</v>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Consultório do Povo</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>https://consultoriodopovo.com.br</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>5596991526779</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr"/>
+      <c r="K376" t="n">
+        <v>69</v>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>https://macapa.infoisinfo-br.com</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr"/>
+      <c r="J377" t="inlineStr"/>
+      <c r="K377" t="n">
+        <v>64</v>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>GUIA MÉDICO: MACAPÁ/ AP Pag.: 1</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>https://old.tjap.jus.br</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr"/>
+      <c r="J378" t="inlineStr"/>
+      <c r="K378" t="n">
+        <v>33</v>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Especialidades Médicas</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>https://www.saocamilomacapa.org.br</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
+      <c r="J379" t="inlineStr"/>
+      <c r="K379" t="n">
+        <v>91</v>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Consultório Dra. Marina Sales</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>https://acheioprofissional.com.br</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr"/>
+      <c r="I380" t="inlineStr"/>
+      <c r="J380" t="inlineStr"/>
+      <c r="K380" t="n">
+        <v>73</v>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Saúde Mental em Macapá</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>https://triagefy.io</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>5548988790123</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr"/>
+      <c r="K381" t="n">
+        <v>81</v>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Unidas</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>https://www.unidas.com.br</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr"/>
+      <c r="I382" t="inlineStr"/>
+      <c r="J382" t="inlineStr"/>
+      <c r="K382" t="n">
+        <v>44</v>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Marly Barbosa</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>https://consultoriosodontologicos.com.br</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr"/>
+      <c r="J383" t="inlineStr"/>
+      <c r="K383" t="n">
+        <v>75</v>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Implantes Dentários em Macapá</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>https://www.oralsin.com.br</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>5511956058611</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="n">
+        <v>62</v>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>LIDIA PEREIRA COSTA</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>https://psicologobrasil.com</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="n">
+        <v>80</v>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Psicólogo em Macapá - AP (Terapia Online)</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>https://ceciliafreytas.com.br</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr"/>
+      <c r="J386" t="inlineStr"/>
+      <c r="K386" t="n">
+        <v>81</v>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>As melhores 5 empresas de Psicólogo em Macapá</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>https://www.buscja.com</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="n">
+        <v>73</v>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Advogados e Escritórios de Advocacia em Macapá</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>https://guia.macapa.br</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="n">
+        <v>82</v>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Coutinho &amp; Ribeiro Advogados</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>https://www.coutinhoeribeiro.adv.br</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="n">
+        <v>55</v>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Advogados em Macapá, Amapá</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>https://listaamarela.com.br</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr"/>
+      <c r="J390" t="inlineStr"/>
+      <c r="K390" t="n">
+        <v>64</v>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Frederico Vales Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>https://fvales.com</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>5596981210358</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr"/>
+      <c r="K391" t="n">
+        <v>64</v>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Advogado em Macapá/Amapá</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>https://www.ribeirocavalcante.com.br</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr"/>
+      <c r="J392" t="inlineStr"/>
+      <c r="K392" t="n">
+        <v>82</v>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Advogado em Macapá</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>https://www.galvaoesilva.com</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr"/>
+      <c r="J393" t="inlineStr"/>
+      <c r="K393" t="n">
+        <v>100</v>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Macapá (AP)</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>https://skyfitacademia.com</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr"/>
+      <c r="J394" t="inlineStr"/>
+      <c r="K394" t="n">
+        <v>40</v>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Faculdades de Macapá. UNIFAP e UNIP</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>https://www.faculdades.inf.br</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr"/>
+      <c r="I395" t="inlineStr"/>
+      <c r="J395" t="inlineStr"/>
+      <c r="K395" t="n">
+        <v>56</v>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>SKYFIT Macapá: da ideia em família à academia que virou ...</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>https://www.jornaldosmunicipiosap.com.br</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr"/>
+      <c r="J396" t="inlineStr"/>
+      <c r="K396" t="n">
+        <v>69</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Musculação</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>https://www.sescamapa.com.br</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>559691525961</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr"/>
+      <c r="K397" t="n">
+        <v>80</v>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Fisioterapeutas perto de você em Macapá</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>https://fisioterapeutaspertodemim.com</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr"/>
+      <c r="K398" t="n">
+        <v>87</v>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>REABILITARE FISIOTERAPIA ESPECIALIZADA em Macapá - AP</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>https://www.acupuntura.net.br</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr"/>
+      <c r="J399" t="inlineStr"/>
+      <c r="K399" t="n">
+        <v>88</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Acesso Saúde Manaus</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>https://acessosaudemanaus.com.br</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>5592994907500</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr"/>
+      <c r="K400" t="n">
+        <v>75</v>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Clínica Mais Vida Manaus</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>https://clinicamaisvida.net.br</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>5592994937838</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr"/>
+      <c r="K401" t="n">
+        <v>76</v>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Mais Clinica</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>https://www.maisclinica.med.br</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>559285565437</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr"/>
+      <c r="K402" t="n">
+        <v>81</v>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Upclin Manaus</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>https://upclinmanaus.com.br</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>5592986025043</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr"/>
+      <c r="K403" t="n">
+        <v>69</v>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Ultrassonografias e Especialidades Médicas Informações</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>https://www.manausmedicalcenter.com.br</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr"/>
+      <c r="K404" t="n">
+        <v>56</v>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Sibamed</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>https://sibamedclinicamedica.com.br</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>5592992927576</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr"/>
+      <c r="K405" t="n">
+        <v>94</v>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Pró-Saúde</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>https://prosaudedrluizfernando.com.br</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="inlineStr"/>
+      <c r="K406" t="n">
+        <v>69</v>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Convênio Médico Manaus (AM)</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>https://conveniomedico.com.br</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>5508001115000</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr"/>
+      <c r="K407" t="n">
+        <v>53</v>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>AM: médico é afastado após ser flagrado com estagiária...</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>https://www.cnnbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr"/>
+      <c r="J408" t="inlineStr"/>
+      <c r="K408" t="n">
+        <v>82</v>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Top 16 Dental Clinics &amp; Dentists in Manaus</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>https://www.dentalclinics.care</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr"/>
+      <c r="J409" t="inlineStr"/>
+      <c r="K409" t="n">
+        <v>33</v>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Dentista em Manaus</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>https://dentistasmanaus.com.br</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr"/>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>5511912062131</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr"/>
+      <c r="K410" t="n">
+        <v>56</v>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Dr. Sebastião Nascimento</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>https://www.sebastiao-nascimento.com</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr"/>
+      <c r="I411" t="inlineStr"/>
+      <c r="J411" t="inlineStr"/>
+      <c r="K411" t="n">
+        <v>73</v>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -17477,10 +17477,8 @@
         </is>
       </c>
       <c r="H350" t="inlineStr"/>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>5512974026261</t>
-        </is>
+      <c r="I350" t="n">
+        <v>5512974026261</v>
       </c>
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="n">
@@ -17529,10 +17527,8 @@
         </is>
       </c>
       <c r="H351" t="inlineStr"/>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>5521972416496</t>
-        </is>
+      <c r="I351" t="n">
+        <v>5521972416496</v>
       </c>
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="n">
@@ -17725,10 +17721,8 @@
         </is>
       </c>
       <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t>5568999847320</t>
-        </is>
+      <c r="I355" t="n">
+        <v>5568999847320</v>
       </c>
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="n">
@@ -17777,10 +17771,8 @@
         </is>
       </c>
       <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr">
-        <is>
-          <t>5568999876708</t>
-        </is>
+      <c r="I356" t="n">
+        <v>5568999876708</v>
       </c>
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="n">
@@ -17877,10 +17869,8 @@
         </is>
       </c>
       <c r="H358" t="inlineStr"/>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>5568999897343</t>
-        </is>
+      <c r="I358" t="n">
+        <v>5568999897343</v>
       </c>
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="n">
@@ -18217,10 +18207,8 @@
         </is>
       </c>
       <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr">
-        <is>
-          <t>556832246324</t>
-        </is>
+      <c r="I365" t="n">
+        <v>556832246324</v>
       </c>
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="n">
@@ -18701,10 +18689,8 @@
         </is>
       </c>
       <c r="H375" t="inlineStr"/>
-      <c r="I375" t="inlineStr">
-        <is>
-          <t>5596991864319</t>
-        </is>
+      <c r="I375" t="n">
+        <v>5596991864319</v>
       </c>
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="n">
@@ -18753,10 +18739,8 @@
         </is>
       </c>
       <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr">
-        <is>
-          <t>5596991526779</t>
-        </is>
+      <c r="I376" t="n">
+        <v>5596991526779</v>
       </c>
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="n">
@@ -18997,10 +18981,8 @@
         </is>
       </c>
       <c r="H381" t="inlineStr"/>
-      <c r="I381" t="inlineStr">
-        <is>
-          <t>5548988790123</t>
-        </is>
+      <c r="I381" t="n">
+        <v>5548988790123</v>
       </c>
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="n">
@@ -19145,10 +19127,8 @@
         </is>
       </c>
       <c r="H384" t="inlineStr"/>
-      <c r="I384" t="inlineStr">
-        <is>
-          <t>5511956058611</t>
-        </is>
+      <c r="I384" t="n">
+        <v>5511956058611</v>
       </c>
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="n">
@@ -19485,10 +19465,8 @@
         </is>
       </c>
       <c r="H391" t="inlineStr"/>
-      <c r="I391" t="inlineStr">
-        <is>
-          <t>5596981210358</t>
-        </is>
+      <c r="I391" t="n">
+        <v>5596981210358</v>
       </c>
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="n">
@@ -19777,10 +19755,8 @@
         </is>
       </c>
       <c r="H397" t="inlineStr"/>
-      <c r="I397" t="inlineStr">
-        <is>
-          <t>559691525961</t>
-        </is>
+      <c r="I397" t="n">
+        <v>559691525961</v>
       </c>
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="n">
@@ -19925,10 +19901,8 @@
         </is>
       </c>
       <c r="H400" t="inlineStr"/>
-      <c r="I400" t="inlineStr">
-        <is>
-          <t>5592994907500</t>
-        </is>
+      <c r="I400" t="n">
+        <v>5592994907500</v>
       </c>
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="n">
@@ -19977,10 +19951,8 @@
         </is>
       </c>
       <c r="H401" t="inlineStr"/>
-      <c r="I401" t="inlineStr">
-        <is>
-          <t>5592994937838</t>
-        </is>
+      <c r="I401" t="n">
+        <v>5592994937838</v>
       </c>
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="n">
@@ -20029,10 +20001,8 @@
         </is>
       </c>
       <c r="H402" t="inlineStr"/>
-      <c r="I402" t="inlineStr">
-        <is>
-          <t>559285565437</t>
-        </is>
+      <c r="I402" t="n">
+        <v>559285565437</v>
       </c>
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="n">
@@ -20081,10 +20051,8 @@
         </is>
       </c>
       <c r="H403" t="inlineStr"/>
-      <c r="I403" t="inlineStr">
-        <is>
-          <t>5592986025043</t>
-        </is>
+      <c r="I403" t="n">
+        <v>5592986025043</v>
       </c>
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="n">
@@ -20181,10 +20149,8 @@
         </is>
       </c>
       <c r="H405" t="inlineStr"/>
-      <c r="I405" t="inlineStr">
-        <is>
-          <t>5592992927576</t>
-        </is>
+      <c r="I405" t="n">
+        <v>5592992927576</v>
       </c>
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="n">
@@ -20281,10 +20247,8 @@
         </is>
       </c>
       <c r="H407" t="inlineStr"/>
-      <c r="I407" t="inlineStr">
-        <is>
-          <t>5508001115000</t>
-        </is>
+      <c r="I407" t="n">
+        <v>5508001115000</v>
       </c>
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="n">
@@ -20429,10 +20393,8 @@
         </is>
       </c>
       <c r="H410" t="inlineStr"/>
-      <c r="I410" t="inlineStr">
-        <is>
-          <t>5511912062131</t>
-        </is>
+      <c r="I410" t="n">
+        <v>5511912062131</v>
       </c>
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="n">

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L411"/>
+  <dimension ref="A1:L458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20454,6 +20454,2338 @@
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Médico em Maceió</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>https://dragiovanaliskoski.com.br</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr"/>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="n">
+        <v>82</v>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Área do Médico</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>https://santacasademaceio.com.br</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="n">
+        <v>33</v>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Centro Médico</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>https://maceioshopping.com</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr"/>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>558221261010</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="n">
+        <v>90</v>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Dr. Mauro Barros</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>https://drmaurobarros.com</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>5582993342119</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="n">
+        <v>94</v>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Dentista em Maceió</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>https://www.dentistaemmaceio.com.br</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>5582991193629</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="n">
+        <v>73</v>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Dental Alagoas</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>https://dentalalagoas.com.br</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>5582988469642</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="n">
+        <v>81</v>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Psicólogo online e terapia sem sair de casa</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>https://zenklub.com.br</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="n">
+        <v>81</v>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Gesiane Gomes Pinto</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>https://www.gesianegomespsi.com</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr"/>
+      <c r="I419" t="inlineStr"/>
+      <c r="J419" t="inlineStr"/>
+      <c r="K419" t="n">
+        <v>73</v>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Maira Godoy</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>https://mairagodoy.com.br</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr"/>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>5582993344904</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="n">
+        <v>67</v>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Massoterapeutas em Maceió (AL)</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>https://massoterapeutas.com</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="inlineStr"/>
+      <c r="J421" t="inlineStr"/>
+      <c r="K421" t="n">
+        <v>88</v>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Espaço Terapêutico</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>https://espaco-terapeutico-maceio.ueniweb.com</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr"/>
+      <c r="I422" t="inlineStr"/>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="n">
+        <v>87</v>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Advogado e Escritório de advocacia em Maceió</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>https://ssmadvogados.adv.br</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="n">
+        <v>73</v>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Advogados e Correspondentes Jurídicos em Maceió - AL</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>https://correspondentedinamico.com.br</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="n">
+        <v>33</v>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>https://karpat.adv.br</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr"/>
+      <c r="K425" t="n">
+        <v>64</v>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>João Paulo Farias</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>https://app.diaumtododia.com.br</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="n">
+        <v>33</v>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>O ensino remoto e as aulas de educação física durante a pandemia...</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>https://ojs.brazilianjournals.com.br</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr"/>
+      <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="n">
+        <v>33</v>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Allp Fit Academia Maceió</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>https://localtreino.com</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr"/>
+      <c r="I428" t="inlineStr"/>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="n">
+        <v>56</v>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Maceió - vagas para fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.com.br</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr"/>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="n">
+        <v>22</v>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Psychiatric disorders in chronic hemodialysis patients in a clinic in...</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr"/>
+      <c r="I430" t="inlineStr"/>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="n">
+        <v>47</v>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Reserva vuelos y tiquetes aéreos online</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>https://www.avianca.com</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="n">
+        <v>22</v>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Dentista</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>https://www.salario.com.br</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr"/>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="n">
+        <v>81</v>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Dr. Hamilton Andrade</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>https://drhamiltonandrade.com.br</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr"/>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>5571988918586</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr"/>
+      <c r="K433" t="n">
+        <v>93</v>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Dentista em Salvador</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>https://dentistaemsalvador.com.br</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>5571989211052</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="n">
+        <v>56</v>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Diego Tavares</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>https://diegotavarespsi.com.br</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>5571991551191</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="n">
+        <v>93</v>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>CENTRALPSI - Psicólogos em Salvador</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>https://centralpsi.com</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>5571992240377</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="n">
+        <v>69</v>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Massagem Salvador - BA</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>https://massagemsalvador.com.br</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr"/>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>5571997432001</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="n">
+        <v>87</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Bianca Terapeuta em Salvador</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>https://guiademassagista.com.br</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>5571997432001</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="n">
+        <v>88</v>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Estágio: Educação Física</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>https://www.futuraestagios.com.br</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr"/>
+      <c r="I439" t="inlineStr"/>
+      <c r="J439" t="inlineStr"/>
+      <c r="K439" t="n">
+        <v>78</v>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>4 Beach Gym</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>https://4beachgym.com.br</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr"/>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="n">
+        <v>80</v>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Electric Body Academia XBody</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>https://electricbody.com.br</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>5571999393214</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="n">
+        <v>80</v>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Salvador - BA</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>https://www.brterapeutas.com.br</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr"/>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="n">
+        <v>55</v>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>https://www.espacolarsaude.com.br</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>5571981600087</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr"/>
+      <c r="K443" t="n">
+        <v>73</v>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Neurale</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>https://neurale.com.br</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr"/>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>5571999220525</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="n">
+        <v>80</v>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Conheça espaços que oferecem fisioterapia gratuita em Salvador</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>https://www.correio24horas.com.br</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="n">
+        <v>73</v>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Salvador - BA</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>https://www.valesaude.com.br</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr"/>
+      <c r="I446" t="inlineStr"/>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="n">
+        <v>22</v>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Prontoclínica de Fortaleza</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>https://prontoclinicafortaleza.com.br</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr"/>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>558533059000</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="n">
+        <v>87</v>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Clínica Delfos</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>https://www.delfosclinica.com.br</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>558535357373</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="n">
+        <v>73</v>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Clínica Medicar</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>https://clinicamedicar.com.br</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr"/>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="n">
+        <v>75</v>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Clinica Salud</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>https://clinicasalud.com.br</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>5585981591045</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="n">
+        <v>69</v>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Guia Médico</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>https://www.unimedfortaleza.com.br</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr"/>
+      <c r="I451" t="inlineStr"/>
+      <c r="J451" t="inlineStr"/>
+      <c r="K451" t="n">
+        <v>76</v>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Dentista en Fortaleza</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>https://esp.dentalby.com</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr"/>
+      <c r="I452" t="inlineStr"/>
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="n">
+        <v>60</v>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Vagas de emprego dentista Fortaleza, CE - 94 empregos</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>https://br.jobsora.com</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr"/>
+      <c r="I453" t="inlineStr"/>
+      <c r="J453" t="inlineStr"/>
+      <c r="K453" t="n">
+        <v>89</v>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Os Melhores Advogados de Fortaleza</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>https://advocaciasfortaleza.com</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr"/>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>5585991507373</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="n">
+        <v>55</v>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Advogado em Fortaleza</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>https://www.guiajus.com.br</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr"/>
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="n">
+        <v>73</v>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Escritório de Advocacia em Fortaleza – Ceará</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>https://azedoefranco.adv.br</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr"/>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="n">
+        <v>64</v>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Instituto de Educação Física e Esportes</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>https://iefes.ufc.br</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr"/>
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="n">
+        <v>67</v>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Educação Física em Fortaleza — de R$157/mês</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>https://www.bolsaclick.com.br</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>551153043216</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="n">
+        <v>91</v>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L458"/>
+  <dimension ref="A1:L510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20587,10 +20587,8 @@
         </is>
       </c>
       <c r="H414" t="inlineStr"/>
-      <c r="I414" t="inlineStr">
-        <is>
-          <t>558221261010</t>
-        </is>
+      <c r="I414" t="n">
+        <v>558221261010</v>
       </c>
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="n">
@@ -20639,10 +20637,8 @@
         </is>
       </c>
       <c r="H415" t="inlineStr"/>
-      <c r="I415" t="inlineStr">
-        <is>
-          <t>5582993342119</t>
-        </is>
+      <c r="I415" t="n">
+        <v>5582993342119</v>
       </c>
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="n">
@@ -20691,10 +20687,8 @@
         </is>
       </c>
       <c r="H416" t="inlineStr"/>
-      <c r="I416" t="inlineStr">
-        <is>
-          <t>5582991193629</t>
-        </is>
+      <c r="I416" t="n">
+        <v>5582991193629</v>
       </c>
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="n">
@@ -20743,10 +20737,8 @@
         </is>
       </c>
       <c r="H417" t="inlineStr"/>
-      <c r="I417" t="inlineStr">
-        <is>
-          <t>5582988469642</t>
-        </is>
+      <c r="I417" t="n">
+        <v>5582988469642</v>
       </c>
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="n">
@@ -20891,10 +20883,8 @@
         </is>
       </c>
       <c r="H420" t="inlineStr"/>
-      <c r="I420" t="inlineStr">
-        <is>
-          <t>5582993344904</t>
-        </is>
+      <c r="I420" t="n">
+        <v>5582993344904</v>
       </c>
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="n">
@@ -21519,10 +21509,8 @@
         </is>
       </c>
       <c r="H433" t="inlineStr"/>
-      <c r="I433" t="inlineStr">
-        <is>
-          <t>5571988918586</t>
-        </is>
+      <c r="I433" t="n">
+        <v>5571988918586</v>
       </c>
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="n">
@@ -21571,10 +21559,8 @@
         </is>
       </c>
       <c r="H434" t="inlineStr"/>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>5571989211052</t>
-        </is>
+      <c r="I434" t="n">
+        <v>5571989211052</v>
       </c>
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="n">
@@ -21623,10 +21609,8 @@
         </is>
       </c>
       <c r="H435" t="inlineStr"/>
-      <c r="I435" t="inlineStr">
-        <is>
-          <t>5571991551191</t>
-        </is>
+      <c r="I435" t="n">
+        <v>5571991551191</v>
       </c>
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="n">
@@ -21675,10 +21659,8 @@
         </is>
       </c>
       <c r="H436" t="inlineStr"/>
-      <c r="I436" t="inlineStr">
-        <is>
-          <t>5571992240377</t>
-        </is>
+      <c r="I436" t="n">
+        <v>5571992240377</v>
       </c>
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="n">
@@ -21727,10 +21709,8 @@
         </is>
       </c>
       <c r="H437" t="inlineStr"/>
-      <c r="I437" t="inlineStr">
-        <is>
-          <t>5571997432001</t>
-        </is>
+      <c r="I437" t="n">
+        <v>5571997432001</v>
       </c>
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="n">
@@ -21779,10 +21759,8 @@
         </is>
       </c>
       <c r="H438" t="inlineStr"/>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>5571997432001</t>
-        </is>
+      <c r="I438" t="n">
+        <v>5571997432001</v>
       </c>
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="n">
@@ -21927,10 +21905,8 @@
         </is>
       </c>
       <c r="H441" t="inlineStr"/>
-      <c r="I441" t="inlineStr">
-        <is>
-          <t>5571999393214</t>
-        </is>
+      <c r="I441" t="n">
+        <v>5571999393214</v>
       </c>
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="n">
@@ -22027,10 +22003,8 @@
         </is>
       </c>
       <c r="H443" t="inlineStr"/>
-      <c r="I443" t="inlineStr">
-        <is>
-          <t>5571981600087</t>
-        </is>
+      <c r="I443" t="n">
+        <v>5571981600087</v>
       </c>
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="n">
@@ -22079,10 +22053,8 @@
         </is>
       </c>
       <c r="H444" t="inlineStr"/>
-      <c r="I444" t="inlineStr">
-        <is>
-          <t>5571999220525</t>
-        </is>
+      <c r="I444" t="n">
+        <v>5571999220525</v>
       </c>
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="n">
@@ -22227,10 +22199,8 @@
         </is>
       </c>
       <c r="H447" t="inlineStr"/>
-      <c r="I447" t="inlineStr">
-        <is>
-          <t>558533059000</t>
-        </is>
+      <c r="I447" t="n">
+        <v>558533059000</v>
       </c>
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="n">
@@ -22279,10 +22249,8 @@
         </is>
       </c>
       <c r="H448" t="inlineStr"/>
-      <c r="I448" t="inlineStr">
-        <is>
-          <t>558535357373</t>
-        </is>
+      <c r="I448" t="n">
+        <v>558535357373</v>
       </c>
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="n">
@@ -22379,10 +22347,8 @@
         </is>
       </c>
       <c r="H450" t="inlineStr"/>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>5585981591045</t>
-        </is>
+      <c r="I450" t="n">
+        <v>5585981591045</v>
       </c>
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="n">
@@ -22575,10 +22541,8 @@
         </is>
       </c>
       <c r="H454" t="inlineStr"/>
-      <c r="I454" t="inlineStr">
-        <is>
-          <t>5585991507373</t>
-        </is>
+      <c r="I454" t="n">
+        <v>5585991507373</v>
       </c>
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="n">
@@ -22771,16 +22735,2590 @@
         </is>
       </c>
       <c r="H458" t="inlineStr"/>
-      <c r="I458" t="inlineStr">
-        <is>
-          <t>551153043216</t>
-        </is>
+      <c r="I458" t="n">
+        <v>551153043216</v>
       </c>
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="n">
         <v>91</v>
       </c>
       <c r="L458" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Clínica Brasília</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>https://clinicabrasilia.bsb.br</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>5561982302016</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="n">
+        <v>75</v>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Brasília</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>https://www.hospitalbrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr"/>
+      <c r="I460" t="inlineStr"/>
+      <c r="J460" t="inlineStr"/>
+      <c r="K460" t="n">
+        <v>22</v>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Clínica Médica Brasília DF</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>https://www.neurogama.com.br</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr"/>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="n">
+        <v>75</v>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Clinica Médica</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>https://www.clinicagaleno.com.br</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>5561995876121</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="n">
+        <v>67</v>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>medbrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>https://medbrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>5561992063400</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="n">
+        <v>73</v>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Nutrologia em Brasília (DF) — Agendar consulta</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>https://endoclinicas.org</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="n">
+        <v>62</v>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Cardiologia</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>https://comerciobrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="n">
+        <v>69</v>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Dentista em Brasília DF é na Ianara Pinho Odontologia</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>https://ianarapinho.odo.br</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr"/>
+      <c r="J466" t="inlineStr"/>
+      <c r="K466" t="n">
+        <v>56</v>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Ulisses Odontologia</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>https://clinicaulissesodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr"/>
+      <c r="J467" t="inlineStr"/>
+      <c r="K467" t="n">
+        <v>53</v>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Verifique os Melhores Dentistas em Brasília DF</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>https://brdental.com.br</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr"/>
+      <c r="J468" t="inlineStr"/>
+      <c r="K468" t="n">
+        <v>80</v>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Blanca Odontologia</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>http://www.blancaodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="inlineStr"/>
+      <c r="J469" t="inlineStr"/>
+      <c r="K469" t="n">
+        <v>73</v>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>iOrto</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>https://www.iorto.com.br</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr"/>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>5561982742299</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr"/>
+      <c r="K470" t="n">
+        <v>73</v>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>StudioUno Odontologia</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>https://www.clinicastudiouno.com.br</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr"/>
+      <c r="I471" t="inlineStr"/>
+      <c r="J471" t="inlineStr"/>
+      <c r="K471" t="n">
+        <v>69</v>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica Brasília</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>https://www.harmonizare.com</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr"/>
+      <c r="I472" t="inlineStr"/>
+      <c r="J472" t="inlineStr"/>
+      <c r="K472" t="n">
+        <v>80</v>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Sintonizze Clinica de Psicologia</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>https://www.sintonizepsicologia.com</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr"/>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>5561996511621</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr"/>
+      <c r="K473" t="n">
+        <v>75</v>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Otávio Calile</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>https://www.otaviocalile.com</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr"/>
+      <c r="I474" t="inlineStr"/>
+      <c r="J474" t="inlineStr"/>
+      <c r="K474" t="n">
+        <v>73</v>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Terapia Tântrica Somática em Brasília - DF</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>https://portal.paraisotantra.com.br</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>5511958248871</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr"/>
+      <c r="K475" t="n">
+        <v>62</v>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Jogos da Copa do Mundo Hoje: Horários (Brasília)...</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>https://radiosfutebol.com.br</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr"/>
+      <c r="I476" t="inlineStr"/>
+      <c r="J476" t="inlineStr"/>
+      <c r="K476" t="n">
+        <v>67</v>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Advogado em Brasília - DF</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>http://advogadoinbrasilia.adv.br</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr"/>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>5561984927284</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr"/>
+      <c r="K477" t="n">
+        <v>55</v>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>José Neto Advogados</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>https://josenetoadvogado.com.br</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>5561998868080</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr"/>
+      <c r="K478" t="n">
+        <v>100</v>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>ADVOGADO BRASÍLIA</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>https://advogadobrasiliadf.com.br</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr"/>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>5561992619440</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr"/>
+      <c r="K479" t="n">
+        <v>82</v>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Advogado em Brasília</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>https://app.advogalia.com</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr"/>
+      <c r="I480" t="inlineStr"/>
+      <c r="J480" t="inlineStr"/>
+      <c r="K480" t="n">
+        <v>33</v>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Edmilson Ferreira</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>https://edmilsonferreira.adv.br</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr"/>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>5561994621652</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr"/>
+      <c r="K481" t="n">
+        <v>64</v>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Rodrigues e Teles Advocacia</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>https://rodrigueseteles.adv.br</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr"/>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>5561998768256</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr"/>
+      <c r="K482" t="n">
+        <v>64</v>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Veirano Advogados, Brasília - DF Office, Global</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>https://chambers.com</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr"/>
+      <c r="I483" t="inlineStr"/>
+      <c r="J483" t="inlineStr"/>
+      <c r="K483" t="n">
+        <v>33</v>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Bom Dia DF</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>https://globoplay.globo.com</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr"/>
+      <c r="I484" t="inlineStr"/>
+      <c r="J484" t="inlineStr"/>
+      <c r="K484" t="n">
+        <v>56</v>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Ironberg Águas Claras</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>https://ironbergbrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr"/>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>556136867106</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr"/>
+      <c r="K485" t="n">
+        <v>70</v>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Brasília DF</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>https://forcafisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr"/>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>5561984500078</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr"/>
+      <c r="K486" t="n">
+        <v>69</v>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>QUALIFISIO</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>https://www.qualifisiodf.com.br</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr"/>
+      <c r="I487" t="inlineStr"/>
+      <c r="J487" t="inlineStr"/>
+      <c r="K487" t="n">
+        <v>73</v>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Pró Physis</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>https://prophysis.com.br</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr"/>
+      <c r="I488" t="inlineStr"/>
+      <c r="J488" t="inlineStr"/>
+      <c r="K488" t="n">
+        <v>62</v>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Bem-vindo à Fisiobrasília</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>https://www.fisiobrasilia.com</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr"/>
+      <c r="I489" t="inlineStr"/>
+      <c r="J489" t="inlineStr"/>
+      <c r="K489" t="n">
+        <v>0</v>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>📞 Fisioterapia Brasília</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>https://imovbsb.com</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr"/>
+      <c r="I490" t="inlineStr"/>
+      <c r="J490" t="inlineStr"/>
+      <c r="K490" t="n">
+        <v>60</v>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Fetalcenter Centro Médico Goiânia</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>https://fetalcentercentromedico.com.br</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr"/>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>5562999147414</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr"/>
+      <c r="K491" t="n">
+        <v>81</v>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Qual Melhor Clínica Médica em Goiânia</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>https://radar.med.br</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr"/>
+      <c r="I492" t="inlineStr"/>
+      <c r="J492" t="inlineStr"/>
+      <c r="K492" t="n">
+        <v>71</v>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>FOCCOS</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>https://www.foccoscentromedico.com.br</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr"/>
+      <c r="I493" t="inlineStr"/>
+      <c r="J493" t="inlineStr"/>
+      <c r="K493" t="n">
+        <v>82</v>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>GOIÂNIA</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>https://homedoctor.com.br</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr"/>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>551136152506</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr"/>
+      <c r="K494" t="n">
+        <v>81</v>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Vitae Odontologia - Goiânia</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>https://www.vitaeodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr"/>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>5562993892212</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr"/>
+      <c r="K495" t="n">
+        <v>75</v>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Dentista em Goiânia GO</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>https://leonardobuenoodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr"/>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>5562993142324</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr"/>
+      <c r="K496" t="n">
+        <v>73</v>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>CD3 Odontologia</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>https://cd3odontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr"/>
+      <c r="I497" t="inlineStr"/>
+      <c r="J497" t="inlineStr"/>
+      <c r="K497" t="n">
+        <v>69</v>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Dentista em Goiânia Centro</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>https://odontoclinic.com.br</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr"/>
+      <c r="I498" t="inlineStr"/>
+      <c r="J498" t="inlineStr"/>
+      <c r="K498" t="n">
+        <v>33</v>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Encontre um dentista</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>https://uniodontogoiania.coop.br</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr"/>
+      <c r="I499" t="inlineStr"/>
+      <c r="J499" t="inlineStr"/>
+      <c r="K499" t="n">
+        <v>93</v>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Alessandra Costa</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>https://www.psicologaalessandracosta.com</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr"/>
+      <c r="I500" t="inlineStr"/>
+      <c r="J500" t="inlineStr"/>
+      <c r="K500" t="n">
+        <v>73</v>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Catão Maranhão Filho</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>https://www.psicologocatao.com</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr"/>
+      <c r="I501" t="inlineStr"/>
+      <c r="J501" t="inlineStr"/>
+      <c r="K501" t="n">
+        <v>73</v>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Psicólogo em Goiânia</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>https://www.wspsicologo.com</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="n">
+        <v>81</v>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Sousa &amp; Rizzo Advogados</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>https://sousaerizzoadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>5561999438050</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="n">
+        <v>91</v>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Advogado em Goiânia</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>https://btediniadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr"/>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>5562982624625</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr"/>
+      <c r="K504" t="n">
+        <v>82</v>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Advogado em Goiânia</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>https://fichtadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr"/>
+      <c r="I505" t="inlineStr"/>
+      <c r="J505" t="inlineStr"/>
+      <c r="K505" t="n">
+        <v>91</v>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Os 10 melhores Advogados em Goiânia, Brasil (2026)</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>https://lawzana.com</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr"/>
+      <c r="I506" t="inlineStr"/>
+      <c r="J506" t="inlineStr"/>
+      <c r="K506" t="n">
+        <v>33</v>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Guia dos Melhores Escritórios de Advocacia em Goiânia GO</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>https://comerciogoiania.com.br</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr"/>
+      <c r="I507" t="inlineStr"/>
+      <c r="J507" t="inlineStr"/>
+      <c r="K507" t="n">
+        <v>64</v>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Escobar Advogados</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>https://escobaradvogados.com</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr"/>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>556296713672</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr"/>
+      <c r="K508" t="n">
+        <v>73</v>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>15 melhores academias nos principais setores de Goiânia</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>https://myside.com.br</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr"/>
+      <c r="I509" t="inlineStr"/>
+      <c r="J509" t="inlineStr"/>
+      <c r="K509" t="n">
+        <v>80</v>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>05 academias em Goiânia para você começar seu treino em 2026</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>https://curtamais.com.br</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr"/>
+      <c r="I510" t="inlineStr"/>
+      <c r="J510" t="inlineStr"/>
+      <c r="K510" t="n">
+        <v>33</v>
+      </c>
+      <c r="L510" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L510"/>
+  <dimension ref="A1:L568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22785,10 +22785,8 @@
         </is>
       </c>
       <c r="H459" t="inlineStr"/>
-      <c r="I459" t="inlineStr">
-        <is>
-          <t>5561982302016</t>
-        </is>
+      <c r="I459" t="n">
+        <v>5561982302016</v>
       </c>
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="n">
@@ -22933,10 +22931,8 @@
         </is>
       </c>
       <c r="H462" t="inlineStr"/>
-      <c r="I462" t="inlineStr">
-        <is>
-          <t>5561995876121</t>
-        </is>
+      <c r="I462" t="n">
+        <v>5561995876121</v>
       </c>
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="n">
@@ -22985,10 +22981,8 @@
         </is>
       </c>
       <c r="H463" t="inlineStr"/>
-      <c r="I463" t="inlineStr">
-        <is>
-          <t>5561992063400</t>
-        </is>
+      <c r="I463" t="n">
+        <v>5561992063400</v>
       </c>
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="n">
@@ -23325,10 +23319,8 @@
         </is>
       </c>
       <c r="H470" t="inlineStr"/>
-      <c r="I470" t="inlineStr">
-        <is>
-          <t>5561982742299</t>
-        </is>
+      <c r="I470" t="n">
+        <v>5561982742299</v>
       </c>
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="n">
@@ -23473,10 +23465,8 @@
         </is>
       </c>
       <c r="H473" t="inlineStr"/>
-      <c r="I473" t="inlineStr">
-        <is>
-          <t>5561996511621</t>
-        </is>
+      <c r="I473" t="n">
+        <v>5561996511621</v>
       </c>
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="n">
@@ -23573,10 +23563,8 @@
         </is>
       </c>
       <c r="H475" t="inlineStr"/>
-      <c r="I475" t="inlineStr">
-        <is>
-          <t>5511958248871</t>
-        </is>
+      <c r="I475" t="n">
+        <v>5511958248871</v>
       </c>
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="n">
@@ -23673,10 +23661,8 @@
         </is>
       </c>
       <c r="H477" t="inlineStr"/>
-      <c r="I477" t="inlineStr">
-        <is>
-          <t>5561984927284</t>
-        </is>
+      <c r="I477" t="n">
+        <v>5561984927284</v>
       </c>
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="n">
@@ -23725,10 +23711,8 @@
         </is>
       </c>
       <c r="H478" t="inlineStr"/>
-      <c r="I478" t="inlineStr">
-        <is>
-          <t>5561998868080</t>
-        </is>
+      <c r="I478" t="n">
+        <v>5561998868080</v>
       </c>
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="n">
@@ -23777,10 +23761,8 @@
         </is>
       </c>
       <c r="H479" t="inlineStr"/>
-      <c r="I479" t="inlineStr">
-        <is>
-          <t>5561992619440</t>
-        </is>
+      <c r="I479" t="n">
+        <v>5561992619440</v>
       </c>
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="n">
@@ -23877,10 +23859,8 @@
         </is>
       </c>
       <c r="H481" t="inlineStr"/>
-      <c r="I481" t="inlineStr">
-        <is>
-          <t>5561994621652</t>
-        </is>
+      <c r="I481" t="n">
+        <v>5561994621652</v>
       </c>
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="n">
@@ -23929,10 +23909,8 @@
         </is>
       </c>
       <c r="H482" t="inlineStr"/>
-      <c r="I482" t="inlineStr">
-        <is>
-          <t>5561998768256</t>
-        </is>
+      <c r="I482" t="n">
+        <v>5561998768256</v>
       </c>
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="n">
@@ -24077,10 +24055,8 @@
         </is>
       </c>
       <c r="H485" t="inlineStr"/>
-      <c r="I485" t="inlineStr">
-        <is>
-          <t>556136867106</t>
-        </is>
+      <c r="I485" t="n">
+        <v>556136867106</v>
       </c>
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="n">
@@ -24129,10 +24105,8 @@
         </is>
       </c>
       <c r="H486" t="inlineStr"/>
-      <c r="I486" t="inlineStr">
-        <is>
-          <t>5561984500078</t>
-        </is>
+      <c r="I486" t="n">
+        <v>5561984500078</v>
       </c>
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="n">
@@ -24373,10 +24347,8 @@
         </is>
       </c>
       <c r="H491" t="inlineStr"/>
-      <c r="I491" t="inlineStr">
-        <is>
-          <t>5562999147414</t>
-        </is>
+      <c r="I491" t="n">
+        <v>5562999147414</v>
       </c>
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="n">
@@ -24521,10 +24493,8 @@
         </is>
       </c>
       <c r="H494" t="inlineStr"/>
-      <c r="I494" t="inlineStr">
-        <is>
-          <t>551136152506</t>
-        </is>
+      <c r="I494" t="n">
+        <v>551136152506</v>
       </c>
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="n">
@@ -24573,10 +24543,8 @@
         </is>
       </c>
       <c r="H495" t="inlineStr"/>
-      <c r="I495" t="inlineStr">
-        <is>
-          <t>5562993892212</t>
-        </is>
+      <c r="I495" t="n">
+        <v>5562993892212</v>
       </c>
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="n">
@@ -24625,10 +24593,8 @@
         </is>
       </c>
       <c r="H496" t="inlineStr"/>
-      <c r="I496" t="inlineStr">
-        <is>
-          <t>5562993142324</t>
-        </is>
+      <c r="I496" t="n">
+        <v>5562993142324</v>
       </c>
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="n">
@@ -24965,10 +24931,8 @@
         </is>
       </c>
       <c r="H503" t="inlineStr"/>
-      <c r="I503" t="inlineStr">
-        <is>
-          <t>5561999438050</t>
-        </is>
+      <c r="I503" t="n">
+        <v>5561999438050</v>
       </c>
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="n">
@@ -25017,10 +24981,8 @@
         </is>
       </c>
       <c r="H504" t="inlineStr"/>
-      <c r="I504" t="inlineStr">
-        <is>
-          <t>5562982624625</t>
-        </is>
+      <c r="I504" t="n">
+        <v>5562982624625</v>
       </c>
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="n">
@@ -25213,10 +25175,8 @@
         </is>
       </c>
       <c r="H508" t="inlineStr"/>
-      <c r="I508" t="inlineStr">
-        <is>
-          <t>556296713672</t>
-        </is>
+      <c r="I508" t="n">
+        <v>556296713672</v>
       </c>
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="n">
@@ -25324,6 +25284,2890 @@
         </is>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Clínica Doutor PASA Vitória</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>https://www.saudepasa.com.br</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr"/>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>551140040183</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr"/>
+      <c r="K511" t="n">
+        <v>81</v>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Departamento de Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>https://ccs.ufes.br</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr"/>
+      <c r="I512" t="inlineStr"/>
+      <c r="J512" t="inlineStr"/>
+      <c r="K512" t="n">
+        <v>69</v>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Centro Médico da Praia em Vitória</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>https://centromedicodapraia.com.br</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr"/>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>5527995755810</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr"/>
+      <c r="K513" t="n">
+        <v>71</v>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Consultas e Exames Acessíveis em Vitória e Vila Velha</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>https://clinicastaisabel.com.br</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr"/>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>5527997077827</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr"/>
+      <c r="K514" t="n">
+        <v>67</v>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Especialidades</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>http://santarita.org.br</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr"/>
+      <c r="I515" t="inlineStr"/>
+      <c r="J515" t="inlineStr"/>
+      <c r="K515" t="n">
+        <v>81</v>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>https://bellacia.com.br</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr"/>
+      <c r="I516" t="inlineStr"/>
+      <c r="J516" t="inlineStr"/>
+      <c r="K516" t="n">
+        <v>78</v>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Bolavip</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>https://bolavip.com</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr"/>
+      <c r="I517" t="inlineStr"/>
+      <c r="J517" t="inlineStr"/>
+      <c r="K517" t="n">
+        <v>56</v>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>International Project Strategy in Vitoria, Brazil</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>https://www.slideserve.com</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr"/>
+      <c r="I518" t="inlineStr"/>
+      <c r="J518" t="inlineStr"/>
+      <c r="K518" t="n">
+        <v>33</v>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Tratamento Invisalign</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>https://www.invisalign.com.br</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr"/>
+      <c r="I519" t="inlineStr"/>
+      <c r="J519" t="inlineStr"/>
+      <c r="K519" t="n">
+        <v>75</v>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Psicólogo em Vitória, ES</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>https://psicologolucasprotti.com.br</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr"/>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>5527998645414</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr"/>
+      <c r="K520" t="n">
+        <v>80</v>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Psicólogo em Vitória - ES</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>https://lorenagomes.com.br</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr"/>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>5527998490174</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr"/>
+      <c r="K521" t="n">
+        <v>60</v>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Psicóloga em Vitória</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>https://psicologasarahsayuri.com.br</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr"/>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>5527999744455</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr"/>
+      <c r="K522" t="n">
+        <v>80</v>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Psicólogos em Vitória/ ES</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>https://www.guiavitoria.com.br</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr"/>
+      <c r="I523" t="inlineStr"/>
+      <c r="J523" t="inlineStr"/>
+      <c r="K523" t="n">
+        <v>0</v>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Terapeuta em Vitória Centro</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>https://www.guiavitoriacentro.com.br</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr"/>
+      <c r="I524" t="inlineStr"/>
+      <c r="J524" t="inlineStr"/>
+      <c r="K524" t="n">
+        <v>0</v>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Advogado em Vitória</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>https://mouraadv.com</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr"/>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>5541988444536</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr"/>
+      <c r="K525" t="n">
+        <v>82</v>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Escritório de advocacia em Vitória</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>https://bergi.adv.br</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr"/>
+      <c r="I526" t="inlineStr"/>
+      <c r="J526" t="inlineStr"/>
+      <c r="K526" t="n">
+        <v>64</v>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Educação Física (Bacharelado)</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>https://www.favi.br</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr"/>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>552734211500</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr"/>
+      <c r="K527" t="n">
+        <v>78</v>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Graduação em Educação Física Bacharelado</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>https://unisales.br</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr"/>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>5527981234566</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr"/>
+      <c r="K528" t="n">
+        <v>56</v>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Academia Razões do Corpo</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>https://www.razoesdocorpo.com</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr"/>
+      <c r="I529" t="inlineStr"/>
+      <c r="J529" t="inlineStr"/>
+      <c r="K529" t="n">
+        <v>75</v>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Academias em Vitória</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>https://vitoria.net.br</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr"/>
+      <c r="I530" t="inlineStr"/>
+      <c r="J530" t="inlineStr"/>
+      <c r="K530" t="n">
+        <v>82</v>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Saúde Esporte Club</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>https://academiasaudeesporte.com.br</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr"/>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>5527988446953</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr"/>
+      <c r="K531" t="n">
+        <v>70</v>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Vitória</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>https://www.anaflaviafisioterapeuta.com.br</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr"/>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>5527997580620</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr"/>
+      <c r="K532" t="n">
+        <v>80</v>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta em Vitória/ES: Danilo Leite</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>https://www.daniloleitefisio.com.br</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr"/>
+      <c r="J533" t="inlineStr"/>
+      <c r="K533" t="n">
+        <v>73</v>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Clínica BHMed</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>https://www.clinicabhmed.com.br</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr"/>
+      <c r="I534" t="inlineStr"/>
+      <c r="J534" t="inlineStr"/>
+      <c r="K534" t="n">
+        <v>73</v>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Clínica do Bem</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>https://clinicadobem.com.br</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr"/>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>5531998696988</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr"/>
+      <c r="K535" t="n">
+        <v>75</v>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Centro Médico: Belo Horizonte - Barreiro</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>https://www.clinicadacidade.com.br</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr"/>
+      <c r="I536" t="inlineStr"/>
+      <c r="J536" t="inlineStr"/>
+      <c r="K536" t="n">
+        <v>50</v>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Hospital Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>https://hospitalbelohorizonte.com.br</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr"/>
+      <c r="I537" t="inlineStr"/>
+      <c r="J537" t="inlineStr"/>
+      <c r="K537" t="n">
+        <v>33</v>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Clinica Castelo – Clinica Médica</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>https://clinicacastelo.med.br</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr"/>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>5531999529288</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr"/>
+      <c r="K538" t="n">
+        <v>67</v>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Mercado de trabalho médico em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>https://educacaomedica.afya.com.br</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr"/>
+      <c r="I539" t="inlineStr"/>
+      <c r="J539" t="inlineStr"/>
+      <c r="K539" t="n">
+        <v>65</v>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Medical Examination</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>https://br.usembassy.gov</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr"/>
+      <c r="I540" t="inlineStr"/>
+      <c r="J540" t="inlineStr"/>
+      <c r="K540" t="n">
+        <v>78</v>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Médicos do Mundo</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>https://medicosdomundo.org.br</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr"/>
+      <c r="I541" t="inlineStr"/>
+      <c r="J541" t="inlineStr"/>
+      <c r="K541" t="n">
+        <v>0</v>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Médico Sem Fila</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>https://medicosemfila.com.br</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr"/>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>553132728200</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr"/>
+      <c r="K542" t="n">
+        <v>76</v>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>GuiaMedico</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>https://app.unimedbh.com.br</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr"/>
+      <c r="I543" t="inlineStr"/>
+      <c r="J543" t="inlineStr"/>
+      <c r="K543" t="n">
+        <v>33</v>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Grupo Odontológico Mangabeiras</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>https://www.gom.com.br</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr"/>
+      <c r="I544" t="inlineStr"/>
+      <c r="J544" t="inlineStr"/>
+      <c r="K544" t="n">
+        <v>0</v>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Dentista 24 horas em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>https://dentista24horas.net.br</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr"/>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>5531997367514</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr"/>
+      <c r="K545" t="n">
+        <v>73</v>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica BH</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>https://clinicaodontologicabh.com</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr"/>
+      <c r="I546" t="inlineStr"/>
+      <c r="J546" t="inlineStr"/>
+      <c r="K546" t="n">
+        <v>69</v>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica Bias Fortes: Dentista 24 Horas</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>https://biasfortes.com.br</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr"/>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>5531994170017</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr"/>
+      <c r="K547" t="n">
+        <v>80</v>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Dentista</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>https://www.nucleodosorrisobh.com.br</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr"/>
+      <c r="I548" t="inlineStr"/>
+      <c r="J548" t="inlineStr"/>
+      <c r="K548" t="n">
+        <v>69</v>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica Santé</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>https://clinicaodontologicasante.com.br</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr"/>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>5531984886689</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr"/>
+      <c r="K549" t="n">
+        <v>81</v>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>https://horizonteodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr"/>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>5511982487984</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr"/>
+      <c r="K550" t="n">
+        <v>73</v>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>20 psicólogos em Belo Horizonte prontos para te atender</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>https://mindee.com.br</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr"/>
+      <c r="I551" t="inlineStr"/>
+      <c r="J551" t="inlineStr"/>
+      <c r="K551" t="n">
+        <v>87</v>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Psicólogo Caio Herscovici Martines</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>https://caiomartines.com</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr"/>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>5516991171894</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr"/>
+      <c r="K552" t="n">
+        <v>73</v>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Psicólogos em Belo Horizonte — Sessões a R$50</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>https://www.psinote.com.br</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr"/>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>5512981029155</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr"/>
+      <c r="K553" t="n">
+        <v>73</v>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Frederico Ragi Curi</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>https://psicuri.com.br</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr"/>
+      <c r="I554" t="inlineStr"/>
+      <c r="J554" t="inlineStr"/>
+      <c r="K554" t="n">
+        <v>69</v>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>TIP Clínica — Método ADI/TIP® em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>https://tipclinica.com.br</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr"/>
+      <c r="I555" t="inlineStr"/>
+      <c r="J555" t="inlineStr"/>
+      <c r="K555" t="n">
+        <v>60</v>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Terapia Online</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>https://psicologiabelohorizonte.com</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr"/>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>5531996800103</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr"/>
+      <c r="K556" t="n">
+        <v>50</v>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Chirley Sato</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>https://basileia.com.br</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr"/>
+      <c r="I557" t="inlineStr"/>
+      <c r="J557" t="inlineStr"/>
+      <c r="K557" t="n">
+        <v>87</v>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Maria Paula Moreira Silva Psicologia Clínica</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>https://www.mariapaulapsi.com</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr"/>
+      <c r="I558" t="inlineStr"/>
+      <c r="J558" t="inlineStr"/>
+      <c r="K558" t="n">
+        <v>80</v>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Advocacia Especializada em BH</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>https://consultoriojuridico.com.br</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr"/>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>5531997022211</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr"/>
+      <c r="K559" t="n">
+        <v>73</v>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>ALEX SANTANA E FERNANDA ROCHA SOCIEDADE DE ADVOGADOS</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>https://www.asaf.adv.br</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr"/>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>5531981102455</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr"/>
+      <c r="K560" t="n">
+        <v>73</v>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Advogados em Belo Horizonte (MG)</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>https://almeidamelo.adv.br</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr"/>
+      <c r="I561" t="inlineStr"/>
+      <c r="J561" t="inlineStr"/>
+      <c r="K561" t="n">
+        <v>73</v>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>https://www.uemg.br</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr"/>
+      <c r="I562" t="inlineStr"/>
+      <c r="J562" t="inlineStr"/>
+      <c r="K562" t="n">
+        <v>22</v>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Academias em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>https://belohorizonte.net.br</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr"/>
+      <c r="I563" t="inlineStr"/>
+      <c r="J563" t="inlineStr"/>
+      <c r="K563" t="n">
+        <v>82</v>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Primeira academia sete estrelas do Brasil será inaugurada em BH</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>https://diariodocomercio.com.br</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr"/>
+      <c r="I564" t="inlineStr"/>
+      <c r="J564" t="inlineStr"/>
+      <c r="K564" t="n">
+        <v>71</v>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Descubra as melhores Clínicas de Fisioterapia em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>https://br.physiofinder.net</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr"/>
+      <c r="I565" t="inlineStr"/>
+      <c r="J565" t="inlineStr"/>
+      <c r="K565" t="n">
+        <v>94</v>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta em Belo Horizonte - MG</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>https://classibh.com.br</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr"/>
+      <c r="I566" t="inlineStr"/>
+      <c r="J566" t="inlineStr"/>
+      <c r="K566" t="n">
+        <v>82</v>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Clínica Cor</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>https://clinicamedicacor.com.br</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr"/>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>5521967870756</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr"/>
+      <c r="K567" t="n">
+        <v>56</v>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>US⋅RIO Medicina e Diagnóstico: Exames de Imagem Duque de ...</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>http://usrio.com.br</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr"/>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>5521951011412</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr"/>
+      <c r="K568" t="n">
+        <v>53</v>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L568"/>
+  <dimension ref="A1:L619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25321,10 +25321,8 @@
         </is>
       </c>
       <c r="H511" t="inlineStr"/>
-      <c r="I511" t="inlineStr">
-        <is>
-          <t>551140040183</t>
-        </is>
+      <c r="I511" t="n">
+        <v>551140040183</v>
       </c>
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="n">
@@ -25421,10 +25419,8 @@
         </is>
       </c>
       <c r="H513" t="inlineStr"/>
-      <c r="I513" t="inlineStr">
-        <is>
-          <t>5527995755810</t>
-        </is>
+      <c r="I513" t="n">
+        <v>5527995755810</v>
       </c>
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="n">
@@ -25473,10 +25469,8 @@
         </is>
       </c>
       <c r="H514" t="inlineStr"/>
-      <c r="I514" t="inlineStr">
-        <is>
-          <t>5527997077827</t>
-        </is>
+      <c r="I514" t="n">
+        <v>5527997077827</v>
       </c>
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="n">
@@ -25765,10 +25759,8 @@
         </is>
       </c>
       <c r="H520" t="inlineStr"/>
-      <c r="I520" t="inlineStr">
-        <is>
-          <t>5527998645414</t>
-        </is>
+      <c r="I520" t="n">
+        <v>5527998645414</v>
       </c>
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="n">
@@ -25817,10 +25809,8 @@
         </is>
       </c>
       <c r="H521" t="inlineStr"/>
-      <c r="I521" t="inlineStr">
-        <is>
-          <t>5527998490174</t>
-        </is>
+      <c r="I521" t="n">
+        <v>5527998490174</v>
       </c>
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="n">
@@ -25869,10 +25859,8 @@
         </is>
       </c>
       <c r="H522" t="inlineStr"/>
-      <c r="I522" t="inlineStr">
-        <is>
-          <t>5527999744455</t>
-        </is>
+      <c r="I522" t="n">
+        <v>5527999744455</v>
       </c>
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="n">
@@ -26017,10 +26005,8 @@
         </is>
       </c>
       <c r="H525" t="inlineStr"/>
-      <c r="I525" t="inlineStr">
-        <is>
-          <t>5541988444536</t>
-        </is>
+      <c r="I525" t="n">
+        <v>5541988444536</v>
       </c>
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="n">
@@ -26117,10 +26103,8 @@
         </is>
       </c>
       <c r="H527" t="inlineStr"/>
-      <c r="I527" t="inlineStr">
-        <is>
-          <t>552734211500</t>
-        </is>
+      <c r="I527" t="n">
+        <v>552734211500</v>
       </c>
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="n">
@@ -26169,10 +26153,8 @@
         </is>
       </c>
       <c r="H528" t="inlineStr"/>
-      <c r="I528" t="inlineStr">
-        <is>
-          <t>5527981234566</t>
-        </is>
+      <c r="I528" t="n">
+        <v>5527981234566</v>
       </c>
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="n">
@@ -26317,10 +26299,8 @@
         </is>
       </c>
       <c r="H531" t="inlineStr"/>
-      <c r="I531" t="inlineStr">
-        <is>
-          <t>5527988446953</t>
-        </is>
+      <c r="I531" t="n">
+        <v>5527988446953</v>
       </c>
       <c r="J531" t="inlineStr"/>
       <c r="K531" t="n">
@@ -26369,10 +26349,8 @@
         </is>
       </c>
       <c r="H532" t="inlineStr"/>
-      <c r="I532" t="inlineStr">
-        <is>
-          <t>5527997580620</t>
-        </is>
+      <c r="I532" t="n">
+        <v>5527997580620</v>
       </c>
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="n">
@@ -26517,10 +26495,8 @@
         </is>
       </c>
       <c r="H535" t="inlineStr"/>
-      <c r="I535" t="inlineStr">
-        <is>
-          <t>5531998696988</t>
-        </is>
+      <c r="I535" t="n">
+        <v>5531998696988</v>
       </c>
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="n">
@@ -26665,10 +26641,8 @@
         </is>
       </c>
       <c r="H538" t="inlineStr"/>
-      <c r="I538" t="inlineStr">
-        <is>
-          <t>5531999529288</t>
-        </is>
+      <c r="I538" t="n">
+        <v>5531999529288</v>
       </c>
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="n">
@@ -26861,10 +26835,8 @@
         </is>
       </c>
       <c r="H542" t="inlineStr"/>
-      <c r="I542" t="inlineStr">
-        <is>
-          <t>553132728200</t>
-        </is>
+      <c r="I542" t="n">
+        <v>553132728200</v>
       </c>
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="n">
@@ -27009,10 +26981,8 @@
         </is>
       </c>
       <c r="H545" t="inlineStr"/>
-      <c r="I545" t="inlineStr">
-        <is>
-          <t>5531997367514</t>
-        </is>
+      <c r="I545" t="n">
+        <v>5531997367514</v>
       </c>
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="n">
@@ -27109,10 +27079,8 @@
         </is>
       </c>
       <c r="H547" t="inlineStr"/>
-      <c r="I547" t="inlineStr">
-        <is>
-          <t>5531994170017</t>
-        </is>
+      <c r="I547" t="n">
+        <v>5531994170017</v>
       </c>
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="n">
@@ -27209,10 +27177,8 @@
         </is>
       </c>
       <c r="H549" t="inlineStr"/>
-      <c r="I549" t="inlineStr">
-        <is>
-          <t>5531984886689</t>
-        </is>
+      <c r="I549" t="n">
+        <v>5531984886689</v>
       </c>
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="n">
@@ -27261,10 +27227,8 @@
         </is>
       </c>
       <c r="H550" t="inlineStr"/>
-      <c r="I550" t="inlineStr">
-        <is>
-          <t>5511982487984</t>
-        </is>
+      <c r="I550" t="n">
+        <v>5511982487984</v>
       </c>
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="n">
@@ -27361,10 +27325,8 @@
         </is>
       </c>
       <c r="H552" t="inlineStr"/>
-      <c r="I552" t="inlineStr">
-        <is>
-          <t>5516991171894</t>
-        </is>
+      <c r="I552" t="n">
+        <v>5516991171894</v>
       </c>
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="n">
@@ -27413,10 +27375,8 @@
         </is>
       </c>
       <c r="H553" t="inlineStr"/>
-      <c r="I553" t="inlineStr">
-        <is>
-          <t>5512981029155</t>
-        </is>
+      <c r="I553" t="n">
+        <v>5512981029155</v>
       </c>
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="n">
@@ -27561,10 +27521,8 @@
         </is>
       </c>
       <c r="H556" t="inlineStr"/>
-      <c r="I556" t="inlineStr">
-        <is>
-          <t>5531996800103</t>
-        </is>
+      <c r="I556" t="n">
+        <v>5531996800103</v>
       </c>
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="n">
@@ -27709,10 +27667,8 @@
         </is>
       </c>
       <c r="H559" t="inlineStr"/>
-      <c r="I559" t="inlineStr">
-        <is>
-          <t>5531997022211</t>
-        </is>
+      <c r="I559" t="n">
+        <v>5531997022211</v>
       </c>
       <c r="J559" t="inlineStr"/>
       <c r="K559" t="n">
@@ -27761,10 +27717,8 @@
         </is>
       </c>
       <c r="H560" t="inlineStr"/>
-      <c r="I560" t="inlineStr">
-        <is>
-          <t>5531981102455</t>
-        </is>
+      <c r="I560" t="n">
+        <v>5531981102455</v>
       </c>
       <c r="J560" t="inlineStr"/>
       <c r="K560" t="n">
@@ -28101,10 +28055,8 @@
         </is>
       </c>
       <c r="H567" t="inlineStr"/>
-      <c r="I567" t="inlineStr">
-        <is>
-          <t>5521967870756</t>
-        </is>
+      <c r="I567" t="n">
+        <v>5521967870756</v>
       </c>
       <c r="J567" t="inlineStr"/>
       <c r="K567" t="n">
@@ -28153,10 +28105,8 @@
         </is>
       </c>
       <c r="H568" t="inlineStr"/>
-      <c r="I568" t="inlineStr">
-        <is>
-          <t>5521951011412</t>
-        </is>
+      <c r="I568" t="n">
+        <v>5521951011412</v>
       </c>
       <c r="J568" t="inlineStr"/>
       <c r="K568" t="n">
@@ -28165,6 +28115,2550 @@
       <c r="L568" t="inlineStr">
         <is>
           <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Nova Salutare</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>https://novasalutare.com.br</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr"/>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>5541988939315</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr"/>
+      <c r="K569" t="n">
+        <v>69</v>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Clínica Médica São Bento</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>https://clinicamedicasaobento.com.br</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr"/>
+      <c r="I570" t="inlineStr"/>
+      <c r="J570" t="inlineStr"/>
+      <c r="K570" t="n">
+        <v>0</v>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Equilíbrio Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>https://clinicadoequilibrio.com.br</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr"/>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>554130397359</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr"/>
+      <c r="K571" t="n">
+        <v>65</v>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>IdealPrev - Clínica Médica em Curitiba</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>https://clinicaidealprev.com.br</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr"/>
+      <c r="I572" t="inlineStr"/>
+      <c r="J572" t="inlineStr"/>
+      <c r="K572" t="n">
+        <v>56</v>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Curitiba PR (2026)</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>https://guiaemcuritiba.com.br</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr"/>
+      <c r="I573" t="inlineStr"/>
+      <c r="J573" t="inlineStr"/>
+      <c r="K573" t="n">
+        <v>91</v>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Equipe Saúde</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>https://equipesaude.com.br</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr"/>
+      <c r="I574" t="inlineStr"/>
+      <c r="J574" t="inlineStr"/>
+      <c r="K574" t="n">
+        <v>64</v>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Médicos e Clínicas em Curitiba</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>https://www.encontracuritiba.com.br</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr"/>
+      <c r="I575" t="inlineStr"/>
+      <c r="J575" t="inlineStr"/>
+      <c r="K575" t="n">
+        <v>55</v>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Marcar consulta em Curitiba</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>https://www.tuasaude.com</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr"/>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>5521967717442</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr"/>
+      <c r="K576" t="n">
+        <v>82</v>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Atendimento à domicílio em Curitiba PR</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>https://lareodontocuritiba.com.br</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr"/>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>5541998045311</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr"/>
+      <c r="K577" t="n">
+        <v>93</v>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Cury Clínica Odontológica</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>https://ortodontiacuritiba.com.br</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr"/>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>5541985147134</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr"/>
+      <c r="K578" t="n">
+        <v>87</v>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Dentistas em Curitiba</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>https://www.anaarantesodonto.com.br</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr"/>
+      <c r="I579" t="inlineStr"/>
+      <c r="J579" t="inlineStr"/>
+      <c r="K579" t="n">
+        <v>80</v>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Dentistas em Curitiba</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>https://dentprime.com.br</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr"/>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>5541987950029</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr"/>
+      <c r="K580" t="n">
+        <v>73</v>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Dentista Curitiba</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>https://www.odontologiacuritiba.com.br</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr"/>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>5511952137463</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr"/>
+      <c r="K581" t="n">
+        <v>67</v>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Dentistas em Curitiba</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>https://www.dentistas.net.br</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr"/>
+      <c r="I582" t="inlineStr"/>
+      <c r="J582" t="inlineStr"/>
+      <c r="K582" t="n">
+        <v>88</v>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Dentista Curitiba</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>https://dentalestheticcenter.com.br</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr"/>
+      <c r="I583" t="inlineStr"/>
+      <c r="J583" t="inlineStr"/>
+      <c r="K583" t="n">
+        <v>81</v>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Psicólogos em Curitiba (PR)</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>https://nossospsicologos.com.br</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr"/>
+      <c r="I584" t="inlineStr"/>
+      <c r="J584" t="inlineStr"/>
+      <c r="K584" t="n">
+        <v>60</v>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Psicólogos em Curitiba, PR</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>https://vittude.com</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr"/>
+      <c r="I585" t="inlineStr"/>
+      <c r="J585" t="inlineStr"/>
+      <c r="K585" t="n">
+        <v>0</v>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Os 10 melhores Psicólogos em Curitiba</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>https://curitiba.infoisinfo-br.com</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr"/>
+      <c r="I586" t="inlineStr"/>
+      <c r="J586" t="inlineStr"/>
+      <c r="K586" t="n">
+        <v>73</v>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Em busca de um psicólogo em Curitiba? Consulte os convênios aceitos</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>https://psicologo.curitiba.br</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr"/>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>5541992704363</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr"/>
+      <c r="K587" t="n">
+        <v>67</v>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Psicoterapia</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>https://psicologiacuritibapr.com.br</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr"/>
+      <c r="I588" t="inlineStr"/>
+      <c r="J588" t="inlineStr"/>
+      <c r="K588" t="n">
+        <v>80</v>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Tarcísio Lemos Advocacia</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>https://www.tarcisiolemos.com</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr"/>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>5541988472631</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr"/>
+      <c r="K589" t="n">
+        <v>82</v>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Evandro Galindo – Advogado Criminal e Cível</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>https://evandrogalindo.adv.br</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr"/>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>5541998064520</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr"/>
+      <c r="K590" t="n">
+        <v>73</v>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Advocacia</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>https://www.brasiljunioradv.com.br</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr"/>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>5541920010559</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr"/>
+      <c r="K591" t="n">
+        <v>73</v>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Willian Nunes Advogados</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>https://wnadvogados.adv.br</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr"/>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>5541999691929</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr"/>
+      <c r="K592" t="n">
+        <v>82</v>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Centro de Educação Física e Desportos</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>https://ced.ufpr.br</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr"/>
+      <c r="I593" t="inlineStr"/>
+      <c r="J593" t="inlineStr"/>
+      <c r="K593" t="n">
+        <v>67</v>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Aulas de educação física em Curitiba - 26 profes - SuperprofFaculdade de Educação Física em Curitiba - PR</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>https://www.superprof.com.br</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr"/>
+      <c r="I594" t="inlineStr"/>
+      <c r="J594" t="inlineStr"/>
+      <c r="K594" t="n">
+        <v>22</v>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Academia Hype Curitiba</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>https://www.academiahype.com.br</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr"/>
+      <c r="I595" t="inlineStr"/>
+      <c r="J595" t="inlineStr"/>
+      <c r="K595" t="n">
+        <v>70</v>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Escola de Natação e Academia</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>https://www.webberacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr"/>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>5541992637053</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr"/>
+      <c r="K596" t="n">
+        <v>70</v>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Academia Corpus</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>https://academiacorpus.com.br</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr"/>
+      <c r="I597" t="inlineStr"/>
+      <c r="J597" t="inlineStr"/>
+      <c r="K597" t="n">
+        <v>50</v>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Academia em Curitiba</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>https://academiaolimpica.esp.br</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr"/>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>554197840457</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr"/>
+      <c r="K598" t="n">
+        <v>70</v>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Top 10 melhores academias e centros de fitness na Curitiba de 2026</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>https://curitibainsider.com</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr"/>
+      <c r="I599" t="inlineStr"/>
+      <c r="J599" t="inlineStr"/>
+      <c r="K599" t="n">
+        <v>55</v>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Academia America</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>https://academiaamerica.com.br</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr"/>
+      <c r="I600" t="inlineStr"/>
+      <c r="J600" t="inlineStr"/>
+      <c r="K600" t="n">
+        <v>70</v>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Academias em Curitiba</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>https://www.diariocidade.com</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr"/>
+      <c r="I601" t="inlineStr"/>
+      <c r="J601" t="inlineStr"/>
+      <c r="K601" t="n">
+        <v>56</v>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Clínica de Fisioterapia Câmara Vicelli</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>https://www.camaravicelli.com.br</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr"/>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>5541992828181</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr"/>
+      <c r="K602" t="n">
+        <v>67</v>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Move - Fisioterapia em Curitiba</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>https://movefisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr"/>
+      <c r="I603" t="inlineStr"/>
+      <c r="J603" t="inlineStr"/>
+      <c r="K603" t="n">
+        <v>80</v>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Dr. Fábio Rezende</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>https://www.fabiorezendefisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr"/>
+      <c r="I604" t="inlineStr"/>
+      <c r="J604" t="inlineStr"/>
+      <c r="K604" t="n">
+        <v>67</v>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Clínica Cefit</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>https://www.cefitfisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr"/>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>554199940799</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr"/>
+      <c r="K605" t="n">
+        <v>73</v>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>4D Clinic</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>https://4dclinic.com.br</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr"/>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>5551996973318</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr"/>
+      <c r="K606" t="n">
+        <v>75</v>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>https://guiaportoalegrers.com.br</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr"/>
+      <c r="I607" t="inlineStr"/>
+      <c r="J607" t="inlineStr"/>
+      <c r="K607" t="n">
+        <v>91</v>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Doca Clínica</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>https://docaclinica.com.br</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr"/>
+      <c r="I608" t="inlineStr"/>
+      <c r="J608" t="inlineStr"/>
+      <c r="K608" t="n">
+        <v>69</v>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Sabre Odonto</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>https://www.portoalegre.sabreodonto.com.br</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr"/>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>5551991937322</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr"/>
+      <c r="K609" t="n">
+        <v>73</v>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Clínica KOK</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>https://clinicakok.com.br</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr"/>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>5551997609007</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr"/>
+      <c r="K610" t="n">
+        <v>94</v>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Psicólogos em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>https://centralpsicologia.com.br</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr"/>
+      <c r="I611" t="inlineStr"/>
+      <c r="J611" t="inlineStr"/>
+      <c r="K611" t="n">
+        <v>73</v>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Psicólogo em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>https://rafaelboucinha.com.br</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr"/>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>5551997926063</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr"/>
+      <c r="K612" t="n">
+        <v>80</v>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Psicólogo em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>https://pluralitapsicologia.com.br</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr"/>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>555132092000</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr"/>
+      <c r="K613" t="n">
+        <v>73</v>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Os Melhores Advogados de Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>https://advocaciasportoalegre.com</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr"/>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>5551999893500</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr"/>
+      <c r="K614" t="n">
+        <v>55</v>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Barbieri Advogados: Home</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>https://barbieriadvogados.com</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr"/>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>555132240169</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr"/>
+      <c r="K615" t="n">
+        <v>82</v>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Advogados Associados em Porto Alegre, RS</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>https://www.sangiogoadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr"/>
+      <c r="I616" t="inlineStr"/>
+      <c r="J616" t="inlineStr"/>
+      <c r="K616" t="n">
+        <v>73</v>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Bernardi &amp; Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>https://bernardi.adv.br</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr"/>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>5551991892837</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr"/>
+      <c r="K617" t="n">
+        <v>91</v>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Faculdade de Educação Física em Porto Alegre / RS</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>https://www.nacionaleducacao.com.br</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr"/>
+      <c r="I618" t="inlineStr"/>
+      <c r="J618" t="inlineStr"/>
+      <c r="K618" t="n">
+        <v>56</v>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Academia Perfect</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>https://academiaperfect.com.br</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr"/>
+      <c r="I619" t="inlineStr"/>
+      <c r="J619" t="inlineStr"/>
+      <c r="K619" t="n">
+        <v>60</v>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>Médio</t>
         </is>
       </c>
     </row>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L619"/>
+  <dimension ref="A1:L651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28155,10 +28155,8 @@
         </is>
       </c>
       <c r="H569" t="inlineStr"/>
-      <c r="I569" t="inlineStr">
-        <is>
-          <t>5541988939315</t>
-        </is>
+      <c r="I569" t="n">
+        <v>5541988939315</v>
       </c>
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="n">
@@ -28255,10 +28253,8 @@
         </is>
       </c>
       <c r="H571" t="inlineStr"/>
-      <c r="I571" t="inlineStr">
-        <is>
-          <t>554130397359</t>
-        </is>
+      <c r="I571" t="n">
+        <v>554130397359</v>
       </c>
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="n">
@@ -28499,10 +28495,8 @@
         </is>
       </c>
       <c r="H576" t="inlineStr"/>
-      <c r="I576" t="inlineStr">
-        <is>
-          <t>5521967717442</t>
-        </is>
+      <c r="I576" t="n">
+        <v>5521967717442</v>
       </c>
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="n">
@@ -28551,10 +28545,8 @@
         </is>
       </c>
       <c r="H577" t="inlineStr"/>
-      <c r="I577" t="inlineStr">
-        <is>
-          <t>5541998045311</t>
-        </is>
+      <c r="I577" t="n">
+        <v>5541998045311</v>
       </c>
       <c r="J577" t="inlineStr"/>
       <c r="K577" t="n">
@@ -28603,10 +28595,8 @@
         </is>
       </c>
       <c r="H578" t="inlineStr"/>
-      <c r="I578" t="inlineStr">
-        <is>
-          <t>5541985147134</t>
-        </is>
+      <c r="I578" t="n">
+        <v>5541985147134</v>
       </c>
       <c r="J578" t="inlineStr"/>
       <c r="K578" t="n">
@@ -28703,10 +28693,8 @@
         </is>
       </c>
       <c r="H580" t="inlineStr"/>
-      <c r="I580" t="inlineStr">
-        <is>
-          <t>5541987950029</t>
-        </is>
+      <c r="I580" t="n">
+        <v>5541987950029</v>
       </c>
       <c r="J580" t="inlineStr"/>
       <c r="K580" t="n">
@@ -28755,10 +28743,8 @@
         </is>
       </c>
       <c r="H581" t="inlineStr"/>
-      <c r="I581" t="inlineStr">
-        <is>
-          <t>5511952137463</t>
-        </is>
+      <c r="I581" t="n">
+        <v>5511952137463</v>
       </c>
       <c r="J581" t="inlineStr"/>
       <c r="K581" t="n">
@@ -29047,10 +29033,8 @@
         </is>
       </c>
       <c r="H587" t="inlineStr"/>
-      <c r="I587" t="inlineStr">
-        <is>
-          <t>5541992704363</t>
-        </is>
+      <c r="I587" t="n">
+        <v>5541992704363</v>
       </c>
       <c r="J587" t="inlineStr"/>
       <c r="K587" t="n">
@@ -29147,10 +29131,8 @@
         </is>
       </c>
       <c r="H589" t="inlineStr"/>
-      <c r="I589" t="inlineStr">
-        <is>
-          <t>5541988472631</t>
-        </is>
+      <c r="I589" t="n">
+        <v>5541988472631</v>
       </c>
       <c r="J589" t="inlineStr"/>
       <c r="K589" t="n">
@@ -29199,10 +29181,8 @@
         </is>
       </c>
       <c r="H590" t="inlineStr"/>
-      <c r="I590" t="inlineStr">
-        <is>
-          <t>5541998064520</t>
-        </is>
+      <c r="I590" t="n">
+        <v>5541998064520</v>
       </c>
       <c r="J590" t="inlineStr"/>
       <c r="K590" t="n">
@@ -29251,10 +29231,8 @@
         </is>
       </c>
       <c r="H591" t="inlineStr"/>
-      <c r="I591" t="inlineStr">
-        <is>
-          <t>5541920010559</t>
-        </is>
+      <c r="I591" t="n">
+        <v>5541920010559</v>
       </c>
       <c r="J591" t="inlineStr"/>
       <c r="K591" t="n">
@@ -29303,10 +29281,8 @@
         </is>
       </c>
       <c r="H592" t="inlineStr"/>
-      <c r="I592" t="inlineStr">
-        <is>
-          <t>5541999691929</t>
-        </is>
+      <c r="I592" t="n">
+        <v>5541999691929</v>
       </c>
       <c r="J592" t="inlineStr"/>
       <c r="K592" t="n">
@@ -29499,10 +29475,8 @@
         </is>
       </c>
       <c r="H596" t="inlineStr"/>
-      <c r="I596" t="inlineStr">
-        <is>
-          <t>5541992637053</t>
-        </is>
+      <c r="I596" t="n">
+        <v>5541992637053</v>
       </c>
       <c r="J596" t="inlineStr"/>
       <c r="K596" t="n">
@@ -29599,10 +29573,8 @@
         </is>
       </c>
       <c r="H598" t="inlineStr"/>
-      <c r="I598" t="inlineStr">
-        <is>
-          <t>554197840457</t>
-        </is>
+      <c r="I598" t="n">
+        <v>554197840457</v>
       </c>
       <c r="J598" t="inlineStr"/>
       <c r="K598" t="n">
@@ -29795,10 +29767,8 @@
         </is>
       </c>
       <c r="H602" t="inlineStr"/>
-      <c r="I602" t="inlineStr">
-        <is>
-          <t>5541992828181</t>
-        </is>
+      <c r="I602" t="n">
+        <v>5541992828181</v>
       </c>
       <c r="J602" t="inlineStr"/>
       <c r="K602" t="n">
@@ -29943,10 +29913,8 @@
         </is>
       </c>
       <c r="H605" t="inlineStr"/>
-      <c r="I605" t="inlineStr">
-        <is>
-          <t>554199940799</t>
-        </is>
+      <c r="I605" t="n">
+        <v>554199940799</v>
       </c>
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="n">
@@ -29995,10 +29963,8 @@
         </is>
       </c>
       <c r="H606" t="inlineStr"/>
-      <c r="I606" t="inlineStr">
-        <is>
-          <t>5551996973318</t>
-        </is>
+      <c r="I606" t="n">
+        <v>5551996973318</v>
       </c>
       <c r="J606" t="inlineStr"/>
       <c r="K606" t="n">
@@ -30143,10 +30109,8 @@
         </is>
       </c>
       <c r="H609" t="inlineStr"/>
-      <c r="I609" t="inlineStr">
-        <is>
-          <t>5551991937322</t>
-        </is>
+      <c r="I609" t="n">
+        <v>5551991937322</v>
       </c>
       <c r="J609" t="inlineStr"/>
       <c r="K609" t="n">
@@ -30195,10 +30159,8 @@
         </is>
       </c>
       <c r="H610" t="inlineStr"/>
-      <c r="I610" t="inlineStr">
-        <is>
-          <t>5551997609007</t>
-        </is>
+      <c r="I610" t="n">
+        <v>5551997609007</v>
       </c>
       <c r="J610" t="inlineStr"/>
       <c r="K610" t="n">
@@ -30295,10 +30257,8 @@
         </is>
       </c>
       <c r="H612" t="inlineStr"/>
-      <c r="I612" t="inlineStr">
-        <is>
-          <t>5551997926063</t>
-        </is>
+      <c r="I612" t="n">
+        <v>5551997926063</v>
       </c>
       <c r="J612" t="inlineStr"/>
       <c r="K612" t="n">
@@ -30347,10 +30307,8 @@
         </is>
       </c>
       <c r="H613" t="inlineStr"/>
-      <c r="I613" t="inlineStr">
-        <is>
-          <t>555132092000</t>
-        </is>
+      <c r="I613" t="n">
+        <v>555132092000</v>
       </c>
       <c r="J613" t="inlineStr"/>
       <c r="K613" t="n">
@@ -30399,10 +30357,8 @@
         </is>
       </c>
       <c r="H614" t="inlineStr"/>
-      <c r="I614" t="inlineStr">
-        <is>
-          <t>5551999893500</t>
-        </is>
+      <c r="I614" t="n">
+        <v>5551999893500</v>
       </c>
       <c r="J614" t="inlineStr"/>
       <c r="K614" t="n">
@@ -30451,10 +30407,8 @@
         </is>
       </c>
       <c r="H615" t="inlineStr"/>
-      <c r="I615" t="inlineStr">
-        <is>
-          <t>555132240169</t>
-        </is>
+      <c r="I615" t="n">
+        <v>555132240169</v>
       </c>
       <c r="J615" t="inlineStr"/>
       <c r="K615" t="n">
@@ -30551,10 +30505,8 @@
         </is>
       </c>
       <c r="H617" t="inlineStr"/>
-      <c r="I617" t="inlineStr">
-        <is>
-          <t>5551991892837</t>
-        </is>
+      <c r="I617" t="n">
+        <v>5551991892837</v>
       </c>
       <c r="J617" t="inlineStr"/>
       <c r="K617" t="n">
@@ -30662,6 +30614,1562 @@
         </is>
       </c>
     </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>MedClin Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>https://medclinclinicas.com.br</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr"/>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>5568999445563</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr"/>
+      <c r="K620" t="n">
+        <v>75</v>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Policlínica Mais Saúde</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>https://maissaudeac.com.br</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr"/>
+      <c r="I621" t="inlineStr"/>
+      <c r="J621" t="inlineStr"/>
+      <c r="K621" t="n">
+        <v>50</v>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Clínica Oncohealth</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>https://clinicaoncohealth.com.br</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr"/>
+      <c r="I622" t="inlineStr"/>
+      <c r="J622" t="inlineStr"/>
+      <c r="K622" t="n">
+        <v>80</v>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>A clínica</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>http://cediacimagem.com.br</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr"/>
+      <c r="I623" t="inlineStr"/>
+      <c r="J623" t="inlineStr"/>
+      <c r="K623" t="n">
+        <v>59</v>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Silvestre Santé</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>https://silvestresante.com.br</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr"/>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>5568999211100</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr"/>
+      <c r="K624" t="n">
+        <v>69</v>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Mottu</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>https://cupommottu.com.br</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr"/>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>556399837387</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr"/>
+      <c r="K625" t="n">
+        <v>78</v>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Dentista Beatriz Côrtes Barbosa</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>https://tr.cybo.com</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr"/>
+      <c r="I626" t="inlineStr"/>
+      <c r="J626" t="inlineStr"/>
+      <c r="K626" t="n">
+        <v>33</v>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>curso de psicologia da universidade federal do acre: história</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>http://www2.ufac.br</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr"/>
+      <c r="I627" t="inlineStr"/>
+      <c r="J627" t="inlineStr"/>
+      <c r="K627" t="n">
+        <v>56</v>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>ThetaHealing Online em Rio Branco</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>https://eeterapeuta.com.br</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr"/>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>5567993398779</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr"/>
+      <c r="K628" t="n">
+        <v>76</v>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>WiFi Map</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>https://www.wifimap.io</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr"/>
+      <c r="I629" t="inlineStr"/>
+      <c r="J629" t="inlineStr"/>
+      <c r="K629" t="n">
+        <v>44</v>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Micro de Ariquemes, RO a Rio Branco, AC</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>https://www.checkmybus.com.ar</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr"/>
+      <c r="I630" t="inlineStr"/>
+      <c r="J630" t="inlineStr"/>
+      <c r="K630" t="n">
+        <v>56</v>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Suporte ao Advogado</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>https://www.tjac.jus.br</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr"/>
+      <c r="I631" t="inlineStr"/>
+      <c r="J631" t="inlineStr"/>
+      <c r="K631" t="n">
+        <v>82</v>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Roberto Duarte</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>https://sapl.riobranco.ac.leg.br</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr"/>
+      <c r="I632" t="inlineStr"/>
+      <c r="J632" t="inlineStr"/>
+      <c r="K632" t="n">
+        <v>67</v>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>OAB-AC: Ordem dos Advogados do Brasil Regional do Acre</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>https://www.caaspsaudeonline.com</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr"/>
+      <c r="I633" t="inlineStr"/>
+      <c r="J633" t="inlineStr"/>
+      <c r="K633" t="n">
+        <v>91</v>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>https://www.ufac.br</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr"/>
+      <c r="I634" t="inlineStr"/>
+      <c r="J634" t="inlineStr"/>
+      <c r="K634" t="n">
+        <v>56</v>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>EDUCAÇÃO FÍSICA</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>https://www.vouprafaculdade.com.br</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr"/>
+      <c r="I635" t="inlineStr"/>
+      <c r="J635" t="inlineStr"/>
+      <c r="K635" t="n">
+        <v>62</v>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Academia Sesc Bosque, Rio Branco: Horário, Preço e Opiniões</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>https://br.fitfit.fitness</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr"/>
+      <c r="I636" t="inlineStr"/>
+      <c r="J636" t="inlineStr"/>
+      <c r="K636" t="n">
+        <v>94</v>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Academias em Rio Branco</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>https://guia.riobranco.br</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr"/>
+      <c r="I637" t="inlineStr"/>
+      <c r="J637" t="inlineStr"/>
+      <c r="K637" t="n">
+        <v>82</v>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>https://academiaevoque.com.br</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr"/>
+      <c r="I638" t="inlineStr"/>
+      <c r="J638" t="inlineStr"/>
+      <c r="K638" t="n">
+        <v>80</v>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>4 academias interessantes na cidade de Rio Branco (AC)</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>https://sairpromundo.com</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr"/>
+      <c r="I639" t="inlineStr"/>
+      <c r="J639" t="inlineStr"/>
+      <c r="K639" t="n">
+        <v>0</v>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Provas Anteriores Daniela Fisioterapeuta Rio Branco...</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>https://www.provasbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr"/>
+      <c r="I640" t="inlineStr"/>
+      <c r="J640" t="inlineStr"/>
+      <c r="K640" t="n">
+        <v>81</v>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta Bruno Henrique em Rio Branco, AC</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>https://mestregeo.com.br</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr"/>
+      <c r="I641" t="inlineStr"/>
+      <c r="J641" t="inlineStr"/>
+      <c r="K641" t="n">
+        <v>33</v>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Dr. Isaias Fiuza Cabral</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>https://www.isaiascabral.com</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr"/>
+      <c r="I642" t="inlineStr"/>
+      <c r="J642" t="inlineStr"/>
+      <c r="K642" t="n">
+        <v>60</v>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Clínica Dra Andrielle Ramalho</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>https://cadeodentista.com.br</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr"/>
+      <c r="I643" t="inlineStr"/>
+      <c r="J643" t="inlineStr"/>
+      <c r="K643" t="n">
+        <v>75</v>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>https://wagner.adv.br</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr"/>
+      <c r="I644" t="inlineStr"/>
+      <c r="J644" t="inlineStr"/>
+      <c r="K644" t="n">
+        <v>73</v>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Licenciatura em Física</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>https://macapa.ifap.edu.br</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr"/>
+      <c r="I645" t="inlineStr"/>
+      <c r="J645" t="inlineStr"/>
+      <c r="K645" t="n">
+        <v>0</v>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Academias em Macapá (AP)</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>https://www.encontramacapa.com</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr"/>
+      <c r="I646" t="inlineStr"/>
+      <c r="J646" t="inlineStr"/>
+      <c r="K646" t="n">
+        <v>64</v>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Atend Já Manaus</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>https://www.atendjaam.com.br</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr"/>
+      <c r="I647" t="inlineStr"/>
+      <c r="J647" t="inlineStr"/>
+      <c r="K647" t="n">
+        <v>0</v>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Transforme sua autoestima com a experiência única de uma clínica de...</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>https://manaus.xn--cirurgiasplsticas-hpb.com</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr"/>
+      <c r="I648" t="inlineStr"/>
+      <c r="J648" t="inlineStr"/>
+      <c r="K648" t="n">
+        <v>22</v>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Guia Médico Unimed FAMA</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>https://www.edoc.ufam.edu.br</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr"/>
+      <c r="I649" t="inlineStr"/>
+      <c r="J649" t="inlineStr"/>
+      <c r="K649" t="n">
+        <v>33</v>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Dentista Manaus Harmonização Facial - Dr. David Amaral</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>https://esteticaguia.com</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr"/>
+      <c r="I650" t="inlineStr"/>
+      <c r="J650" t="inlineStr"/>
+      <c r="K650" t="n">
+        <v>53</v>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Rafael Belizário</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>https://rafaelbelizario.com.br</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr"/>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>5592992049276</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr"/>
+      <c r="K651" t="n">
+        <v>73</v>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L651"/>
+  <dimension ref="A1:L680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30651,10 +30651,8 @@
         </is>
       </c>
       <c r="H620" t="inlineStr"/>
-      <c r="I620" t="inlineStr">
-        <is>
-          <t>5568999445563</t>
-        </is>
+      <c r="I620" t="n">
+        <v>5568999445563</v>
       </c>
       <c r="J620" t="inlineStr"/>
       <c r="K620" t="n">
@@ -30847,10 +30845,8 @@
         </is>
       </c>
       <c r="H624" t="inlineStr"/>
-      <c r="I624" t="inlineStr">
-        <is>
-          <t>5568999211100</t>
-        </is>
+      <c r="I624" t="n">
+        <v>5568999211100</v>
       </c>
       <c r="J624" t="inlineStr"/>
       <c r="K624" t="n">
@@ -30899,10 +30895,8 @@
         </is>
       </c>
       <c r="H625" t="inlineStr"/>
-      <c r="I625" t="inlineStr">
-        <is>
-          <t>556399837387</t>
-        </is>
+      <c r="I625" t="n">
+        <v>556399837387</v>
       </c>
       <c r="J625" t="inlineStr"/>
       <c r="K625" t="n">
@@ -31047,10 +31041,8 @@
         </is>
       </c>
       <c r="H628" t="inlineStr"/>
-      <c r="I628" t="inlineStr">
-        <is>
-          <t>5567993398779</t>
-        </is>
+      <c r="I628" t="n">
+        <v>5567993398779</v>
       </c>
       <c r="J628" t="inlineStr"/>
       <c r="K628" t="n">
@@ -32155,16 +32147,1442 @@
         </is>
       </c>
       <c r="H651" t="inlineStr"/>
-      <c r="I651" t="inlineStr">
-        <is>
-          <t>5592992049276</t>
-        </is>
+      <c r="I651" t="n">
+        <v>5592992049276</v>
       </c>
       <c r="J651" t="inlineStr"/>
       <c r="K651" t="n">
         <v>73</v>
       </c>
       <c r="L651" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Clinlabin</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>https://clinlabin.com.br</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr"/>
+      <c r="I652" t="inlineStr"/>
+      <c r="J652" t="inlineStr"/>
+      <c r="K652" t="n">
+        <v>82</v>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Clínicas Médicas em Maceió</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>https://listatudo.com.br</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr"/>
+      <c r="I653" t="inlineStr"/>
+      <c r="J653" t="inlineStr"/>
+      <c r="K653" t="n">
+        <v>80</v>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>ADVOGADO PREVIDENCIÁRIO MACEIÓ whatsapp</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>https://advogadoprevidenciariomaceio.com</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr"/>
+      <c r="I654" t="inlineStr"/>
+      <c r="J654" t="inlineStr"/>
+      <c r="K654" t="n">
+        <v>64</v>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Nicholas &amp; Marinela Advogados: Página Inicial</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>https://www.nicholasemarinela.com.br</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr"/>
+      <c r="I655" t="inlineStr"/>
+      <c r="J655" t="inlineStr"/>
+      <c r="K655" t="n">
+        <v>82</v>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>https://vitorinoemurta.com.br</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr"/>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>553133470444</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr"/>
+      <c r="K656" t="n">
+        <v>64</v>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Nível superior/educação física/ a partir do 3° semestre/ maceió-al</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>https://brasiliaestagios.com.br</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr"/>
+      <c r="I657" t="inlineStr"/>
+      <c r="J657" t="inlineStr"/>
+      <c r="K657" t="n">
+        <v>81</v>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>https://www.eusoutop.com</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr"/>
+      <c r="I658" t="inlineStr"/>
+      <c r="J658" t="inlineStr"/>
+      <c r="K658" t="n">
+        <v>70</v>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Academias em Maceió, Alagoas, AL</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>https://www.encontraal.com.br</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr"/>
+      <c r="I659" t="inlineStr"/>
+      <c r="J659" t="inlineStr"/>
+      <c r="K659" t="n">
+        <v>64</v>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>https://interfisio.com.br</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr"/>
+      <c r="I660" t="inlineStr"/>
+      <c r="J660" t="inlineStr"/>
+      <c r="K660" t="n">
+        <v>22</v>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Nossas Unidades</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>https://www.hospitalsantaizabel.org.br</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr"/>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>5571981883380</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr"/>
+      <c r="K661" t="n">
+        <v>81</v>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Clínica de Ginecologia e Obstetrícia em Salvador</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>https://clinicasagio.com.br</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr"/>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>5571993547157</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr"/>
+      <c r="K662" t="n">
+        <v>75</v>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Buscar Médicos</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>https://www.cremeb.org.br</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr"/>
+      <c r="I663" t="inlineStr"/>
+      <c r="J663" t="inlineStr"/>
+      <c r="K663" t="n">
+        <v>70</v>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Odonto Clínica Iguatemi</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>https://www.odontoclinicaiguatemi.com</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr"/>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>557196241448</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr"/>
+      <c r="K664" t="n">
+        <v>81</v>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Local: Salvador</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>https://senhoraterapia.com</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr"/>
+      <c r="I665" t="inlineStr"/>
+      <c r="J665" t="inlineStr"/>
+      <c r="K665" t="n">
+        <v>69</v>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Advogado em Salvador</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>https://advogado.salvador.br</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr"/>
+      <c r="I666" t="inlineStr"/>
+      <c r="J666" t="inlineStr"/>
+      <c r="K666" t="n">
+        <v>64</v>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Educacao Fisica em Salvador-BA — Faculdades...</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>https://aluno.com.br</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr"/>
+      <c r="I667" t="inlineStr"/>
+      <c r="J667" t="inlineStr"/>
+      <c r="K667" t="n">
+        <v>78</v>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Academias em Salvador, Bahia, BA</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>https://www.encontraba.com.br</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr"/>
+      <c r="I668" t="inlineStr"/>
+      <c r="J668" t="inlineStr"/>
+      <c r="K668" t="n">
+        <v>64</v>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Top 20: Academias</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>https://unilocal.com.br</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr"/>
+      <c r="I669" t="inlineStr"/>
+      <c r="J669" t="inlineStr"/>
+      <c r="K669" t="n">
+        <v>33</v>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Clinica Escola de Fisioterapia</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>https://fisioterapia.ufba.br</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr"/>
+      <c r="I670" t="inlineStr"/>
+      <c r="J670" t="inlineStr"/>
+      <c r="K670" t="n">
+        <v>0</v>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Multiclinica Fortaleza</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>https://multiclinicafortaleza.com.br</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr"/>
+      <c r="I671" t="inlineStr"/>
+      <c r="J671" t="inlineStr"/>
+      <c r="K671" t="n">
+        <v>60</v>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Clínica SiM: Saúde em Fortaleza, Recife e Salvador</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>https://www.clinicasim.com</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr"/>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>558003576060</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr"/>
+      <c r="K672" t="n">
+        <v>73</v>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Clínica Atualmedic: Especialistas em Saúde em Fortaleza e Consultas Online</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>https://clinicaatualmedic.com.br</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr"/>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>5585981801104</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr"/>
+      <c r="K673" t="n">
+        <v>88</v>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Clínica Santa Clara</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>https://santaclarafortaleza.com.br</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr"/>
+      <c r="I674" t="inlineStr"/>
+      <c r="J674" t="inlineStr"/>
+      <c r="K674" t="n">
+        <v>33</v>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Atend Já Fortaleza</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>https://fortaleza.atendja.com.br</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr"/>
+      <c r="I675" t="inlineStr"/>
+      <c r="J675" t="inlineStr"/>
+      <c r="K675" t="n">
+        <v>90</v>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Clínica Centro</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>https://clinicadocentro.com.br</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr"/>
+      <c r="I676" t="inlineStr"/>
+      <c r="J676" t="inlineStr"/>
+      <c r="K676" t="n">
+        <v>65</v>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Médicos em Fortaleza (CE)</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>https://gradualmedic.com.br</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr"/>
+      <c r="I677" t="inlineStr"/>
+      <c r="J677" t="inlineStr"/>
+      <c r="K677" t="n">
+        <v>56</v>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Dra. Isabela Leandro</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>https://www.draisabelaleandro.com.br</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr"/>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>5585981830066</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr"/>
+      <c r="K678" t="n">
+        <v>81</v>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Onde Atendemos em Fortaleza-CE</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>https://dentistasemfortaleza.com.br</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr"/>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>5511912062131</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr"/>
+      <c r="K679" t="n">
+        <v>56</v>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Psicólogo Clínico em Fortaleza</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>https://www.psicologo-fortaleza.com</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr"/>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>558599426056</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr"/>
+      <c r="K680" t="n">
+        <v>80</v>
+      </c>
+      <c r="L680" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L680"/>
+  <dimension ref="A1:L710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32389,10 +32389,8 @@
         </is>
       </c>
       <c r="H656" t="inlineStr"/>
-      <c r="I656" t="inlineStr">
-        <is>
-          <t>553133470444</t>
-        </is>
+      <c r="I656" t="n">
+        <v>553133470444</v>
       </c>
       <c r="J656" t="inlineStr"/>
       <c r="K656" t="n">
@@ -32633,10 +32631,8 @@
         </is>
       </c>
       <c r="H661" t="inlineStr"/>
-      <c r="I661" t="inlineStr">
-        <is>
-          <t>5571981883380</t>
-        </is>
+      <c r="I661" t="n">
+        <v>5571981883380</v>
       </c>
       <c r="J661" t="inlineStr"/>
       <c r="K661" t="n">
@@ -32685,10 +32681,8 @@
         </is>
       </c>
       <c r="H662" t="inlineStr"/>
-      <c r="I662" t="inlineStr">
-        <is>
-          <t>5571993547157</t>
-        </is>
+      <c r="I662" t="n">
+        <v>5571993547157</v>
       </c>
       <c r="J662" t="inlineStr"/>
       <c r="K662" t="n">
@@ -32785,10 +32779,8 @@
         </is>
       </c>
       <c r="H664" t="inlineStr"/>
-      <c r="I664" t="inlineStr">
-        <is>
-          <t>557196241448</t>
-        </is>
+      <c r="I664" t="n">
+        <v>557196241448</v>
       </c>
       <c r="J664" t="inlineStr"/>
       <c r="K664" t="n">
@@ -33173,10 +33165,8 @@
         </is>
       </c>
       <c r="H672" t="inlineStr"/>
-      <c r="I672" t="inlineStr">
-        <is>
-          <t>558003576060</t>
-        </is>
+      <c r="I672" t="n">
+        <v>558003576060</v>
       </c>
       <c r="J672" t="inlineStr"/>
       <c r="K672" t="n">
@@ -33225,10 +33215,8 @@
         </is>
       </c>
       <c r="H673" t="inlineStr"/>
-      <c r="I673" t="inlineStr">
-        <is>
-          <t>5585981801104</t>
-        </is>
+      <c r="I673" t="n">
+        <v>5585981801104</v>
       </c>
       <c r="J673" t="inlineStr"/>
       <c r="K673" t="n">
@@ -33469,10 +33457,8 @@
         </is>
       </c>
       <c r="H678" t="inlineStr"/>
-      <c r="I678" t="inlineStr">
-        <is>
-          <t>5585981830066</t>
-        </is>
+      <c r="I678" t="n">
+        <v>5585981830066</v>
       </c>
       <c r="J678" t="inlineStr"/>
       <c r="K678" t="n">
@@ -33521,10 +33507,8 @@
         </is>
       </c>
       <c r="H679" t="inlineStr"/>
-      <c r="I679" t="inlineStr">
-        <is>
-          <t>5511912062131</t>
-        </is>
+      <c r="I679" t="n">
+        <v>5511912062131</v>
       </c>
       <c r="J679" t="inlineStr"/>
       <c r="K679" t="n">
@@ -33573,16 +33557,1502 @@
         </is>
       </c>
       <c r="H680" t="inlineStr"/>
-      <c r="I680" t="inlineStr">
-        <is>
-          <t>558599426056</t>
-        </is>
+      <c r="I680" t="n">
+        <v>558599426056</v>
       </c>
       <c r="J680" t="inlineStr"/>
       <c r="K680" t="n">
         <v>80</v>
       </c>
       <c r="L680" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Busca por médicos</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>https://crmdf.org.br</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr"/>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>556133220001</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr"/>
+      <c r="K681" t="n">
+        <v>64</v>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Clinica Brasilia</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>https://clinicabrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr"/>
+      <c r="I682" t="inlineStr"/>
+      <c r="J682" t="inlineStr"/>
+      <c r="K682" t="n">
+        <v>0</v>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Dentista Em Brasília DF</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>https://centralodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr"/>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>5561992022622</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr"/>
+      <c r="K683" t="n">
+        <v>62</v>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Clínica Inovar</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>https://clinicainovarbrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr"/>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>5561996851690</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr"/>
+      <c r="K684" t="n">
+        <v>60</v>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Dentista Conjunto Nacional</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>https://aquariusodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr"/>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>5561996104900</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr"/>
+      <c r="K685" t="n">
+        <v>73</v>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>EM Odonto</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>https://emodonto.com.br</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr"/>
+      <c r="I686" t="inlineStr"/>
+      <c r="J686" t="inlineStr"/>
+      <c r="K686" t="n">
+        <v>69</v>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Menicucci Odontologia</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>https://www.menicucciodonto.com.br</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr"/>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>556192150204</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr"/>
+      <c r="K687" t="n">
+        <v>62</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Psicólogo Brasília</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>https://clinica.cetfisio.com.br</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr"/>
+      <c r="I688" t="inlineStr"/>
+      <c r="J688" t="inlineStr"/>
+      <c r="K688" t="n">
+        <v>62</v>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Costa Couto Advogados Associados S/S</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>https://costacouto.com.br</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr"/>
+      <c r="I689" t="inlineStr"/>
+      <c r="J689" t="inlineStr"/>
+      <c r="K689" t="n">
+        <v>73</v>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Fonseca de Melo e Britto Advogados</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>https://www.fonsecademelobritto.com</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr"/>
+      <c r="I690" t="inlineStr"/>
+      <c r="J690" t="inlineStr"/>
+      <c r="K690" t="n">
+        <v>0</v>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Advocacia Fernanda Hernandez</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>https://hernandez.adv.br</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr"/>
+      <c r="I691" t="inlineStr"/>
+      <c r="J691" t="inlineStr"/>
+      <c r="K691" t="n">
+        <v>55</v>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>áreas de atuação desejadas por estudantes de educação física</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>https://periodicos.ufsm.br</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr"/>
+      <c r="I692" t="inlineStr"/>
+      <c r="J692" t="inlineStr"/>
+      <c r="K692" t="n">
+        <v>67</v>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Akad Academia</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>https://www.origym.com.br</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr"/>
+      <c r="I693" t="inlineStr"/>
+      <c r="J693" t="inlineStr"/>
+      <c r="K693" t="n">
+        <v>60</v>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>academia bodytech lago sul</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>https://www.judobrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr"/>
+      <c r="I694" t="inlineStr"/>
+      <c r="J694" t="inlineStr"/>
+      <c r="K694" t="n">
+        <v>44</v>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Acuas Fitness</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>https://www.acuasfitness.com.br</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr"/>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>5561992582131</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr"/>
+      <c r="K695" t="n">
+        <v>69</v>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta in Brasília</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>https://www.misterwhat.com.br</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr"/>
+      <c r="I696" t="inlineStr"/>
+      <c r="J696" t="inlineStr"/>
+      <c r="K696" t="n">
+        <v>69</v>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Clínica De Fisioterapia Na Região Administrativa Em Brasília DF...</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>https://evoluirfisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr"/>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>5561986783951</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr"/>
+      <c r="K697" t="n">
+        <v>75</v>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Clínica MedPrime</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>https://www.medprime.com.br</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr"/>
+      <c r="I698" t="inlineStr"/>
+      <c r="J698" t="inlineStr"/>
+      <c r="K698" t="n">
+        <v>50</v>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Análise da demografia médica de um município Goiano</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>http://revistasaudecoletiva.com.br</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr"/>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>551136543193</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr"/>
+      <c r="K699" t="n">
+        <v>56</v>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Contato e Agendamento</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>https://www.studiodental.dental</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr"/>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>5562982433773</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr"/>
+      <c r="K700" t="n">
+        <v>73</v>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>OdontoTop Goiânia - GO</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>https://clinicaodontotop.com.br</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr"/>
+      <c r="I701" t="inlineStr"/>
+      <c r="J701" t="inlineStr"/>
+      <c r="K701" t="n">
+        <v>44</v>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Psicólogo em Goiânia</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>https://felipeoliveirapsicologia.com.br</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr"/>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>5562994127181</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr"/>
+      <c r="K702" t="n">
+        <v>60</v>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Instituto Psicologia Goiânia</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>http://www.psicologiagoiania.com.br</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr"/>
+      <c r="I703" t="inlineStr"/>
+      <c r="J703" t="inlineStr"/>
+      <c r="K703" t="n">
+        <v>0</v>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Rede Âmago</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>https://www.redeamago.com.br</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr"/>
+      <c r="I704" t="inlineStr"/>
+      <c r="J704" t="inlineStr"/>
+      <c r="K704" t="n">
+        <v>67</v>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Wagner Souza</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>https://www.wagnersouzaadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr"/>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>5562996421788</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr"/>
+      <c r="K705" t="n">
+        <v>100</v>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Gomes Bezerra &amp; Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>https://gomesbezerra.adv.br</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr"/>
+      <c r="I706" t="inlineStr"/>
+      <c r="J706" t="inlineStr"/>
+      <c r="K706" t="n">
+        <v>73</v>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Os Melhores Advogados de Goiânia</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>https://advocaciasgoiania.com</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr"/>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>5562999502587</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr"/>
+      <c r="K707" t="n">
+        <v>55</v>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Academia Goiás-GO</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>https://sni.org.br</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr"/>
+      <c r="I708" t="inlineStr"/>
+      <c r="J708" t="inlineStr"/>
+      <c r="K708" t="n">
+        <v>80</v>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Formula Academia</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>https://www.formulaacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr"/>
+      <c r="I709" t="inlineStr"/>
+      <c r="J709" t="inlineStr"/>
+      <c r="K709" t="n">
+        <v>40</v>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Clínica de Fisioterapia em Goiânia Instituto Navez Queiroz</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>https://institutonavesqueiroz.com</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr"/>
+      <c r="I710" t="inlineStr"/>
+      <c r="J710" t="inlineStr"/>
+      <c r="K710" t="n">
+        <v>75</v>
+      </c>
+      <c r="L710" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L710"/>
+  <dimension ref="A1:L748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33607,10 +33607,8 @@
         </is>
       </c>
       <c r="H681" t="inlineStr"/>
-      <c r="I681" t="inlineStr">
-        <is>
-          <t>556133220001</t>
-        </is>
+      <c r="I681" t="n">
+        <v>556133220001</v>
       </c>
       <c r="J681" t="inlineStr"/>
       <c r="K681" t="n">
@@ -33707,10 +33705,8 @@
         </is>
       </c>
       <c r="H683" t="inlineStr"/>
-      <c r="I683" t="inlineStr">
-        <is>
-          <t>5561992022622</t>
-        </is>
+      <c r="I683" t="n">
+        <v>5561992022622</v>
       </c>
       <c r="J683" t="inlineStr"/>
       <c r="K683" t="n">
@@ -33759,10 +33755,8 @@
         </is>
       </c>
       <c r="H684" t="inlineStr"/>
-      <c r="I684" t="inlineStr">
-        <is>
-          <t>5561996851690</t>
-        </is>
+      <c r="I684" t="n">
+        <v>5561996851690</v>
       </c>
       <c r="J684" t="inlineStr"/>
       <c r="K684" t="n">
@@ -33811,10 +33805,8 @@
         </is>
       </c>
       <c r="H685" t="inlineStr"/>
-      <c r="I685" t="inlineStr">
-        <is>
-          <t>5561996104900</t>
-        </is>
+      <c r="I685" t="n">
+        <v>5561996104900</v>
       </c>
       <c r="J685" t="inlineStr"/>
       <c r="K685" t="n">
@@ -33911,10 +33903,8 @@
         </is>
       </c>
       <c r="H687" t="inlineStr"/>
-      <c r="I687" t="inlineStr">
-        <is>
-          <t>556192150204</t>
-        </is>
+      <c r="I687" t="n">
+        <v>556192150204</v>
       </c>
       <c r="J687" t="inlineStr"/>
       <c r="K687" t="n">
@@ -34299,10 +34289,8 @@
         </is>
       </c>
       <c r="H695" t="inlineStr"/>
-      <c r="I695" t="inlineStr">
-        <is>
-          <t>5561992582131</t>
-        </is>
+      <c r="I695" t="n">
+        <v>5561992582131</v>
       </c>
       <c r="J695" t="inlineStr"/>
       <c r="K695" t="n">
@@ -34399,10 +34387,8 @@
         </is>
       </c>
       <c r="H697" t="inlineStr"/>
-      <c r="I697" t="inlineStr">
-        <is>
-          <t>5561986783951</t>
-        </is>
+      <c r="I697" t="n">
+        <v>5561986783951</v>
       </c>
       <c r="J697" t="inlineStr"/>
       <c r="K697" t="n">
@@ -34499,10 +34485,8 @@
         </is>
       </c>
       <c r="H699" t="inlineStr"/>
-      <c r="I699" t="inlineStr">
-        <is>
-          <t>551136543193</t>
-        </is>
+      <c r="I699" t="n">
+        <v>551136543193</v>
       </c>
       <c r="J699" t="inlineStr"/>
       <c r="K699" t="n">
@@ -34551,10 +34535,8 @@
         </is>
       </c>
       <c r="H700" t="inlineStr"/>
-      <c r="I700" t="inlineStr">
-        <is>
-          <t>5562982433773</t>
-        </is>
+      <c r="I700" t="n">
+        <v>5562982433773</v>
       </c>
       <c r="J700" t="inlineStr"/>
       <c r="K700" t="n">
@@ -34651,10 +34633,8 @@
         </is>
       </c>
       <c r="H702" t="inlineStr"/>
-      <c r="I702" t="inlineStr">
-        <is>
-          <t>5562994127181</t>
-        </is>
+      <c r="I702" t="n">
+        <v>5562994127181</v>
       </c>
       <c r="J702" t="inlineStr"/>
       <c r="K702" t="n">
@@ -34799,10 +34779,8 @@
         </is>
       </c>
       <c r="H705" t="inlineStr"/>
-      <c r="I705" t="inlineStr">
-        <is>
-          <t>5562996421788</t>
-        </is>
+      <c r="I705" t="n">
+        <v>5562996421788</v>
       </c>
       <c r="J705" t="inlineStr"/>
       <c r="K705" t="n">
@@ -34899,10 +34877,8 @@
         </is>
       </c>
       <c r="H707" t="inlineStr"/>
-      <c r="I707" t="inlineStr">
-        <is>
-          <t>5562999502587</t>
-        </is>
+      <c r="I707" t="n">
+        <v>5562999502587</v>
       </c>
       <c r="J707" t="inlineStr"/>
       <c r="K707" t="n">
@@ -35058,6 +35034,1870 @@
         </is>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Clínica Vitória</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>http://www.clinicavitoriavc.com.br</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr"/>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>5577999902581</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr"/>
+      <c r="K711" t="n">
+        <v>62</v>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Centro Médico Vitória</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>http://www.centromedicovitoria.com.br</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr"/>
+      <c r="I712" t="inlineStr"/>
+      <c r="J712" t="inlineStr"/>
+      <c r="K712" t="n">
+        <v>56</v>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Clínica Médica da Praia da Vitória</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>https://clinicamedicapraiavitoria.pt</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr"/>
+      <c r="I713" t="inlineStr"/>
+      <c r="J713" t="inlineStr"/>
+      <c r="K713" t="n">
+        <v>75</v>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Centermed Vitória</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>https://centermedvitoria.com.br</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr"/>
+      <c r="I714" t="inlineStr"/>
+      <c r="J714" t="inlineStr"/>
+      <c r="K714" t="n">
+        <v>65</v>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>clínica vitória</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>https://www.guiamedicoconquista.com.br</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr"/>
+      <c r="I715" t="inlineStr"/>
+      <c r="J715" t="inlineStr"/>
+      <c r="K715" t="n">
+        <v>81</v>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Vitória é a capital com mais médicos por habitantes do Brasil</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>https://crmes.org.br</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr"/>
+      <c r="I716" t="inlineStr"/>
+      <c r="J716" t="inlineStr"/>
+      <c r="K716" t="n">
+        <v>80</v>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Dentistas em Vitória e região</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>https://saude.melhores.com</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr"/>
+      <c r="I717" t="inlineStr"/>
+      <c r="J717" t="inlineStr"/>
+      <c r="K717" t="n">
+        <v>60</v>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Dentistas em Vitória, ES</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>https://mobile.guiamais.com.br</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr"/>
+      <c r="I718" t="inlineStr"/>
+      <c r="J718" t="inlineStr"/>
+      <c r="K718" t="n">
+        <v>100</v>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Dentista em Vitória</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>https://rayanemagnol.com.br</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr"/>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>5527997292224</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr"/>
+      <c r="K719" t="n">
+        <v>73</v>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Hora actual en España</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>https://es.true-time.com</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr"/>
+      <c r="I720" t="inlineStr"/>
+      <c r="J720" t="inlineStr"/>
+      <c r="K720" t="n">
+        <v>56</v>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Advogado família em Damolândia</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>https://advaqui.com</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr"/>
+      <c r="I721" t="inlineStr"/>
+      <c r="J721" t="inlineStr"/>
+      <c r="K721" t="n">
+        <v>73</v>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Seja bem-vindo</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>https://educacaofisica.ufes.br</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr"/>
+      <c r="I722" t="inlineStr"/>
+      <c r="J722" t="inlineStr"/>
+      <c r="K722" t="n">
+        <v>65</v>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>EDUCAÇÃO FÍSICA ESCOLAR</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>https://faculdadedevitoria.edu.br</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>552732221608</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr"/>
+      <c r="K723" t="n">
+        <v>78</v>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Centro de Educação Física e Desportos - CEFD</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>https://prograd.ufes.br</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="inlineStr"/>
+      <c r="J724" t="inlineStr"/>
+      <c r="K724" t="n">
+        <v>65</v>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Fisioterapia Avançada Juliana Moura - Serra</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>https://julianamourafisio.com.br</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr"/>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>5527988370502</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr"/>
+      <c r="K725" t="n">
+        <v>80</v>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Rehabili</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>https://www.rehabili.com.br</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr"/>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>5527998996823</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr"/>
+      <c r="K726" t="n">
+        <v>67</v>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Vitória GrandFisio</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>http://www.vitoriagrandfisio.com</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr"/>
+      <c r="I727" t="inlineStr"/>
+      <c r="J727" t="inlineStr"/>
+      <c r="K727" t="n">
+        <v>50</v>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Os 10 melhores centros de Fisioterapia em Vitória</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>https://vitoria.infoisinfo-br.com</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr"/>
+      <c r="I728" t="inlineStr"/>
+      <c r="J728" t="inlineStr"/>
+      <c r="K728" t="n">
+        <v>64</v>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Dr. Cristiano Leite Praça Filho</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>https://www.drcristianoleite.com</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr"/>
+      <c r="I729" t="inlineStr"/>
+      <c r="J729" t="inlineStr"/>
+      <c r="K729" t="n">
+        <v>67</v>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Simples Sublocação BH</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>http://www.simplespsicologia.com.br</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr"/>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>5531982131701</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr"/>
+      <c r="K730" t="n">
+        <v>67</v>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Terapeuta em Belo Horizonte, MG</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>https://www.findhealthclinics.org</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr"/>
+      <c r="I731" t="inlineStr"/>
+      <c r="J731" t="inlineStr"/>
+      <c r="K731" t="n">
+        <v>33</v>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>MassagemJ !</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>https://massagemja.com.br</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr"/>
+      <c r="I732" t="inlineStr"/>
+      <c r="J732" t="inlineStr"/>
+      <c r="K732" t="n">
+        <v>75</v>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Aroeira Salles Advogados: Há 20 anos auxiliando grandes ...</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>https://www.aroeirasalles.com.br</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr"/>
+      <c r="I733" t="inlineStr"/>
+      <c r="J733" t="inlineStr"/>
+      <c r="K733" t="n">
+        <v>73</v>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Advogado de Familia em Belo Horizonte: Página Inicial</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>https://advogadofamiliarbh.com.br</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr"/>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>5531996362444</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr"/>
+      <c r="K734" t="n">
+        <v>73</v>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>https://www.wantcourse.com</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr"/>
+      <c r="I735" t="inlineStr"/>
+      <c r="J735" t="inlineStr"/>
+      <c r="K735" t="n">
+        <v>89</v>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Treinador</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>https://empregosvagasbh.com.br</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr"/>
+      <c r="I736" t="inlineStr"/>
+      <c r="J736" t="inlineStr"/>
+      <c r="K736" t="n">
+        <v>33</v>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Vaga De Treinador</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>https://betavagas.com</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="inlineStr"/>
+      <c r="J737" t="inlineStr"/>
+      <c r="K737" t="n">
+        <v>78</v>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Academia Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>https://academiaexito.com.br</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr"/>
+      <c r="I738" t="inlineStr"/>
+      <c r="J738" t="inlineStr"/>
+      <c r="K738" t="n">
+        <v>70</v>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Vibefit Academia</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>https://www.vibefit.fit</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr"/>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>5531991570414</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr"/>
+      <c r="K739" t="n">
+        <v>60</v>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Clínica Vicci: Fisioterapia e Ortopedia em BH</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>https://www.clinicavicci.com.br</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr"/>
+      <c r="I740" t="inlineStr"/>
+      <c r="J740" t="inlineStr"/>
+      <c r="K740" t="n">
+        <v>50</v>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>MoviMente Reabilitação</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>https://movimentereabilitacao.com.br</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr"/>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>5531991785185</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr"/>
+      <c r="K741" t="n">
+        <v>69</v>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Reabilitar</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>https://reabilitarqv.com.br</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr"/>
+      <c r="I742" t="inlineStr"/>
+      <c r="J742" t="inlineStr"/>
+      <c r="K742" t="n">
+        <v>22</v>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Articularis</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>https://articularisfisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr"/>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>553182230326</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr"/>
+      <c r="K743" t="n">
+        <v>69</v>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Inicio</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>https://www.centerfisioclinica.com.br</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr"/>
+      <c r="I744" t="inlineStr"/>
+      <c r="J744" t="inlineStr"/>
+      <c r="K744" t="n">
+        <v>50</v>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Irio Odontologia</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>https://irioodonto.com.br</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr"/>
+      <c r="I745" t="inlineStr"/>
+      <c r="J745" t="inlineStr"/>
+      <c r="K745" t="n">
+        <v>0</v>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Busca por médicos</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>https://portal.cremerj.org.br</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr"/>
+      <c r="I746" t="inlineStr"/>
+      <c r="J746" t="inlineStr"/>
+      <c r="K746" t="n">
+        <v>65</v>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Guia Médico</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>https://consulta101.com.br</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr"/>
+      <c r="I747" t="inlineStr"/>
+      <c r="J747" t="inlineStr"/>
+      <c r="K747" t="n">
+        <v>81</v>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Dentista em Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>https://doutorhealth.com.br</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr"/>
+      <c r="I748" t="inlineStr"/>
+      <c r="J748" t="inlineStr"/>
+      <c r="K748" t="n">
+        <v>88</v>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L748"/>
+  <dimension ref="A1:L772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35071,10 +35071,8 @@
         </is>
       </c>
       <c r="H711" t="inlineStr"/>
-      <c r="I711" t="inlineStr">
-        <is>
-          <t>5577999902581</t>
-        </is>
+      <c r="I711" t="n">
+        <v>5577999902581</v>
       </c>
       <c r="J711" t="inlineStr"/>
       <c r="K711" t="n">
@@ -35459,10 +35457,8 @@
         </is>
       </c>
       <c r="H719" t="inlineStr"/>
-      <c r="I719" t="inlineStr">
-        <is>
-          <t>5527997292224</t>
-        </is>
+      <c r="I719" t="n">
+        <v>5527997292224</v>
       </c>
       <c r="J719" t="inlineStr"/>
       <c r="K719" t="n">
@@ -35655,10 +35651,8 @@
         </is>
       </c>
       <c r="H723" t="inlineStr"/>
-      <c r="I723" t="inlineStr">
-        <is>
-          <t>552732221608</t>
-        </is>
+      <c r="I723" t="n">
+        <v>552732221608</v>
       </c>
       <c r="J723" t="inlineStr"/>
       <c r="K723" t="n">
@@ -35755,10 +35749,8 @@
         </is>
       </c>
       <c r="H725" t="inlineStr"/>
-      <c r="I725" t="inlineStr">
-        <is>
-          <t>5527988370502</t>
-        </is>
+      <c r="I725" t="n">
+        <v>5527988370502</v>
       </c>
       <c r="J725" t="inlineStr"/>
       <c r="K725" t="n">
@@ -35807,10 +35799,8 @@
         </is>
       </c>
       <c r="H726" t="inlineStr"/>
-      <c r="I726" t="inlineStr">
-        <is>
-          <t>5527998996823</t>
-        </is>
+      <c r="I726" t="n">
+        <v>5527998996823</v>
       </c>
       <c r="J726" t="inlineStr"/>
       <c r="K726" t="n">
@@ -36003,10 +35993,8 @@
         </is>
       </c>
       <c r="H730" t="inlineStr"/>
-      <c r="I730" t="inlineStr">
-        <is>
-          <t>5531982131701</t>
-        </is>
+      <c r="I730" t="n">
+        <v>5531982131701</v>
       </c>
       <c r="J730" t="inlineStr"/>
       <c r="K730" t="n">
@@ -36199,10 +36187,8 @@
         </is>
       </c>
       <c r="H734" t="inlineStr"/>
-      <c r="I734" t="inlineStr">
-        <is>
-          <t>5531996362444</t>
-        </is>
+      <c r="I734" t="n">
+        <v>5531996362444</v>
       </c>
       <c r="J734" t="inlineStr"/>
       <c r="K734" t="n">
@@ -36443,10 +36429,8 @@
         </is>
       </c>
       <c r="H739" t="inlineStr"/>
-      <c r="I739" t="inlineStr">
-        <is>
-          <t>5531991570414</t>
-        </is>
+      <c r="I739" t="n">
+        <v>5531991570414</v>
       </c>
       <c r="J739" t="inlineStr"/>
       <c r="K739" t="n">
@@ -36543,10 +36527,8 @@
         </is>
       </c>
       <c r="H741" t="inlineStr"/>
-      <c r="I741" t="inlineStr">
-        <is>
-          <t>5531991785185</t>
-        </is>
+      <c r="I741" t="n">
+        <v>5531991785185</v>
       </c>
       <c r="J741" t="inlineStr"/>
       <c r="K741" t="n">
@@ -36643,10 +36625,8 @@
         </is>
       </c>
       <c r="H743" t="inlineStr"/>
-      <c r="I743" t="inlineStr">
-        <is>
-          <t>553182230326</t>
-        </is>
+      <c r="I743" t="n">
+        <v>553182230326</v>
       </c>
       <c r="J743" t="inlineStr"/>
       <c r="K743" t="n">
@@ -36898,6 +36878,1194 @@
         </is>
       </c>
     </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Clínica Médica Curitiba</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>https://consultacrm.com.br</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr"/>
+      <c r="I749" t="inlineStr"/>
+      <c r="J749" t="inlineStr"/>
+      <c r="K749" t="n">
+        <v>55</v>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>Dentista em Curitiba</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>https://www.institutobucalle.com.br</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr"/>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>5541997113046</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr"/>
+      <c r="K750" t="n">
+        <v>87</v>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Terapeuta em Curitiba</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>https://patriciabredaterapeuta.com.br</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr"/>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>5541992892604</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr"/>
+      <c r="K751" t="n">
+        <v>67</v>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Os Melhores Advogados de Curitiba</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>https://advocaciascuritiba.com</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>5541992425454</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr"/>
+      <c r="K752" t="n">
+        <v>55</v>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Justen, Pereira Oliveira &amp; Talamini</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>https://justen.com.br</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr"/>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>554130171800</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr"/>
+      <c r="K753" t="n">
+        <v>82</v>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>ADVOGADOS EM CURITIBA Oliveira &amp; Santos Advogados Escritório de Advocacia em Curitiba Advogados Criminalistas em Curitib</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>https://oliveiraesantosadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr"/>
+      <c r="I754" t="inlineStr"/>
+      <c r="J754" t="inlineStr"/>
+      <c r="K754" t="n">
+        <v>73</v>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>NIWA ADVOGADOS</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>https://niwaadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr"/>
+      <c r="I755" t="inlineStr"/>
+      <c r="J755" t="inlineStr"/>
+      <c r="K755" t="n">
+        <v>91</v>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Fisiosim - Clínica de Fisioterapia</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>http://www.fisiosim.com.br</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr"/>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>554132781553</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr"/>
+      <c r="K756" t="n">
+        <v>47</v>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Fisioterapia e Fisioterapia Esportiva em Curitiba</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>https://clinicaredes.com.br</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr"/>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>554184781302</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr"/>
+      <c r="K757" t="n">
+        <v>67</v>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Pilates - Fisioterapia - Osteopatia</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>https://www.fisioclinicacuritiba.com.br</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr"/>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>5541998885620</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr"/>
+      <c r="K758" t="n">
+        <v>80</v>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Clínica de Fisioterapia Centro Curitiba PR</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>https://www.fisiocarecwb.com.br</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr"/>
+      <c r="I759" t="inlineStr"/>
+      <c r="J759" t="inlineStr"/>
+      <c r="K759" t="n">
+        <v>81</v>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>A CLÍNICA</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>https://www.alianceclinicamedica.com.br</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr"/>
+      <c r="I760" t="inlineStr"/>
+      <c r="J760" t="inlineStr"/>
+      <c r="K760" t="n">
+        <v>65</v>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Portal Hospital de Clínicas de Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>https://www.hcpa.edu.br</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr"/>
+      <c r="I761" t="inlineStr"/>
+      <c r="J761" t="inlineStr"/>
+      <c r="K761" t="n">
+        <v>76</v>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Clínica Assis Brasil 3224</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>https://centraldeconsultas.med.br</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr"/>
+      <c r="I762" t="inlineStr"/>
+      <c r="J762" t="inlineStr"/>
+      <c r="K762" t="n">
+        <v>33</v>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Centro Médico Adventista</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>https://portoalegre.clinicaadventista.org.br</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr"/>
+      <c r="I763" t="inlineStr"/>
+      <c r="J763" t="inlineStr"/>
+      <c r="K763" t="n">
+        <v>22</v>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Hospital Moinhos de Vento: Página Principal</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>https://www.hospitalmoinhos.org.br</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr"/>
+      <c r="I764" t="inlineStr"/>
+      <c r="J764" t="inlineStr"/>
+      <c r="K764" t="n">
+        <v>56</v>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Psicologo Acessivel</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>https://en.nucleodepsicologiapoa.com</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr"/>
+      <c r="I765" t="inlineStr"/>
+      <c r="J765" t="inlineStr"/>
+      <c r="K765" t="n">
+        <v>73</v>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Lippert Advogados</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>https://www.lippert.com.br</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr"/>
+      <c r="I766" t="inlineStr"/>
+      <c r="J766" t="inlineStr"/>
+      <c r="K766" t="n">
+        <v>64</v>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Garcia &amp; Garcia Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>https://www.garciaegarcia.com.br</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr"/>
+      <c r="I767" t="inlineStr"/>
+      <c r="J767" t="inlineStr"/>
+      <c r="K767" t="n">
+        <v>73</v>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>AM Advogados</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>https://www.andrademaia.com.br</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr"/>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>555193425529</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr"/>
+      <c r="K768" t="n">
+        <v>55</v>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Rezende Avogados S/S</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>https://www.rezendeadvogados.adv.br</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr"/>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>5551984910761</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr"/>
+      <c r="K769" t="n">
+        <v>64</v>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Escola de Educação Física da UFRGS (ESEF) em Porto Alegre/RS</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>https://www.hagah.com.br</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr"/>
+      <c r="I770" t="inlineStr"/>
+      <c r="J770" t="inlineStr"/>
+      <c r="K770" t="n">
+        <v>22</v>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>As 10 melhores academias de Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>https://curtindoportoalegre.com.br</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr"/>
+      <c r="I771" t="inlineStr"/>
+      <c r="J771" t="inlineStr"/>
+      <c r="K771" t="n">
+        <v>67</v>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>Academias em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>https://www.encontraportoalegre.com.br</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr"/>
+      <c r="I772" t="inlineStr"/>
+      <c r="J772" t="inlineStr"/>
+      <c r="K772" t="n">
+        <v>55</v>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L772"/>
+  <dimension ref="A1:L792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36963,10 +36963,8 @@
         </is>
       </c>
       <c r="H750" t="inlineStr"/>
-      <c r="I750" t="inlineStr">
-        <is>
-          <t>5541997113046</t>
-        </is>
+      <c r="I750" t="n">
+        <v>5541997113046</v>
       </c>
       <c r="J750" t="inlineStr"/>
       <c r="K750" t="n">
@@ -37015,10 +37013,8 @@
         </is>
       </c>
       <c r="H751" t="inlineStr"/>
-      <c r="I751" t="inlineStr">
-        <is>
-          <t>5541992892604</t>
-        </is>
+      <c r="I751" t="n">
+        <v>5541992892604</v>
       </c>
       <c r="J751" t="inlineStr"/>
       <c r="K751" t="n">
@@ -37067,10 +37063,8 @@
         </is>
       </c>
       <c r="H752" t="inlineStr"/>
-      <c r="I752" t="inlineStr">
-        <is>
-          <t>5541992425454</t>
-        </is>
+      <c r="I752" t="n">
+        <v>5541992425454</v>
       </c>
       <c r="J752" t="inlineStr"/>
       <c r="K752" t="n">
@@ -37119,10 +37113,8 @@
         </is>
       </c>
       <c r="H753" t="inlineStr"/>
-      <c r="I753" t="inlineStr">
-        <is>
-          <t>554130171800</t>
-        </is>
+      <c r="I753" t="n">
+        <v>554130171800</v>
       </c>
       <c r="J753" t="inlineStr"/>
       <c r="K753" t="n">
@@ -37267,10 +37259,8 @@
         </is>
       </c>
       <c r="H756" t="inlineStr"/>
-      <c r="I756" t="inlineStr">
-        <is>
-          <t>554132781553</t>
-        </is>
+      <c r="I756" t="n">
+        <v>554132781553</v>
       </c>
       <c r="J756" t="inlineStr"/>
       <c r="K756" t="n">
@@ -37319,10 +37309,8 @@
         </is>
       </c>
       <c r="H757" t="inlineStr"/>
-      <c r="I757" t="inlineStr">
-        <is>
-          <t>554184781302</t>
-        </is>
+      <c r="I757" t="n">
+        <v>554184781302</v>
       </c>
       <c r="J757" t="inlineStr"/>
       <c r="K757" t="n">
@@ -37371,10 +37359,8 @@
         </is>
       </c>
       <c r="H758" t="inlineStr"/>
-      <c r="I758" t="inlineStr">
-        <is>
-          <t>5541998885620</t>
-        </is>
+      <c r="I758" t="n">
+        <v>5541998885620</v>
       </c>
       <c r="J758" t="inlineStr"/>
       <c r="K758" t="n">
@@ -37855,10 +37841,8 @@
         </is>
       </c>
       <c r="H768" t="inlineStr"/>
-      <c r="I768" t="inlineStr">
-        <is>
-          <t>555193425529</t>
-        </is>
+      <c r="I768" t="n">
+        <v>555193425529</v>
       </c>
       <c r="J768" t="inlineStr"/>
       <c r="K768" t="n">
@@ -37907,10 +37891,8 @@
         </is>
       </c>
       <c r="H769" t="inlineStr"/>
-      <c r="I769" t="inlineStr">
-        <is>
-          <t>5551984910761</t>
-        </is>
+      <c r="I769" t="n">
+        <v>5551984910761</v>
       </c>
       <c r="J769" t="inlineStr"/>
       <c r="K769" t="n">
@@ -38066,6 +38048,994 @@
         </is>
       </c>
     </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>médicos em Rio Branco</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>https://buscamedico.org</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr"/>
+      <c r="I773" t="inlineStr"/>
+      <c r="J773" t="inlineStr"/>
+      <c r="K773" t="n">
+        <v>0</v>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Características nutricionais de pacientes com a COVID-19 em uma ...</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>https://braspenjournal.org</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr"/>
+      <c r="I774" t="inlineStr"/>
+      <c r="J774" t="inlineStr"/>
+      <c r="K774" t="n">
+        <v>56</v>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Rede Referenciada</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>http://www.sulamerica.com.br</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr"/>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>551130049723</t>
+        </is>
+      </c>
+      <c r="J775" t="inlineStr"/>
+      <c r="K775" t="n">
+        <v>80</v>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Advogado Trabalhista em Rio Branco/AC</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>https://www.mattozoadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr"/>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>5584991061400</t>
+        </is>
+      </c>
+      <c r="J776" t="inlineStr"/>
+      <c r="K776" t="n">
+        <v>64</v>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>https://www.uninorteac.edu.br</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr"/>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>556833027000</t>
+        </is>
+      </c>
+      <c r="J777" t="inlineStr"/>
+      <c r="K777" t="n">
+        <v>33</v>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>A DANÇA NAS AULAS DE EDUCAÇÃO FÍSICA NO ENSINO MÉDIO ...</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>https://periodicos.ifac.edu.br</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr"/>
+      <c r="I778" t="inlineStr"/>
+      <c r="J778" t="inlineStr"/>
+      <c r="K778" t="n">
+        <v>56</v>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>articulação do conhecimento da educação física no ensino médio</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>https://periodicos.upe.br</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr"/>
+      <c r="I779" t="inlineStr"/>
+      <c r="J779" t="inlineStr"/>
+      <c r="K779" t="n">
+        <v>62</v>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>Estagiário(A) De Educação Física</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>https://bebee.com</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr"/>
+      <c r="I780" t="inlineStr"/>
+      <c r="J780" t="inlineStr"/>
+      <c r="K780" t="n">
+        <v>69</v>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>Eventos Regionais</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>https://cbce.org.br</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr"/>
+      <c r="I781" t="inlineStr"/>
+      <c r="J781" t="inlineStr"/>
+      <c r="K781" t="n">
+        <v>89</v>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>https://www.ceap.br</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr"/>
+      <c r="I782" t="inlineStr"/>
+      <c r="J782" t="inlineStr"/>
+      <c r="K782" t="n">
+        <v>56</v>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Educação Física escolar: diagnóstico da infraestrutura de escolas ...</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>https://ojs.studiespublicacoes.com.br</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr"/>
+      <c r="I783" t="inlineStr"/>
+      <c r="J783" t="inlineStr"/>
+      <c r="K783" t="n">
+        <v>33</v>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>CRS 003/2026</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>https://sescamapa.enlizt.me</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr"/>
+      <c r="I784" t="inlineStr"/>
+      <c r="J784" t="inlineStr"/>
+      <c r="K784" t="n">
+        <v>56</v>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Instituto Federal do Amapá</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>https://processoseletivo.ifap.edu.br</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr"/>
+      <c r="I785" t="inlineStr"/>
+      <c r="J785" t="inlineStr"/>
+      <c r="K785" t="n">
+        <v>22</v>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Maioral Tucuju Academia - Academia Completa em Macapá AP</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>https://maioraltucujuacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr"/>
+      <c r="I786" t="inlineStr"/>
+      <c r="J786" t="inlineStr"/>
+      <c r="K786" t="n">
+        <v>40</v>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>PRECEPTOR</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>https://vempraestacio.gupy.io</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr"/>
+      <c r="I787" t="inlineStr"/>
+      <c r="J787" t="inlineStr"/>
+      <c r="K787" t="n">
+        <v>69</v>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>um estudo experimental</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>https://ojs.atlanticaeditora.com.br</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr"/>
+      <c r="I788" t="inlineStr"/>
+      <c r="J788" t="inlineStr"/>
+      <c r="K788" t="n">
+        <v>67</v>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>ONCOLÓGICA DO BRASIL</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>https://caaam.org.br</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr"/>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>5592984091888</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr"/>
+      <c r="K789" t="n">
+        <v>73</v>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Cimédica</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>https://www.cimedica.com.br</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr"/>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>5592993974848</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr"/>
+      <c r="K790" t="n">
+        <v>69</v>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Geap credencia clínica Oncológica do Brasil, em Manaus</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>https://www.geap.org.br</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr"/>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>5561998593861</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr"/>
+      <c r="K791" t="n">
+        <v>62</v>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>CMM Clínica Médica Manaus</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>https://cmmclinica.com.br</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr"/>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>5592991124340</t>
+        </is>
+      </c>
+      <c r="J792" t="inlineStr"/>
+      <c r="K792" t="n">
+        <v>93</v>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L792"/>
+  <dimension ref="A1:L811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38181,10 +38181,8 @@
         </is>
       </c>
       <c r="H775" t="inlineStr"/>
-      <c r="I775" t="inlineStr">
-        <is>
-          <t>551130049723</t>
-        </is>
+      <c r="I775" t="n">
+        <v>551130049723</v>
       </c>
       <c r="J775" t="inlineStr"/>
       <c r="K775" t="n">
@@ -38233,10 +38231,8 @@
         </is>
       </c>
       <c r="H776" t="inlineStr"/>
-      <c r="I776" t="inlineStr">
-        <is>
-          <t>5584991061400</t>
-        </is>
+      <c r="I776" t="n">
+        <v>5584991061400</v>
       </c>
       <c r="J776" t="inlineStr"/>
       <c r="K776" t="n">
@@ -38285,10 +38281,8 @@
         </is>
       </c>
       <c r="H777" t="inlineStr"/>
-      <c r="I777" t="inlineStr">
-        <is>
-          <t>556833027000</t>
-        </is>
+      <c r="I777" t="n">
+        <v>556833027000</v>
       </c>
       <c r="J777" t="inlineStr"/>
       <c r="K777" t="n">
@@ -38865,10 +38859,8 @@
         </is>
       </c>
       <c r="H789" t="inlineStr"/>
-      <c r="I789" t="inlineStr">
-        <is>
-          <t>5592984091888</t>
-        </is>
+      <c r="I789" t="n">
+        <v>5592984091888</v>
       </c>
       <c r="J789" t="inlineStr"/>
       <c r="K789" t="n">
@@ -38917,10 +38909,8 @@
         </is>
       </c>
       <c r="H790" t="inlineStr"/>
-      <c r="I790" t="inlineStr">
-        <is>
-          <t>5592993974848</t>
-        </is>
+      <c r="I790" t="n">
+        <v>5592993974848</v>
       </c>
       <c r="J790" t="inlineStr"/>
       <c r="K790" t="n">
@@ -38969,10 +38959,8 @@
         </is>
       </c>
       <c r="H791" t="inlineStr"/>
-      <c r="I791" t="inlineStr">
-        <is>
-          <t>5561998593861</t>
-        </is>
+      <c r="I791" t="n">
+        <v>5561998593861</v>
       </c>
       <c r="J791" t="inlineStr"/>
       <c r="K791" t="n">
@@ -39021,16 +39009,962 @@
         </is>
       </c>
       <c r="H792" t="inlineStr"/>
-      <c r="I792" t="inlineStr">
-        <is>
-          <t>5592991124340</t>
-        </is>
+      <c r="I792" t="n">
+        <v>5592991124340</v>
       </c>
       <c r="J792" t="inlineStr"/>
       <c r="K792" t="n">
         <v>93</v>
       </c>
       <c r="L792" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>tabuleiro</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>https://cpsaudemaceio.com.br</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr"/>
+      <c r="I793" t="inlineStr"/>
+      <c r="J793" t="inlineStr"/>
+      <c r="K793" t="n">
+        <v>62</v>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>Clínica Médica da UNIMA</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>https://maceio.afya.com.br</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr"/>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>558291260598</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr"/>
+      <c r="K794" t="n">
+        <v>73</v>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Central de Saúde</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>https://clinicacentraldesaude.com.br</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr"/>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>5582988367695</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr"/>
+      <c r="K795" t="n">
+        <v>64</v>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Dentista em Maceió – AL</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>https://prismaodonto.com</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr"/>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>5582996885655</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr"/>
+      <c r="K796" t="n">
+        <v>60</v>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Marianna Pereira Correia das Neves Lacerda</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>https://www.psimariannapereira.com</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr"/>
+      <c r="I797" t="inlineStr"/>
+      <c r="J797" t="inlineStr"/>
+      <c r="K797" t="n">
+        <v>73</v>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Débora Terapeuta Holística</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>https://www.topsmassagens.com.br</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr"/>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>5582988709008</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr"/>
+      <c r="K798" t="n">
+        <v>89</v>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>Gisele Costa Terapeuta Tântrica</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>https://massagemplusbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr"/>
+      <c r="I799" t="inlineStr"/>
+      <c r="J799" t="inlineStr"/>
+      <c r="K799" t="n">
+        <v>76</v>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>ADVOGADOS EM MACEIÓ, ALAGOAS</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>https://www.alvesjacob.com</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr"/>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>5521983708551</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr"/>
+      <c r="K800" t="n">
+        <v>55</v>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>PSICOLOGO SALVADOR</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>https://psicologoemsalvador.com.br</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr"/>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>5571992103934</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr"/>
+      <c r="K801" t="n">
+        <v>73</v>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Psicólogos em Salvador</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>https://clinicapsique.com</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr"/>
+      <c r="I802" t="inlineStr"/>
+      <c r="J802" t="inlineStr"/>
+      <c r="K802" t="n">
+        <v>73</v>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Terapia de Casal em Salvador</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>https://elidioalmeida.com.br</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr"/>
+      <c r="I803" t="inlineStr"/>
+      <c r="J803" t="inlineStr"/>
+      <c r="K803" t="n">
+        <v>75</v>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Dr. Felipe Guimarães</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>https://www.felipeguimaraesmd.com</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr"/>
+      <c r="I804" t="inlineStr"/>
+      <c r="J804" t="inlineStr"/>
+      <c r="K804" t="n">
+        <v>75</v>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Dra. Andrea Alencar</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>https://nutrologafortaleza.com.br</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr"/>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>558582173952</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr"/>
+      <c r="K805" t="n">
+        <v>75</v>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Clínica Médica Nossa Senhora das Graças em Fortaleza</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>https://superdestaque.com.br</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr"/>
+      <c r="I806" t="inlineStr"/>
+      <c r="J806" t="inlineStr"/>
+      <c r="K806" t="n">
+        <v>56</v>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Telemedicina Médico de Dor</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>https://www.dorfortaleza.com.br</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr"/>
+      <c r="I807" t="inlineStr"/>
+      <c r="J807" t="inlineStr"/>
+      <c r="K807" t="n">
+        <v>69</v>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Centros Integrados de Medicina</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>https://livsaude.com.br</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr"/>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>5508009400044</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr"/>
+      <c r="K808" t="n">
+        <v>65</v>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>Dentista em Fortaleza</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>https://www.clinicamarcelomagalhaes.com.br</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr"/>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>5585991780463</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr"/>
+      <c r="K809" t="n">
+        <v>67</v>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Dentista em Fortaleza</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>https://draalinemelo.com.br</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr"/>
+      <c r="I810" t="inlineStr"/>
+      <c r="J810" t="inlineStr"/>
+      <c r="K810" t="n">
+        <v>69</v>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Psicóloga em Fortaleza Erica Rodrigues</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>https://www.psicologaemfortaleza.com.br</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr"/>
+      <c r="I811" t="inlineStr"/>
+      <c r="J811" t="inlineStr"/>
+      <c r="K811" t="n">
+        <v>0</v>
+      </c>
+      <c r="L811" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L811"/>
+  <dimension ref="A1:L842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39107,10 +39107,8 @@
         </is>
       </c>
       <c r="H794" t="inlineStr"/>
-      <c r="I794" t="inlineStr">
-        <is>
-          <t>558291260598</t>
-        </is>
+      <c r="I794" t="n">
+        <v>558291260598</v>
       </c>
       <c r="J794" t="inlineStr"/>
       <c r="K794" t="n">
@@ -39159,10 +39157,8 @@
         </is>
       </c>
       <c r="H795" t="inlineStr"/>
-      <c r="I795" t="inlineStr">
-        <is>
-          <t>5582988367695</t>
-        </is>
+      <c r="I795" t="n">
+        <v>5582988367695</v>
       </c>
       <c r="J795" t="inlineStr"/>
       <c r="K795" t="n">
@@ -39211,10 +39207,8 @@
         </is>
       </c>
       <c r="H796" t="inlineStr"/>
-      <c r="I796" t="inlineStr">
-        <is>
-          <t>5582996885655</t>
-        </is>
+      <c r="I796" t="n">
+        <v>5582996885655</v>
       </c>
       <c r="J796" t="inlineStr"/>
       <c r="K796" t="n">
@@ -39311,10 +39305,8 @@
         </is>
       </c>
       <c r="H798" t="inlineStr"/>
-      <c r="I798" t="inlineStr">
-        <is>
-          <t>5582988709008</t>
-        </is>
+      <c r="I798" t="n">
+        <v>5582988709008</v>
       </c>
       <c r="J798" t="inlineStr"/>
       <c r="K798" t="n">
@@ -39411,10 +39403,8 @@
         </is>
       </c>
       <c r="H800" t="inlineStr"/>
-      <c r="I800" t="inlineStr">
-        <is>
-          <t>5521983708551</t>
-        </is>
+      <c r="I800" t="n">
+        <v>5521983708551</v>
       </c>
       <c r="J800" t="inlineStr"/>
       <c r="K800" t="n">
@@ -39463,10 +39453,8 @@
         </is>
       </c>
       <c r="H801" t="inlineStr"/>
-      <c r="I801" t="inlineStr">
-        <is>
-          <t>5571992103934</t>
-        </is>
+      <c r="I801" t="n">
+        <v>5571992103934</v>
       </c>
       <c r="J801" t="inlineStr"/>
       <c r="K801" t="n">
@@ -39659,10 +39647,8 @@
         </is>
       </c>
       <c r="H805" t="inlineStr"/>
-      <c r="I805" t="inlineStr">
-        <is>
-          <t>558582173952</t>
-        </is>
+      <c r="I805" t="n">
+        <v>558582173952</v>
       </c>
       <c r="J805" t="inlineStr"/>
       <c r="K805" t="n">
@@ -39807,10 +39793,8 @@
         </is>
       </c>
       <c r="H808" t="inlineStr"/>
-      <c r="I808" t="inlineStr">
-        <is>
-          <t>5508009400044</t>
-        </is>
+      <c r="I808" t="n">
+        <v>5508009400044</v>
       </c>
       <c r="J808" t="inlineStr"/>
       <c r="K808" t="n">
@@ -39859,10 +39843,8 @@
         </is>
       </c>
       <c r="H809" t="inlineStr"/>
-      <c r="I809" t="inlineStr">
-        <is>
-          <t>5585991780463</t>
-        </is>
+      <c r="I809" t="n">
+        <v>5585991780463</v>
       </c>
       <c r="J809" t="inlineStr"/>
       <c r="K809" t="n">
@@ -39970,6 +39952,1554 @@
         </is>
       </c>
     </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Clínica Confiance</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>http://confiancemed.com.br</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr"/>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>556182022056</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr"/>
+      <c r="K812" t="n">
+        <v>75</v>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Centro Clinico Saint Moritz</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>https://centroclinicosaintmoritz.com.br</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr"/>
+      <c r="I813" t="inlineStr"/>
+      <c r="J813" t="inlineStr"/>
+      <c r="K813" t="n">
+        <v>80</v>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>Clínica CED</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>https://clinicaced.com</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr"/>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>5561991497434</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr"/>
+      <c r="K814" t="n">
+        <v>62</v>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Dr. Maurício Silva de Lemos Soares</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>https://www.clinicogeralbrasilia.com</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr"/>
+      <c r="I815" t="inlineStr"/>
+      <c r="J815" t="inlineStr"/>
+      <c r="K815" t="n">
+        <v>67</v>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Odonto Brasília</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>https://www.odontobrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr"/>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>5561985801610</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr"/>
+      <c r="K816" t="n">
+        <v>73</v>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Instituto de Psicologia Quality Vita</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>https://institutopsicologiaqualityvita.com</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr"/>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>5561999692026</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr"/>
+      <c r="K817" t="n">
+        <v>75</v>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Terapeuta para adolescentes</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>https://www.anabrigida.com.br</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr"/>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>5561992200973</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr"/>
+      <c r="K818" t="n">
+        <v>73</v>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>10 Melhores Advogados em Brasília</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>https://advocaciasbrasilia.com</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr"/>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>5561992510446</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr"/>
+      <c r="K819" t="n">
+        <v>55</v>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Advocacia Maciel</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>https://advocaciamaciel.adv.br</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr"/>
+      <c r="I820" t="inlineStr"/>
+      <c r="J820" t="inlineStr"/>
+      <c r="K820" t="n">
+        <v>55</v>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>Advogados Brasília</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>https://advogadosbrasiliadf.com.br</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr"/>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>5561981598841</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr"/>
+      <c r="K821" t="n">
+        <v>82</v>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Escritório de Advocacia em Brasília DF</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>https://teixeiraadvocacia.com</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr"/>
+      <c r="I822" t="inlineStr"/>
+      <c r="J822" t="inlineStr"/>
+      <c r="K822" t="n">
+        <v>55</v>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Faculdade de Educação Física (4 anos) em Brasília - DF</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>https://cursos.udf.edu.br</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr"/>
+      <c r="I823" t="inlineStr"/>
+      <c r="J823" t="inlineStr"/>
+      <c r="K823" t="n">
+        <v>44</v>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>https://www.uniplandf.edu.br</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr"/>
+      <c r="I824" t="inlineStr"/>
+      <c r="J824" t="inlineStr"/>
+      <c r="K824" t="n">
+        <v>81</v>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Curso de Educação Física</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>https://ucb.catolica.edu.br</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr"/>
+      <c r="I825" t="inlineStr"/>
+      <c r="J825" t="inlineStr"/>
+      <c r="K825" t="n">
+        <v>69</v>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>https://www.unieuro.edu.br</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr"/>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>556140425125</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr"/>
+      <c r="K826" t="n">
+        <v>73</v>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Academias/Esportes</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>https://www.sjpdf.org.br</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr"/>
+      <c r="I827" t="inlineStr"/>
+      <c r="J827" t="inlineStr"/>
+      <c r="K827" t="n">
+        <v>56</v>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Andrea Luiza Monteiro Fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>https://www.andreafisio.com</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr"/>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>5561998355130</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr"/>
+      <c r="K828" t="n">
+        <v>67</v>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Distrito Federal — Encontre Fisioterapeutas</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>https://www.portaldafisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr"/>
+      <c r="I829" t="inlineStr"/>
+      <c r="J829" t="inlineStr"/>
+      <c r="K829" t="n">
+        <v>88</v>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Dínamos</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>https://www.dinamos.com.br</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr"/>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>5561996766620</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr"/>
+      <c r="K830" t="n">
+        <v>80</v>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Brasília</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>https://ibrafisio.com.br</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr"/>
+      <c r="I831" t="inlineStr"/>
+      <c r="J831" t="inlineStr"/>
+      <c r="K831" t="n">
+        <v>69</v>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>SB Fisio</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>https://sbfisio.com.br</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr"/>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>5561994336620</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr"/>
+      <c r="K832" t="n">
+        <v>80</v>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>Clínica Médica no Setor Aeroporto</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>https://www.clinicasifam.com.br</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr"/>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>5562999340065</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr"/>
+      <c r="K833" t="n">
+        <v>75</v>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Página de Agendamento da Unidade do Acesso Saúde Goiânia</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>https://acessosaudegoiania.com.br</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr"/>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>556230863030</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr"/>
+      <c r="K834" t="n">
+        <v>80</v>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>https://conteudo.sesiesenaigoias.com.br</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr"/>
+      <c r="I835" t="inlineStr"/>
+      <c r="J835" t="inlineStr"/>
+      <c r="K835" t="n">
+        <v>22</v>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Goiânia Clínica</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>https://www.goianiaclinica.com.br</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr"/>
+      <c r="I836" t="inlineStr"/>
+      <c r="J836" t="inlineStr"/>
+      <c r="K836" t="n">
+        <v>50</v>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Quanto Cobra um Terapeuta Holístico em Goiânia...</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>https://www.freelasemcrise.com.br</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr"/>
+      <c r="I837" t="inlineStr"/>
+      <c r="J837" t="inlineStr"/>
+      <c r="K837" t="n">
+        <v>73</v>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Advogado Goiânia Escritório de Advocacia? Pimenta &amp; Oliveira</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>https://marcosoliveira.adv.br</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr"/>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>5562999675135</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr"/>
+      <c r="K838" t="n">
+        <v>64</v>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>FEFD</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>https://fef.ufg.br</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr"/>
+      <c r="I839" t="inlineStr"/>
+      <c r="J839" t="inlineStr"/>
+      <c r="K839" t="n">
+        <v>67</v>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Educação Física (Bacharelado)</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>https://www.uniceug.com.br</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr"/>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>5562998206942</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr"/>
+      <c r="K840" t="n">
+        <v>81</v>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>https://estudenaufg.prograd.ufg.br</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr"/>
+      <c r="I841" t="inlineStr"/>
+      <c r="J841" t="inlineStr"/>
+      <c r="K841" t="n">
+        <v>67</v>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Educação Física (Goiânia)</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>https://prograd.ufg.br</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr"/>
+      <c r="I842" t="inlineStr"/>
+      <c r="J842" t="inlineStr"/>
+      <c r="K842" t="n">
+        <v>69</v>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L842"/>
+  <dimension ref="A1:L866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39989,10 +39989,8 @@
         </is>
       </c>
       <c r="H812" t="inlineStr"/>
-      <c r="I812" t="inlineStr">
-        <is>
-          <t>556182022056</t>
-        </is>
+      <c r="I812" t="n">
+        <v>556182022056</v>
       </c>
       <c r="J812" t="inlineStr"/>
       <c r="K812" t="n">
@@ -40089,10 +40087,8 @@
         </is>
       </c>
       <c r="H814" t="inlineStr"/>
-      <c r="I814" t="inlineStr">
-        <is>
-          <t>5561991497434</t>
-        </is>
+      <c r="I814" t="n">
+        <v>5561991497434</v>
       </c>
       <c r="J814" t="inlineStr"/>
       <c r="K814" t="n">
@@ -40189,10 +40185,8 @@
         </is>
       </c>
       <c r="H816" t="inlineStr"/>
-      <c r="I816" t="inlineStr">
-        <is>
-          <t>5561985801610</t>
-        </is>
+      <c r="I816" t="n">
+        <v>5561985801610</v>
       </c>
       <c r="J816" t="inlineStr"/>
       <c r="K816" t="n">
@@ -40241,10 +40235,8 @@
         </is>
       </c>
       <c r="H817" t="inlineStr"/>
-      <c r="I817" t="inlineStr">
-        <is>
-          <t>5561999692026</t>
-        </is>
+      <c r="I817" t="n">
+        <v>5561999692026</v>
       </c>
       <c r="J817" t="inlineStr"/>
       <c r="K817" t="n">
@@ -40293,10 +40285,8 @@
         </is>
       </c>
       <c r="H818" t="inlineStr"/>
-      <c r="I818" t="inlineStr">
-        <is>
-          <t>5561992200973</t>
-        </is>
+      <c r="I818" t="n">
+        <v>5561992200973</v>
       </c>
       <c r="J818" t="inlineStr"/>
       <c r="K818" t="n">
@@ -40345,10 +40335,8 @@
         </is>
       </c>
       <c r="H819" t="inlineStr"/>
-      <c r="I819" t="inlineStr">
-        <is>
-          <t>5561992510446</t>
-        </is>
+      <c r="I819" t="n">
+        <v>5561992510446</v>
       </c>
       <c r="J819" t="inlineStr"/>
       <c r="K819" t="n">
@@ -40445,10 +40433,8 @@
         </is>
       </c>
       <c r="H821" t="inlineStr"/>
-      <c r="I821" t="inlineStr">
-        <is>
-          <t>5561981598841</t>
-        </is>
+      <c r="I821" t="n">
+        <v>5561981598841</v>
       </c>
       <c r="J821" t="inlineStr"/>
       <c r="K821" t="n">
@@ -40689,10 +40675,8 @@
         </is>
       </c>
       <c r="H826" t="inlineStr"/>
-      <c r="I826" t="inlineStr">
-        <is>
-          <t>556140425125</t>
-        </is>
+      <c r="I826" t="n">
+        <v>556140425125</v>
       </c>
       <c r="J826" t="inlineStr"/>
       <c r="K826" t="n">
@@ -40789,10 +40773,8 @@
         </is>
       </c>
       <c r="H828" t="inlineStr"/>
-      <c r="I828" t="inlineStr">
-        <is>
-          <t>5561998355130</t>
-        </is>
+      <c r="I828" t="n">
+        <v>5561998355130</v>
       </c>
       <c r="J828" t="inlineStr"/>
       <c r="K828" t="n">
@@ -40889,10 +40871,8 @@
         </is>
       </c>
       <c r="H830" t="inlineStr"/>
-      <c r="I830" t="inlineStr">
-        <is>
-          <t>5561996766620</t>
-        </is>
+      <c r="I830" t="n">
+        <v>5561996766620</v>
       </c>
       <c r="J830" t="inlineStr"/>
       <c r="K830" t="n">
@@ -40989,10 +40969,8 @@
         </is>
       </c>
       <c r="H832" t="inlineStr"/>
-      <c r="I832" t="inlineStr">
-        <is>
-          <t>5561994336620</t>
-        </is>
+      <c r="I832" t="n">
+        <v>5561994336620</v>
       </c>
       <c r="J832" t="inlineStr"/>
       <c r="K832" t="n">
@@ -41041,10 +41019,8 @@
         </is>
       </c>
       <c r="H833" t="inlineStr"/>
-      <c r="I833" t="inlineStr">
-        <is>
-          <t>5562999340065</t>
-        </is>
+      <c r="I833" t="n">
+        <v>5562999340065</v>
       </c>
       <c r="J833" t="inlineStr"/>
       <c r="K833" t="n">
@@ -41093,10 +41069,8 @@
         </is>
       </c>
       <c r="H834" t="inlineStr"/>
-      <c r="I834" t="inlineStr">
-        <is>
-          <t>556230863030</t>
-        </is>
+      <c r="I834" t="n">
+        <v>556230863030</v>
       </c>
       <c r="J834" t="inlineStr"/>
       <c r="K834" t="n">
@@ -41289,10 +41263,8 @@
         </is>
       </c>
       <c r="H838" t="inlineStr"/>
-      <c r="I838" t="inlineStr">
-        <is>
-          <t>5562999675135</t>
-        </is>
+      <c r="I838" t="n">
+        <v>5562999675135</v>
       </c>
       <c r="J838" t="inlineStr"/>
       <c r="K838" t="n">
@@ -41389,10 +41361,8 @@
         </is>
       </c>
       <c r="H840" t="inlineStr"/>
-      <c r="I840" t="inlineStr">
-        <is>
-          <t>5562998206942</t>
-        </is>
+      <c r="I840" t="n">
+        <v>5562998206942</v>
       </c>
       <c r="J840" t="inlineStr"/>
       <c r="K840" t="n">
@@ -41500,6 +41470,1182 @@
         </is>
       </c>
     </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>Você sabe o que faz um clínico médico? Especialista...</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>https://www.sitetribuna.com.br</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr"/>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>5573991987617</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr"/>
+      <c r="K843" t="n">
+        <v>22</v>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>Masioli Odontologia</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>https://masioliodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr"/>
+      <c r="I844" t="inlineStr"/>
+      <c r="J844" t="inlineStr"/>
+      <c r="K844" t="n">
+        <v>60</v>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>Psicólogo Online Particular</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>https://psicologaluanaamaral.com.br</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr"/>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>5519992289437</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr"/>
+      <c r="K845" t="n">
+        <v>73</v>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>Terapeuta em Jardim Camburi</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>https://www.portaljardimcamburi.com.br</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr"/>
+      <c r="I846" t="inlineStr"/>
+      <c r="J846" t="inlineStr"/>
+      <c r="K846" t="n">
+        <v>0</v>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Psicóloga e Psicoterapeuta em Vitoria ES</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>https://laizemonteiro.com.br</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr"/>
+      <c r="I847" t="inlineStr"/>
+      <c r="J847" t="inlineStr"/>
+      <c r="K847" t="n">
+        <v>69</v>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Advogados e Escritórios de Advocacia em Vitória</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>https://www.encontrabrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr"/>
+      <c r="I848" t="inlineStr"/>
+      <c r="J848" t="inlineStr"/>
+      <c r="K848" t="n">
+        <v>64</v>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>Hilton Rebello</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>https://www.hiltonrebello.com.br</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr"/>
+      <c r="I849" t="inlineStr"/>
+      <c r="J849" t="inlineStr"/>
+      <c r="K849" t="n">
+        <v>45</v>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>Advogados e Escritórios de Advocacia em Vitória</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>https://www.encontravitoria.com.br</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr"/>
+      <c r="I850" t="inlineStr"/>
+      <c r="J850" t="inlineStr"/>
+      <c r="K850" t="n">
+        <v>55</v>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>BKM Advogados</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>https://www.bkmadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr"/>
+      <c r="I851" t="inlineStr"/>
+      <c r="J851" t="inlineStr"/>
+      <c r="K851" t="n">
+        <v>64</v>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>Educação Física na Educação Infantil na rede pública de ensino da ...</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>http://educa.fcc.org.br</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr"/>
+      <c r="I852" t="inlineStr"/>
+      <c r="J852" t="inlineStr"/>
+      <c r="K852" t="n">
+        <v>67</v>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Goiabeiras</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>https://www.guiagoiabeiras.com.br</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr"/>
+      <c r="I853" t="inlineStr"/>
+      <c r="J853" t="inlineStr"/>
+      <c r="K853" t="n">
+        <v>0</v>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Os 10 melhores Dentistas em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>https://belo-horizonte.infoisinfo-br.com</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr"/>
+      <c r="I854" t="inlineStr"/>
+      <c r="J854" t="inlineStr"/>
+      <c r="K854" t="n">
+        <v>64</v>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Lorena Lustosa</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>https://www.lorenalustosa.com</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr"/>
+      <c r="I855" t="inlineStr"/>
+      <c r="J855" t="inlineStr"/>
+      <c r="K855" t="n">
+        <v>67</v>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Psicóloga Grasielle Silva</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>https://www.grasiellesilva.com.br</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr"/>
+      <c r="I856" t="inlineStr"/>
+      <c r="J856" t="inlineStr"/>
+      <c r="K856" t="n">
+        <v>80</v>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>Advogado em Belo Horizonte/MG</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>https://eduardoleonadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr"/>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>5531983866120</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr"/>
+      <c r="K857" t="n">
+        <v>73</v>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Hidroginástica em Belo Horizonte, Minas Gerais, MG</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>https://www.encontramg.com.br</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr"/>
+      <c r="I858" t="inlineStr"/>
+      <c r="J858" t="inlineStr"/>
+      <c r="K858" t="n">
+        <v>64</v>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Horizonte Saúde &amp; Bem-estar</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>https://www.horizontefisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr"/>
+      <c r="I859" t="inlineStr"/>
+      <c r="J859" t="inlineStr"/>
+      <c r="K859" t="n">
+        <v>60</v>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Fisioterapia Domiciliar em Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>https://ortopedia.clinicavicci.com.br</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr"/>
+      <c r="I860" t="inlineStr"/>
+      <c r="J860" t="inlineStr"/>
+      <c r="K860" t="n">
+        <v>60</v>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Clínica Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>https://www.clinicariodejaneiro.com.br</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr"/>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>5521976830437</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr"/>
+      <c r="K861" t="n">
+        <v>75</v>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Rio de Janeiro RJ (2026)</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>https://guiariodejaneirorj.com.br</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr"/>
+      <c r="I862" t="inlineStr"/>
+      <c r="J862" t="inlineStr"/>
+      <c r="K862" t="n">
+        <v>91</v>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Clínica Médica Rio de Janeiro, Avenida Getúlio de Moura, 1286 ...Clínica Rio de Janeiro: Marcação de Exames, Horário, En</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>https://www.findglocal.com</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr"/>
+      <c r="I863" t="inlineStr"/>
+      <c r="J863" t="inlineStr"/>
+      <c r="K863" t="n">
+        <v>33</v>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>Clínica Rio de Janeiro: Marcação de Exames, Horário, Endereço ...</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>https://www.encontrariodejaneiro.com.br</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr"/>
+      <c r="I864" t="inlineStr"/>
+      <c r="J864" t="inlineStr"/>
+      <c r="K864" t="n">
+        <v>55</v>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>https://alllab.com.br</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr"/>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>5521998952903</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr"/>
+      <c r="K865" t="n">
+        <v>71</v>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Clínica Life 360</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>https://clinicalife360.com.br</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr"/>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>5521999148969</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr"/>
+      <c r="K866" t="n">
+        <v>73</v>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L866"/>
+  <dimension ref="A1:L890"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41507,10 +41507,8 @@
         </is>
       </c>
       <c r="H843" t="inlineStr"/>
-      <c r="I843" t="inlineStr">
-        <is>
-          <t>5573991987617</t>
-        </is>
+      <c r="I843" t="n">
+        <v>5573991987617</v>
       </c>
       <c r="J843" t="inlineStr"/>
       <c r="K843" t="n">
@@ -41607,10 +41605,8 @@
         </is>
       </c>
       <c r="H845" t="inlineStr"/>
-      <c r="I845" t="inlineStr">
-        <is>
-          <t>5519992289437</t>
-        </is>
+      <c r="I845" t="n">
+        <v>5519992289437</v>
       </c>
       <c r="J845" t="inlineStr"/>
       <c r="K845" t="n">
@@ -42187,10 +42183,8 @@
         </is>
       </c>
       <c r="H857" t="inlineStr"/>
-      <c r="I857" t="inlineStr">
-        <is>
-          <t>5531983866120</t>
-        </is>
+      <c r="I857" t="n">
+        <v>5531983866120</v>
       </c>
       <c r="J857" t="inlineStr"/>
       <c r="K857" t="n">
@@ -42383,10 +42377,8 @@
         </is>
       </c>
       <c r="H861" t="inlineStr"/>
-      <c r="I861" t="inlineStr">
-        <is>
-          <t>5521976830437</t>
-        </is>
+      <c r="I861" t="n">
+        <v>5521976830437</v>
       </c>
       <c r="J861" t="inlineStr"/>
       <c r="K861" t="n">
@@ -42579,10 +42571,8 @@
         </is>
       </c>
       <c r="H865" t="inlineStr"/>
-      <c r="I865" t="inlineStr">
-        <is>
-          <t>5521998952903</t>
-        </is>
+      <c r="I865" t="n">
+        <v>5521998952903</v>
       </c>
       <c r="J865" t="inlineStr"/>
       <c r="K865" t="n">
@@ -42631,16 +42621,1222 @@
         </is>
       </c>
       <c r="H866" t="inlineStr"/>
-      <c r="I866" t="inlineStr">
-        <is>
-          <t>5521999148969</t>
-        </is>
+      <c r="I866" t="n">
+        <v>5521999148969</v>
       </c>
       <c r="J866" t="inlineStr"/>
       <c r="K866" t="n">
         <v>73</v>
       </c>
       <c r="L866" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Clínica Médica Doutor Agora Centro — Centro</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>https://www.imovelnaplantacuritiba.com.br</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr"/>
+      <c r="I867" t="inlineStr"/>
+      <c r="J867" t="inlineStr"/>
+      <c r="K867" t="n">
+        <v>56</v>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Asinelli Clinica Medica, Curitiba</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>https://www.doctuo.com.br</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr"/>
+      <c r="I868" t="inlineStr"/>
+      <c r="J868" t="inlineStr"/>
+      <c r="K868" t="n">
+        <v>81</v>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica Curitiba Instituto Kopp Odontologia</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>https://institutokopp.com.br</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr"/>
+      <c r="I869" t="inlineStr"/>
+      <c r="J869" t="inlineStr"/>
+      <c r="K869" t="n">
+        <v>87</v>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>Terapeuta Holístico Integrativo em Curitiba - Mesa Radiônica e Terapias Holísticas</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>https://therapistcwb.com.br</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr"/>
+      <c r="I870" t="inlineStr"/>
+      <c r="J870" t="inlineStr"/>
+      <c r="K870" t="n">
+        <v>0</v>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Academia Sesc Paraná</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>https://www.sescpr.com.br</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr"/>
+      <c r="I871" t="inlineStr"/>
+      <c r="J871" t="inlineStr"/>
+      <c r="K871" t="n">
+        <v>81</v>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Carpe Diem Academia // Na academia e na viva. // Curitiba</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>https://www.carpediemacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr"/>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>5541999712276</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr"/>
+      <c r="K872" t="n">
+        <v>80</v>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Fisioterapeutas em Curitiba</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>https://www.fisioterapias.com.br</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr"/>
+      <c r="I873" t="inlineStr"/>
+      <c r="J873" t="inlineStr"/>
+      <c r="K873" t="n">
+        <v>0</v>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Curitiba — RPG e Pilates</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>https://clinicaavanttos.com.br</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr"/>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>5541998500156</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr"/>
+      <c r="K874" t="n">
+        <v>62</v>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Dr. Marcelo Gonçalves Sade</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>https://www.marcelosadeosteopatia.com</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr"/>
+      <c r="I875" t="inlineStr"/>
+      <c r="J875" t="inlineStr"/>
+      <c r="K875" t="n">
+        <v>73</v>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Clínicas - MedCenter</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>https://www.medcenter.com.br</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr"/>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>5551998767319</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr"/>
+      <c r="K876" t="n">
+        <v>88</v>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>R+ Saúde</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>https://www.rmaissaude.poa.br</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr"/>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>5551993202379</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr"/>
+      <c r="K877" t="n">
+        <v>67</v>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>Dentista Zona Norte Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>https://www.heraodontologia.poa.br</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr"/>
+      <c r="I878" t="inlineStr"/>
+      <c r="J878" t="inlineStr"/>
+      <c r="K878" t="n">
+        <v>69</v>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>Academias em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>https://portoalegre.net.br</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr"/>
+      <c r="I879" t="inlineStr"/>
+      <c r="J879" t="inlineStr"/>
+      <c r="K879" t="n">
+        <v>82</v>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Academia Porto Alegre 26fit Vicente Fontoura • 26Fit</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>https://26fit.com.br</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr"/>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>555189142923</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr"/>
+      <c r="K880" t="n">
+        <v>67</v>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>https://www.fisiotres.com.br</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr"/>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>5551984836836</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr"/>
+      <c r="K881" t="n">
+        <v>67</v>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>Clinica de Fisioterapia Porto Alegre - (51) 3321-2577</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>https://www.physiomet.com.br</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr"/>
+      <c r="I882" t="inlineStr"/>
+      <c r="J882" t="inlineStr"/>
+      <c r="K882" t="n">
+        <v>69</v>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>FisioAbreu</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>https://www.fisioabreu.com.br</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr"/>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>5551998405015</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr"/>
+      <c r="K883" t="n">
+        <v>73</v>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>Clínica de Reabilitação Física em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>https://medfisio.net</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr"/>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>5551997776618</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr"/>
+      <c r="K884" t="n">
+        <v>73</v>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>https://clinicafysioviver.com.br</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr"/>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>555132270378</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr"/>
+      <c r="K885" t="n">
+        <v>56</v>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>Fisioterapia especializada em Traumato Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>https://fisioespecializada.com.br</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr"/>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>5551996643344</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr"/>
+      <c r="K886" t="n">
+        <v>80</v>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Clínica Médica Florianópolis, Palhoça e Tubarão</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>https://icamed.com.br</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr"/>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>5548999149672</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr"/>
+      <c r="K887" t="n">
+        <v>81</v>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>Florianópolis Clínicas</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>https://florianopolisclinicas.com.br</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr"/>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>554839524000</t>
+        </is>
+      </c>
+      <c r="J888" t="inlineStr"/>
+      <c r="K888" t="n">
+        <v>73</v>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Clínica Médica Multidisciplinar em Florianópolis</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>https://clinifemina.com.br</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr"/>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>554832233031</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr"/>
+      <c r="K889" t="n">
+        <v>88</v>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Clínica Médica Saúde Popular</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>https://clinicamedicasaudepopular.com.br</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr"/>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>5548998655296</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr"/>
+      <c r="K890" t="n">
+        <v>67</v>
+      </c>
+      <c r="L890" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L890"/>
+  <dimension ref="A1:L909"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42911,10 +42911,8 @@
         </is>
       </c>
       <c r="H872" t="inlineStr"/>
-      <c r="I872" t="inlineStr">
-        <is>
-          <t>5541999712276</t>
-        </is>
+      <c r="I872" t="n">
+        <v>5541999712276</v>
       </c>
       <c r="J872" t="inlineStr"/>
       <c r="K872" t="n">
@@ -43011,10 +43009,8 @@
         </is>
       </c>
       <c r="H874" t="inlineStr"/>
-      <c r="I874" t="inlineStr">
-        <is>
-          <t>5541998500156</t>
-        </is>
+      <c r="I874" t="n">
+        <v>5541998500156</v>
       </c>
       <c r="J874" t="inlineStr"/>
       <c r="K874" t="n">
@@ -43111,10 +43107,8 @@
         </is>
       </c>
       <c r="H876" t="inlineStr"/>
-      <c r="I876" t="inlineStr">
-        <is>
-          <t>5551998767319</t>
-        </is>
+      <c r="I876" t="n">
+        <v>5551998767319</v>
       </c>
       <c r="J876" t="inlineStr"/>
       <c r="K876" t="n">
@@ -43163,10 +43157,8 @@
         </is>
       </c>
       <c r="H877" t="inlineStr"/>
-      <c r="I877" t="inlineStr">
-        <is>
-          <t>5551993202379</t>
-        </is>
+      <c r="I877" t="n">
+        <v>5551993202379</v>
       </c>
       <c r="J877" t="inlineStr"/>
       <c r="K877" t="n">
@@ -43311,10 +43303,8 @@
         </is>
       </c>
       <c r="H880" t="inlineStr"/>
-      <c r="I880" t="inlineStr">
-        <is>
-          <t>555189142923</t>
-        </is>
+      <c r="I880" t="n">
+        <v>555189142923</v>
       </c>
       <c r="J880" t="inlineStr"/>
       <c r="K880" t="n">
@@ -43363,10 +43353,8 @@
         </is>
       </c>
       <c r="H881" t="inlineStr"/>
-      <c r="I881" t="inlineStr">
-        <is>
-          <t>5551984836836</t>
-        </is>
+      <c r="I881" t="n">
+        <v>5551984836836</v>
       </c>
       <c r="J881" t="inlineStr"/>
       <c r="K881" t="n">
@@ -43463,10 +43451,8 @@
         </is>
       </c>
       <c r="H883" t="inlineStr"/>
-      <c r="I883" t="inlineStr">
-        <is>
-          <t>5551998405015</t>
-        </is>
+      <c r="I883" t="n">
+        <v>5551998405015</v>
       </c>
       <c r="J883" t="inlineStr"/>
       <c r="K883" t="n">
@@ -43515,10 +43501,8 @@
         </is>
       </c>
       <c r="H884" t="inlineStr"/>
-      <c r="I884" t="inlineStr">
-        <is>
-          <t>5551997776618</t>
-        </is>
+      <c r="I884" t="n">
+        <v>5551997776618</v>
       </c>
       <c r="J884" t="inlineStr"/>
       <c r="K884" t="n">
@@ -43567,10 +43551,8 @@
         </is>
       </c>
       <c r="H885" t="inlineStr"/>
-      <c r="I885" t="inlineStr">
-        <is>
-          <t>555132270378</t>
-        </is>
+      <c r="I885" t="n">
+        <v>555132270378</v>
       </c>
       <c r="J885" t="inlineStr"/>
       <c r="K885" t="n">
@@ -43619,10 +43601,8 @@
         </is>
       </c>
       <c r="H886" t="inlineStr"/>
-      <c r="I886" t="inlineStr">
-        <is>
-          <t>5551996643344</t>
-        </is>
+      <c r="I886" t="n">
+        <v>5551996643344</v>
       </c>
       <c r="J886" t="inlineStr"/>
       <c r="K886" t="n">
@@ -43671,10 +43651,8 @@
         </is>
       </c>
       <c r="H887" t="inlineStr"/>
-      <c r="I887" t="inlineStr">
-        <is>
-          <t>5548999149672</t>
-        </is>
+      <c r="I887" t="n">
+        <v>5548999149672</v>
       </c>
       <c r="J887" t="inlineStr"/>
       <c r="K887" t="n">
@@ -43723,10 +43701,8 @@
         </is>
       </c>
       <c r="H888" t="inlineStr"/>
-      <c r="I888" t="inlineStr">
-        <is>
-          <t>554839524000</t>
-        </is>
+      <c r="I888" t="n">
+        <v>554839524000</v>
       </c>
       <c r="J888" t="inlineStr"/>
       <c r="K888" t="n">
@@ -43775,10 +43751,8 @@
         </is>
       </c>
       <c r="H889" t="inlineStr"/>
-      <c r="I889" t="inlineStr">
-        <is>
-          <t>554832233031</t>
-        </is>
+      <c r="I889" t="n">
+        <v>554832233031</v>
       </c>
       <c r="J889" t="inlineStr"/>
       <c r="K889" t="n">
@@ -43827,16 +43801,938 @@
         </is>
       </c>
       <c r="H890" t="inlineStr"/>
-      <c r="I890" t="inlineStr">
-        <is>
-          <t>5548998655296</t>
-        </is>
+      <c r="I890" t="n">
+        <v>5548998655296</v>
       </c>
       <c r="J890" t="inlineStr"/>
       <c r="K890" t="n">
         <v>67</v>
       </c>
       <c r="L890" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>Guia Médico de Prestadores de Saúde em Rio Branco</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>https://clinica101.com.br</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr"/>
+      <c r="I891" t="inlineStr"/>
+      <c r="J891" t="inlineStr"/>
+      <c r="K891" t="n">
+        <v>81</v>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>Guia Médico Unimed Rio Branco 2025</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>https://pt.scribd.com</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr"/>
+      <c r="I892" t="inlineStr"/>
+      <c r="J892" t="inlineStr"/>
+      <c r="K892" t="n">
+        <v>40</v>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Psicólogo em Rio Branco</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>https://ciceraalvespsicologa.com</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr"/>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>5574981542389</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr"/>
+      <c r="K893" t="n">
+        <v>73</v>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>Vaga ago/26: Acompanhamento de audiência em Rio Branco (AC)...</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>https://radar.juriscorrespondente.com.br</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr"/>
+      <c r="I894" t="inlineStr"/>
+      <c r="J894" t="inlineStr"/>
+      <c r="K894" t="n">
+        <v>45</v>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>Academias em Rio Branco, AC</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>https://www.guiamais.com.br</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr"/>
+      <c r="I895" t="inlineStr"/>
+      <c r="J895" t="inlineStr"/>
+      <c r="K895" t="n">
+        <v>100</v>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Rio Branco</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>https://fisio.net.br</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr"/>
+      <c r="I896" t="inlineStr"/>
+      <c r="J896" t="inlineStr"/>
+      <c r="K896" t="n">
+        <v>88</v>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>Buscar: em macapa ap guiareunimedicos.med.br - Catálogo Médico</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>https://www.guiareunimedicos.med.br</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr"/>
+      <c r="I897" t="inlineStr"/>
+      <c r="J897" t="inlineStr"/>
+      <c r="K897" t="n">
+        <v>62</v>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>Dentista em Macapá</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>https://clinicaperfetha.com.br</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr"/>
+      <c r="I898" t="inlineStr"/>
+      <c r="J898" t="inlineStr"/>
+      <c r="K898" t="n">
+        <v>0</v>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>Dentistas em Macapá 【262 empresas】</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>https://dentistaspertodemim.com</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr"/>
+      <c r="I899" t="inlineStr"/>
+      <c r="J899" t="inlineStr"/>
+      <c r="K899" t="n">
+        <v>87</v>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Mayk Camelo Advogados</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>https://maykcameloadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr"/>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>559681072847</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr"/>
+      <c r="K900" t="n">
+        <v>73</v>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>Conselho Seccional</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>https://deoab.oab.org.br</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr"/>
+      <c r="I901" t="inlineStr"/>
+      <c r="J901" t="inlineStr"/>
+      <c r="K901" t="n">
+        <v>45</v>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>Academias em Macapá, AP</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>https://www.solutudo.com.br</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr"/>
+      <c r="I902" t="inlineStr"/>
+      <c r="J902" t="inlineStr"/>
+      <c r="K902" t="n">
+        <v>33</v>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>CMM- Clínica Médica Manaus</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>https://cmm-clinica-medica.localo.site</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr"/>
+      <c r="I903" t="inlineStr"/>
+      <c r="J903" t="inlineStr"/>
+      <c r="K903" t="n">
+        <v>80</v>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Dentista em Manaus - AM</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>https://rankodonto.com.br</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr"/>
+      <c r="I904" t="inlineStr"/>
+      <c r="J904" t="inlineStr"/>
+      <c r="K904" t="n">
+        <v>60</v>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>Dentista em Manaus, AM</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>https://guiapinzon.com.br</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr"/>
+      <c r="I905" t="inlineStr"/>
+      <c r="J905" t="inlineStr"/>
+      <c r="K905" t="n">
+        <v>56</v>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Psicólogo em Manaus</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>https://www.clinicadosentido.com</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr"/>
+      <c r="I906" t="inlineStr"/>
+      <c r="J906" t="inlineStr"/>
+      <c r="K906" t="n">
+        <v>80</v>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>TERAPEUTA JANYMASSAG Formada em terapia tantrica...</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>https://br.skokka.com</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr"/>
+      <c r="I907" t="inlineStr"/>
+      <c r="J907" t="inlineStr"/>
+      <c r="K907" t="n">
+        <v>33</v>
+      </c>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Manaus/AM abre concurso para Professor de Educação Física</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>https://concursosedfisica.com</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr"/>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>5585999458789</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr"/>
+      <c r="K908" t="n">
+        <v>56</v>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Formação continuada de professores de Educação Física em...</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>https://periodicos.sbu.unicamp.br</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr"/>
+      <c r="I909" t="inlineStr"/>
+      <c r="J909" t="inlineStr"/>
+      <c r="K909" t="n">
+        <v>73</v>
+      </c>
+      <c r="L909" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L909"/>
+  <dimension ref="A1:L922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43947,10 +43947,8 @@
         </is>
       </c>
       <c r="H893" t="inlineStr"/>
-      <c r="I893" t="inlineStr">
-        <is>
-          <t>5574981542389</t>
-        </is>
+      <c r="I893" t="n">
+        <v>5574981542389</v>
       </c>
       <c r="J893" t="inlineStr"/>
       <c r="K893" t="n">
@@ -44287,10 +44285,8 @@
         </is>
       </c>
       <c r="H900" t="inlineStr"/>
-      <c r="I900" t="inlineStr">
-        <is>
-          <t>559681072847</t>
-        </is>
+      <c r="I900" t="n">
+        <v>559681072847</v>
       </c>
       <c r="J900" t="inlineStr"/>
       <c r="K900" t="n">
@@ -44675,10 +44671,8 @@
         </is>
       </c>
       <c r="H908" t="inlineStr"/>
-      <c r="I908" t="inlineStr">
-        <is>
-          <t>5585999458789</t>
-        </is>
+      <c r="I908" t="n">
+        <v>5585999458789</v>
       </c>
       <c r="J908" t="inlineStr"/>
       <c r="K908" t="n">
@@ -44738,6 +44732,650 @@
         </is>
       </c>
     </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Agenda do Terapeuta Eliete Oliveira</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>https://unimasso.com.br</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr"/>
+      <c r="I910" t="inlineStr"/>
+      <c r="J910" t="inlineStr"/>
+      <c r="K910" t="n">
+        <v>33</v>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Guia Completo de Clínicas médicas em Salvador</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>https://alisaude.com.br</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr"/>
+      <c r="I911" t="inlineStr"/>
+      <c r="J911" t="inlineStr"/>
+      <c r="K911" t="n">
+        <v>76</v>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Clínica</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>https://www.clinicavistar.com</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr"/>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>5571982373780</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr"/>
+      <c r="K912" t="n">
+        <v>70</v>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>Clinicas em Salvador</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>https://www.centromedicobelavista.com.br</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr"/>
+      <c r="I913" t="inlineStr"/>
+      <c r="J913" t="inlineStr"/>
+      <c r="K913" t="n">
+        <v>70</v>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Seta Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>https://clinicasetabahia.com.br</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr"/>
+      <c r="I914" t="inlineStr"/>
+      <c r="J914" t="inlineStr"/>
+      <c r="K914" t="n">
+        <v>73</v>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Hospitais e Clínicas : Salvador, Bahia</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>https://salvador-ba.brasil-infos.com</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr"/>
+      <c r="I915" t="inlineStr"/>
+      <c r="J915" t="inlineStr"/>
+      <c r="K915" t="n">
+        <v>81</v>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Clínica Angiclin</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>https://angiclin.com.br</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr"/>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>5571999241313</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr"/>
+      <c r="K916" t="n">
+        <v>73</v>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>Leonardo Saldanha</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>https://leonardosaldanha.com.br</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr"/>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>5571996902910</t>
+        </is>
+      </c>
+      <c r="J917" t="inlineStr"/>
+      <c r="K917" t="n">
+        <v>73</v>
+      </c>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>Guia de Massoterapeuta Massagista e Massagens</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>https://relaxzen.com.br</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr"/>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>5571981547350</t>
+        </is>
+      </c>
+      <c r="J918" t="inlineStr"/>
+      <c r="K918" t="n">
+        <v>81</v>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>Advogado Salvador Bahia Advogado Especialista em Acidente de...</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>https://www.onaldo.com.br</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr"/>
+      <c r="I919" t="inlineStr"/>
+      <c r="J919" t="inlineStr"/>
+      <c r="K919" t="n">
+        <v>55</v>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>Academias em 3849, BA Em atividade há 23 anos.</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>https://anunce.com</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr"/>
+      <c r="I920" t="inlineStr"/>
+      <c r="J920" t="inlineStr"/>
+      <c r="K920" t="n">
+        <v>33</v>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Première Medicina e Saúde Fortaleza |</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>https://premieremedicina.com.br</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr"/>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>558537713180</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr"/>
+      <c r="K921" t="n">
+        <v>76</v>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>Dentista 24 Horas em Fortaleza</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>https://dentistafortaleza.net</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr"/>
+      <c r="I922" t="inlineStr"/>
+      <c r="J922" t="inlineStr"/>
+      <c r="K922" t="n">
+        <v>60</v>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L922"/>
+  <dimension ref="A1:L936"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44865,10 +44865,8 @@
         </is>
       </c>
       <c r="H912" t="inlineStr"/>
-      <c r="I912" t="inlineStr">
-        <is>
-          <t>5571982373780</t>
-        </is>
+      <c r="I912" t="n">
+        <v>5571982373780</v>
       </c>
       <c r="J912" t="inlineStr"/>
       <c r="K912" t="n">
@@ -45061,10 +45059,8 @@
         </is>
       </c>
       <c r="H916" t="inlineStr"/>
-      <c r="I916" t="inlineStr">
-        <is>
-          <t>5571999241313</t>
-        </is>
+      <c r="I916" t="n">
+        <v>5571999241313</v>
       </c>
       <c r="J916" t="inlineStr"/>
       <c r="K916" t="n">
@@ -45113,10 +45109,8 @@
         </is>
       </c>
       <c r="H917" t="inlineStr"/>
-      <c r="I917" t="inlineStr">
-        <is>
-          <t>5571996902910</t>
-        </is>
+      <c r="I917" t="n">
+        <v>5571996902910</v>
       </c>
       <c r="J917" t="inlineStr"/>
       <c r="K917" t="n">
@@ -45165,10 +45159,8 @@
         </is>
       </c>
       <c r="H918" t="inlineStr"/>
-      <c r="I918" t="inlineStr">
-        <is>
-          <t>5571981547350</t>
-        </is>
+      <c r="I918" t="n">
+        <v>5571981547350</v>
       </c>
       <c r="J918" t="inlineStr"/>
       <c r="K918" t="n">
@@ -45313,10 +45305,8 @@
         </is>
       </c>
       <c r="H921" t="inlineStr"/>
-      <c r="I921" t="inlineStr">
-        <is>
-          <t>558537713180</t>
-        </is>
+      <c r="I921" t="n">
+        <v>558537713180</v>
       </c>
       <c r="J921" t="inlineStr"/>
       <c r="K921" t="n">
@@ -45376,6 +45366,706 @@
         </is>
       </c>
     </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>Clinicordis Brasília</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>https://clinicordisbrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr"/>
+      <c r="I923" t="inlineStr"/>
+      <c r="J923" t="inlineStr"/>
+      <c r="K923" t="n">
+        <v>76</v>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Psicólogo em Brasília - Clínica Brasília de Psicologia ...Clínica Diálogo – Psicologia em BrasíliaConselho Regional de P</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>https://www.cbrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr"/>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>5561998855556</t>
+        </is>
+      </c>
+      <c r="J924" t="inlineStr"/>
+      <c r="K924" t="n">
+        <v>60</v>
+      </c>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Escola de Psicanálise de Brasília</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>https://escoladepsicanalisedebrasilia.com</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr"/>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>5561996576062</t>
+        </is>
+      </c>
+      <c r="J925" t="inlineStr"/>
+      <c r="K925" t="n">
+        <v>62</v>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>62 ideias de Advogado Condominial e Imobiliário Brasília DF</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>https://es.pinterest.com</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr"/>
+      <c r="I926" t="inlineStr"/>
+      <c r="J926" t="inlineStr"/>
+      <c r="K926" t="n">
+        <v>56</v>
+      </c>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>Advocacia em Brasília</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>https://www.msbadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr"/>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>5561991340595</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr"/>
+      <c r="K927" t="n">
+        <v>82</v>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>CREF7/DF</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>https://www.cref7.org.br</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr"/>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>556137714061</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr"/>
+      <c r="K928" t="n">
+        <v>80</v>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>https://www.uniceub.br</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr"/>
+      <c r="I929" t="inlineStr"/>
+      <c r="J929" t="inlineStr"/>
+      <c r="K929" t="n">
+        <v>0</v>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>Academias em Brasília - Diretório fitness</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>https://gymbrasilia.com</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr"/>
+      <c r="I930" t="inlineStr"/>
+      <c r="J930" t="inlineStr"/>
+      <c r="K930" t="n">
+        <v>70</v>
+      </c>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>Clínica médica em Goiânia</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>https://www.clinicasalve.com.br</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr"/>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>556236372773</t>
+        </is>
+      </c>
+      <c r="J931" t="inlineStr"/>
+      <c r="K931" t="n">
+        <v>67</v>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Dr. Regis Augusto Aleixo Alves</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>https://www.drregisaugustoaleixoalves.com</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr"/>
+      <c r="I932" t="inlineStr"/>
+      <c r="J932" t="inlineStr"/>
+      <c r="K932" t="n">
+        <v>73</v>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Bruno Aernoudts — Psicologia</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>https://psicologobrunoaernoudts.com.br</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr"/>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>5564999878711</t>
+        </is>
+      </c>
+      <c r="J933" t="inlineStr"/>
+      <c r="K933" t="n">
+        <v>80</v>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>Advogado em Goiânia</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>https://arthursantiagoadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr"/>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>5562986421050</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr"/>
+      <c r="K934" t="n">
+        <v>91</v>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>Advogados e Escritórios de Advocacia em Goiânia</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>https://www.encontragoiania.com.br</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr"/>
+      <c r="I935" t="inlineStr"/>
+      <c r="J935" t="inlineStr"/>
+      <c r="K935" t="n">
+        <v>55</v>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>(PDF) Educação Física Na Atenção Básica Do Sus: Revisão Integrativa</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>https://www.academia.edu</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr"/>
+      <c r="I936" t="inlineStr"/>
+      <c r="J936" t="inlineStr"/>
+      <c r="K936" t="n">
+        <v>30</v>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L936"/>
+  <dimension ref="A1:L944"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45451,10 +45451,8 @@
         </is>
       </c>
       <c r="H924" t="inlineStr"/>
-      <c r="I924" t="inlineStr">
-        <is>
-          <t>5561998855556</t>
-        </is>
+      <c r="I924" t="n">
+        <v>5561998855556</v>
       </c>
       <c r="J924" t="inlineStr"/>
       <c r="K924" t="n">
@@ -45503,10 +45501,8 @@
         </is>
       </c>
       <c r="H925" t="inlineStr"/>
-      <c r="I925" t="inlineStr">
-        <is>
-          <t>5561996576062</t>
-        </is>
+      <c r="I925" t="n">
+        <v>5561996576062</v>
       </c>
       <c r="J925" t="inlineStr"/>
       <c r="K925" t="n">
@@ -45603,10 +45599,8 @@
         </is>
       </c>
       <c r="H927" t="inlineStr"/>
-      <c r="I927" t="inlineStr">
-        <is>
-          <t>5561991340595</t>
-        </is>
+      <c r="I927" t="n">
+        <v>5561991340595</v>
       </c>
       <c r="J927" t="inlineStr"/>
       <c r="K927" t="n">
@@ -45655,10 +45649,8 @@
         </is>
       </c>
       <c r="H928" t="inlineStr"/>
-      <c r="I928" t="inlineStr">
-        <is>
-          <t>556137714061</t>
-        </is>
+      <c r="I928" t="n">
+        <v>556137714061</v>
       </c>
       <c r="J928" t="inlineStr"/>
       <c r="K928" t="n">
@@ -45803,10 +45795,8 @@
         </is>
       </c>
       <c r="H931" t="inlineStr"/>
-      <c r="I931" t="inlineStr">
-        <is>
-          <t>556236372773</t>
-        </is>
+      <c r="I931" t="n">
+        <v>556236372773</v>
       </c>
       <c r="J931" t="inlineStr"/>
       <c r="K931" t="n">
@@ -45903,10 +45893,8 @@
         </is>
       </c>
       <c r="H933" t="inlineStr"/>
-      <c r="I933" t="inlineStr">
-        <is>
-          <t>5564999878711</t>
-        </is>
+      <c r="I933" t="n">
+        <v>5564999878711</v>
       </c>
       <c r="J933" t="inlineStr"/>
       <c r="K933" t="n">
@@ -45955,10 +45943,8 @@
         </is>
       </c>
       <c r="H934" t="inlineStr"/>
-      <c r="I934" t="inlineStr">
-        <is>
-          <t>5562986421050</t>
-        </is>
+      <c r="I934" t="n">
+        <v>5562986421050</v>
       </c>
       <c r="J934" t="inlineStr"/>
       <c r="K934" t="n">
@@ -46066,6 +46052,402 @@
         </is>
       </c>
     </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>Dentistas de VITÓRIA</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>https://odonto101.com.br</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr"/>
+      <c r="I937" t="inlineStr"/>
+      <c r="J937" t="inlineStr"/>
+      <c r="K937" t="n">
+        <v>73</v>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>Objetivos da fisioterapia</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>https://www.agorasudoeste.com.br</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr"/>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>5577999923542</t>
+        </is>
+      </c>
+      <c r="J938" t="inlineStr"/>
+      <c r="K938" t="n">
+        <v>90</v>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta em Vitória das Missões</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>https://fitlocal.com.br</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr"/>
+      <c r="I939" t="inlineStr"/>
+      <c r="J939" t="inlineStr"/>
+      <c r="K939" t="n">
+        <v>90</v>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>Benefícios Surpreendentes do tratamento com Ventosaterapia...</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>https://www.flfisio.site</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr"/>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>5527988065756</t>
+        </is>
+      </c>
+      <c r="J940" t="inlineStr"/>
+      <c r="K940" t="n">
+        <v>67</v>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>Clínica Santa Amélia</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>https://www.clinicasantaamelia.com.br</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr"/>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>553184239022</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr"/>
+      <c r="K941" t="n">
+        <v>65</v>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>UniclínicaBH</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>https://uniclinicabh.com.br</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr"/>
+      <c r="I942" t="inlineStr"/>
+      <c r="J942" t="inlineStr"/>
+      <c r="K942" t="n">
+        <v>67</v>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta em Belo Horizonte, MG</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>https://uworkpro.com</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr"/>
+      <c r="I943" t="inlineStr"/>
+      <c r="J943" t="inlineStr"/>
+      <c r="K943" t="n">
+        <v>44</v>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>Centro Médico Pastore</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>https://www.centromedicopastore.com.br</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr"/>
+      <c r="I944" t="inlineStr"/>
+      <c r="J944" t="inlineStr"/>
+      <c r="K944" t="n">
+        <v>33</v>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L944"/>
+  <dimension ref="A1:L955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46137,10 +46137,8 @@
         </is>
       </c>
       <c r="H938" t="inlineStr"/>
-      <c r="I938" t="inlineStr">
-        <is>
-          <t>5577999923542</t>
-        </is>
+      <c r="I938" t="n">
+        <v>5577999923542</v>
       </c>
       <c r="J938" t="inlineStr"/>
       <c r="K938" t="n">
@@ -46237,10 +46235,8 @@
         </is>
       </c>
       <c r="H940" t="inlineStr"/>
-      <c r="I940" t="inlineStr">
-        <is>
-          <t>5527988065756</t>
-        </is>
+      <c r="I940" t="n">
+        <v>5527988065756</v>
       </c>
       <c r="J940" t="inlineStr"/>
       <c r="K940" t="n">
@@ -46289,10 +46285,8 @@
         </is>
       </c>
       <c r="H941" t="inlineStr"/>
-      <c r="I941" t="inlineStr">
-        <is>
-          <t>553184239022</t>
-        </is>
+      <c r="I941" t="n">
+        <v>553184239022</v>
       </c>
       <c r="J941" t="inlineStr"/>
       <c r="K941" t="n">
@@ -46448,6 +46442,554 @@
         </is>
       </c>
     </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>https://clinicacastell.com.br</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr"/>
+      <c r="I945" t="inlineStr"/>
+      <c r="J945" t="inlineStr"/>
+      <c r="K945" t="n">
+        <v>80</v>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>Douglas Raimondi</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>https://douglasraimondi.com.br</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr"/>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>5547992745563</t>
+        </is>
+      </c>
+      <c r="J946" t="inlineStr"/>
+      <c r="K946" t="n">
+        <v>69</v>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>Academias em Curitiba, Paraná, PR</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>https://www.encontrapr.com.br</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr"/>
+      <c r="I947" t="inlineStr"/>
+      <c r="J947" t="inlineStr"/>
+      <c r="K947" t="n">
+        <v>33</v>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>iSaúde Clínica Particular + Acessível</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>https://isaude.med.br</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr"/>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>555130131110</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr"/>
+      <c r="K948" t="n">
+        <v>75</v>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>Psicólogo Felipe Kruse</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>https://www.felipekrusepsicologo.com.br</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr"/>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>5551998081317</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr"/>
+      <c r="K949" t="n">
+        <v>80</v>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>Psicólogo Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>https://psicologovaguenir.com.br</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr"/>
+      <c r="I950" t="inlineStr"/>
+      <c r="J950" t="inlineStr"/>
+      <c r="K950" t="n">
+        <v>60</v>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>Bacharelado em Educação Física</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>https://www.fadergs.edu.br</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr"/>
+      <c r="I951" t="inlineStr"/>
+      <c r="J951" t="inlineStr"/>
+      <c r="K951" t="n">
+        <v>62</v>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>As 10 melhores Academias em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>https://porto-alegre.infoisinfo-br.com</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr"/>
+      <c r="I952" t="inlineStr"/>
+      <c r="J952" t="inlineStr"/>
+      <c r="K952" t="n">
+        <v>64</v>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>Academia Sportcenter Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>https://www.academiasportcenter.com.br</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr"/>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>5551982690040</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr"/>
+      <c r="K953" t="n">
+        <v>70</v>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>Academia do Bairro</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>https://www.novaacademiadobairro.com.br</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr"/>
+      <c r="I954" t="inlineStr"/>
+      <c r="J954" t="inlineStr"/>
+      <c r="K954" t="n">
+        <v>70</v>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>[RED CULTURE] [MOINHOS FITNESS]</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>https://www.moinhosfitness.com.br</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr"/>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>5551994024624</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr"/>
+      <c r="K955" t="n">
+        <v>70</v>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L955"/>
+  <dimension ref="A1:L970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46527,10 +46527,8 @@
         </is>
       </c>
       <c r="H946" t="inlineStr"/>
-      <c r="I946" t="inlineStr">
-        <is>
-          <t>5547992745563</t>
-        </is>
+      <c r="I946" t="n">
+        <v>5547992745563</v>
       </c>
       <c r="J946" t="inlineStr"/>
       <c r="K946" t="n">
@@ -46627,10 +46625,8 @@
         </is>
       </c>
       <c r="H948" t="inlineStr"/>
-      <c r="I948" t="inlineStr">
-        <is>
-          <t>555130131110</t>
-        </is>
+      <c r="I948" t="n">
+        <v>555130131110</v>
       </c>
       <c r="J948" t="inlineStr"/>
       <c r="K948" t="n">
@@ -46679,10 +46675,8 @@
         </is>
       </c>
       <c r="H949" t="inlineStr"/>
-      <c r="I949" t="inlineStr">
-        <is>
-          <t>5551998081317</t>
-        </is>
+      <c r="I949" t="n">
+        <v>5551998081317</v>
       </c>
       <c r="J949" t="inlineStr"/>
       <c r="K949" t="n">
@@ -46875,10 +46869,8 @@
         </is>
       </c>
       <c r="H953" t="inlineStr"/>
-      <c r="I953" t="inlineStr">
-        <is>
-          <t>5551982690040</t>
-        </is>
+      <c r="I953" t="n">
+        <v>5551982690040</v>
       </c>
       <c r="J953" t="inlineStr"/>
       <c r="K953" t="n">
@@ -46975,10 +46967,8 @@
         </is>
       </c>
       <c r="H955" t="inlineStr"/>
-      <c r="I955" t="inlineStr">
-        <is>
-          <t>5551994024624</t>
-        </is>
+      <c r="I955" t="n">
+        <v>5551994024624</v>
       </c>
       <c r="J955" t="inlineStr"/>
       <c r="K955" t="n">
@@ -46987,6 +46977,754 @@
       <c r="L955" t="inlineStr">
         <is>
           <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>Os 5 melhores Psicólogos em Rio Branco</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>https://rio-branco.infoisinfo-br.com</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr"/>
+      <c r="I956" t="inlineStr"/>
+      <c r="J956" t="inlineStr"/>
+      <c r="K956" t="n">
+        <v>64</v>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>Maris</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>https://www.marispsicologia.com</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr"/>
+      <c r="I957" t="inlineStr"/>
+      <c r="J957" t="inlineStr"/>
+      <c r="K957" t="n">
+        <v>80</v>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>https://itamazonia.com.br</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr"/>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>5568999787806</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr"/>
+      <c r="K958" t="n">
+        <v>88</v>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>TABELA DE CONVÊNIOS ACADEMIA DESCONTO POWER ...</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>https://www.oabac.org.br</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr"/>
+      <c r="I959" t="inlineStr"/>
+      <c r="J959" t="inlineStr"/>
+      <c r="K959" t="n">
+        <v>22</v>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>ABL celebra os 80 anos do Instituto Rio Branco</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>https://www.academia.org.br</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr"/>
+      <c r="I960" t="inlineStr"/>
+      <c r="J960" t="inlineStr"/>
+      <c r="K960" t="n">
+        <v>80</v>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>Centerclin Odontologia</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>https://www.centerclinsaude.com.br</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr"/>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>5596999050219</t>
+        </is>
+      </c>
+      <c r="J961" t="inlineStr"/>
+      <c r="K961" t="n">
+        <v>53</v>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Macapá</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>https://www.encontramacapa.com.br</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr"/>
+      <c r="I962" t="inlineStr"/>
+      <c r="J962" t="inlineStr"/>
+      <c r="K962" t="n">
+        <v>64</v>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>Psicólogo em Manaus</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>https://www.clinicadosentido.com.br</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr"/>
+      <c r="I963" t="inlineStr"/>
+      <c r="J963" t="inlineStr"/>
+      <c r="K963" t="n">
+        <v>80</v>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>Psicologia</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>https://www.psicologia.espmais.com.br</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr"/>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>5592992249046</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr"/>
+      <c r="K964" t="n">
+        <v>80</v>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>Terapeuta Em Manaus</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>https://marciadamasceno.com</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr"/>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>559299767074</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr"/>
+      <c r="K965" t="n">
+        <v>89</v>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>Advogados Manaus</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>https://www.manausadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr"/>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>5592981818182</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr"/>
+      <c r="K966" t="n">
+        <v>45</v>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>Advogados em Manaus</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>https://fariasribeiroadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr"/>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>5592995026464</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr"/>
+      <c r="K967" t="n">
+        <v>64</v>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>Os Melhores Advogados de Manaus</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>https://advocaciasmanaus.com</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr"/>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>5592991479179</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr"/>
+      <c r="K968" t="n">
+        <v>55</v>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>Advogados e Escritórios de Advocacia em Manaus</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>https://www.encontramanausam.com.br</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr"/>
+      <c r="I969" t="inlineStr"/>
+      <c r="J969" t="inlineStr"/>
+      <c r="K969" t="n">
+        <v>55</v>
+      </c>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>Advogados Manaus</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>https://lehmann.adv.br</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr"/>
+      <c r="I970" t="inlineStr"/>
+      <c r="J970" t="inlineStr"/>
+      <c r="K970" t="n">
+        <v>91</v>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>Baixo</t>
         </is>
       </c>
     </row>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L970"/>
+  <dimension ref="A1:L981"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47113,10 +47113,8 @@
         </is>
       </c>
       <c r="H958" t="inlineStr"/>
-      <c r="I958" t="inlineStr">
-        <is>
-          <t>5568999787806</t>
-        </is>
+      <c r="I958" t="n">
+        <v>5568999787806</v>
       </c>
       <c r="J958" t="inlineStr"/>
       <c r="K958" t="n">
@@ -47261,10 +47259,8 @@
         </is>
       </c>
       <c r="H961" t="inlineStr"/>
-      <c r="I961" t="inlineStr">
-        <is>
-          <t>5596999050219</t>
-        </is>
+      <c r="I961" t="n">
+        <v>5596999050219</v>
       </c>
       <c r="J961" t="inlineStr"/>
       <c r="K961" t="n">
@@ -47409,10 +47405,8 @@
         </is>
       </c>
       <c r="H964" t="inlineStr"/>
-      <c r="I964" t="inlineStr">
-        <is>
-          <t>5592992249046</t>
-        </is>
+      <c r="I964" t="n">
+        <v>5592992249046</v>
       </c>
       <c r="J964" t="inlineStr"/>
       <c r="K964" t="n">
@@ -47461,10 +47455,8 @@
         </is>
       </c>
       <c r="H965" t="inlineStr"/>
-      <c r="I965" t="inlineStr">
-        <is>
-          <t>559299767074</t>
-        </is>
+      <c r="I965" t="n">
+        <v>559299767074</v>
       </c>
       <c r="J965" t="inlineStr"/>
       <c r="K965" t="n">
@@ -47513,10 +47505,8 @@
         </is>
       </c>
       <c r="H966" t="inlineStr"/>
-      <c r="I966" t="inlineStr">
-        <is>
-          <t>5592981818182</t>
-        </is>
+      <c r="I966" t="n">
+        <v>5592981818182</v>
       </c>
       <c r="J966" t="inlineStr"/>
       <c r="K966" t="n">
@@ -47565,10 +47555,8 @@
         </is>
       </c>
       <c r="H967" t="inlineStr"/>
-      <c r="I967" t="inlineStr">
-        <is>
-          <t>5592995026464</t>
-        </is>
+      <c r="I967" t="n">
+        <v>5592995026464</v>
       </c>
       <c r="J967" t="inlineStr"/>
       <c r="K967" t="n">
@@ -47617,10 +47605,8 @@
         </is>
       </c>
       <c r="H968" t="inlineStr"/>
-      <c r="I968" t="inlineStr">
-        <is>
-          <t>5592991479179</t>
-        </is>
+      <c r="I968" t="n">
+        <v>5592991479179</v>
       </c>
       <c r="J968" t="inlineStr"/>
       <c r="K968" t="n">
@@ -47728,6 +47714,538 @@
         </is>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>Maceió Saúde</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>https://maceiosaude.com</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr"/>
+      <c r="I971" t="inlineStr"/>
+      <c r="J971" t="inlineStr"/>
+      <c r="K971" t="n">
+        <v>69</v>
+      </c>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Salvador</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>https://clivalemais.com.br</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr"/>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>557121027777</t>
+        </is>
+      </c>
+      <c r="J972" t="inlineStr"/>
+      <c r="K972" t="n">
+        <v>69</v>
+      </c>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>CMA Clínica e Day Hospital</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>https://clinicamedicacma.com.br</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr"/>
+      <c r="I973" t="inlineStr"/>
+      <c r="J973" t="inlineStr"/>
+      <c r="K973" t="n">
+        <v>56</v>
+      </c>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>Lista de Médicos e Clínicas em Salvador - BA</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>https://inteligue.com.br</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr"/>
+      <c r="I974" t="inlineStr"/>
+      <c r="J974" t="inlineStr"/>
+      <c r="K974" t="n">
+        <v>33</v>
+      </c>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>Dra Ana Carolina Odontologia, Dentista em Salvador, BA</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>https://dentistasalvadorbahia.com.br</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr"/>
+      <c r="I975" t="inlineStr"/>
+      <c r="J975" t="inlineStr"/>
+      <c r="K975" t="n">
+        <v>67</v>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>OAB : Ordem dos Advogados do Brasil</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>https://www.oab-ba.org.br</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr"/>
+      <c r="I976" t="inlineStr"/>
+      <c r="J976" t="inlineStr"/>
+      <c r="K976" t="n">
+        <v>73</v>
+      </c>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>CEFE</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>http://www.cefe.ufba.br</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr"/>
+      <c r="I977" t="inlineStr"/>
+      <c r="J977" t="inlineStr"/>
+      <c r="K977" t="n">
+        <v>33</v>
+      </c>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>EDUCAÇÃO FÍSICA</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>https://inscricao.ucsal.br</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr"/>
+      <c r="I978" t="inlineStr"/>
+      <c r="J978" t="inlineStr"/>
+      <c r="K978" t="n">
+        <v>33</v>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>https://faced.ufba.br</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr"/>
+      <c r="I979" t="inlineStr"/>
+      <c r="J979" t="inlineStr"/>
+      <c r="K979" t="n">
+        <v>69</v>
+      </c>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>Academia Salvador</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>https://www.salvadordabahia.com</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr"/>
+      <c r="I980" t="inlineStr"/>
+      <c r="J980" t="inlineStr"/>
+      <c r="K980" t="n">
+        <v>100</v>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>Prime Academia</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>https://www.wellprime.com.br</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr"/>
+      <c r="I981" t="inlineStr"/>
+      <c r="J981" t="inlineStr"/>
+      <c r="K981" t="n">
+        <v>70</v>
+      </c>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L981"/>
+  <dimension ref="A1:L998"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47799,10 +47799,8 @@
         </is>
       </c>
       <c r="H972" t="inlineStr"/>
-      <c r="I972" t="inlineStr">
-        <is>
-          <t>557121027777</t>
-        </is>
+      <c r="I972" t="n">
+        <v>557121027777</v>
       </c>
       <c r="J972" t="inlineStr"/>
       <c r="K972" t="n">
@@ -48246,6 +48244,850 @@
         </is>
       </c>
     </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>Clínica Vascular</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>https://luisfernandobastos.com.br</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr"/>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>5561999355005</t>
+        </is>
+      </c>
+      <c r="J982" t="inlineStr"/>
+      <c r="K982" t="n">
+        <v>75</v>
+      </c>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>Odontologia com excelência em Brasília</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>https://clinicablu.com.br</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr"/>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>556196138793</t>
+        </is>
+      </c>
+      <c r="J983" t="inlineStr"/>
+      <c r="K983" t="n">
+        <v>73</v>
+      </c>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>Melhores Psicólogos em Brasília</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>https://livegenda.com.br</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr"/>
+      <c r="I984" t="inlineStr"/>
+      <c r="J984" t="inlineStr"/>
+      <c r="K984" t="n">
+        <v>62</v>
+      </c>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>Psicólogo em Ceilândia - Brasília DF</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>https://clinicadepsicologiaalmer.com.br</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr"/>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>5561992112177</t>
+        </is>
+      </c>
+      <c r="J985" t="inlineStr"/>
+      <c r="K985" t="n">
+        <v>60</v>
+      </c>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>Terapeutas em DF</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>https://buscaterapeutas.com.br</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr"/>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>5515981224202</t>
+        </is>
+      </c>
+      <c r="J986" t="inlineStr"/>
+      <c r="K986" t="n">
+        <v>70</v>
+      </c>
+      <c r="L986" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>Encontre Terapeuta em Brasília/DF com o Helpie!</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>https://www.helpie.com.br</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr"/>
+      <c r="I987" t="inlineStr"/>
+      <c r="J987" t="inlineStr"/>
+      <c r="K987" t="n">
+        <v>67</v>
+      </c>
+      <c r="L987" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>https://www.iesb.br</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr"/>
+      <c r="I988" t="inlineStr"/>
+      <c r="J988" t="inlineStr"/>
+      <c r="K988" t="n">
+        <v>0</v>
+      </c>
+      <c r="L988" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>https://aabbdf.com.br</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr"/>
+      <c r="I989" t="inlineStr"/>
+      <c r="J989" t="inlineStr"/>
+      <c r="K989" t="n">
+        <v>60</v>
+      </c>
+      <c r="L989" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>Academia Vasco Neto</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>https://www.academiavasconeto.com.br</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr"/>
+      <c r="I990" t="inlineStr"/>
+      <c r="J990" t="inlineStr"/>
+      <c r="K990" t="n">
+        <v>70</v>
+      </c>
+      <c r="L990" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Academia em Brasília: venha conhecer a melhor academia da cidade</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>https://blog.ciaathletica.com.br</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr"/>
+      <c r="I991" t="inlineStr"/>
+      <c r="J991" t="inlineStr"/>
+      <c r="K991" t="n">
+        <v>56</v>
+      </c>
+      <c r="L991" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>Spazio Vita Fisioterapia</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>https://spaziovitafisioterapia.com</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr"/>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>5561999963898</t>
+        </is>
+      </c>
+      <c r="J992" t="inlineStr"/>
+      <c r="K992" t="n">
+        <v>69</v>
+      </c>
+      <c r="L992" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>Arquivo de Goiânia</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>https://doctorbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr"/>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>5562998228647</t>
+        </is>
+      </c>
+      <c r="J993" t="inlineStr"/>
+      <c r="K993" t="n">
+        <v>88</v>
+      </c>
+      <c r="L993" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Guia Médico</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>https://guiamedico.unimedgoiania.coop.br</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr"/>
+      <c r="I994" t="inlineStr"/>
+      <c r="J994" t="inlineStr"/>
+      <c r="K994" t="n">
+        <v>62</v>
+      </c>
+      <c r="L994" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>20 melhores profissionais terapeutas em Goiânia</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>https://constelacaoclinica.com</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr"/>
+      <c r="I995" t="inlineStr"/>
+      <c r="J995" t="inlineStr"/>
+      <c r="K995" t="n">
+        <v>56</v>
+      </c>
+      <c r="L995" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Bruno Araújo Advocacia</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>https://brunoaraujoadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr"/>
+      <c r="I996" t="inlineStr"/>
+      <c r="J996" t="inlineStr"/>
+      <c r="K996" t="n">
+        <v>33</v>
+      </c>
+      <c r="L996" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>ADVOGADO EM GOIÂNIA</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>https://www.advbacellar.com.br</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr"/>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>5562996768223</t>
+        </is>
+      </c>
+      <c r="J997" t="inlineStr"/>
+      <c r="K997" t="n">
+        <v>73</v>
+      </c>
+      <c r="L997" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>Fisioterapia em Goiânia: Conheça o COE Ortopedia Especializada</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>https://blog.coegoiania.com.br</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr"/>
+      <c r="I998" t="inlineStr"/>
+      <c r="J998" t="inlineStr"/>
+      <c r="K998" t="n">
+        <v>33</v>
+      </c>
+      <c r="L998" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L998"/>
+  <dimension ref="A1:L1018"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48281,10 +48281,8 @@
         </is>
       </c>
       <c r="H982" t="inlineStr"/>
-      <c r="I982" t="inlineStr">
-        <is>
-          <t>5561999355005</t>
-        </is>
+      <c r="I982" t="n">
+        <v>5561999355005</v>
       </c>
       <c r="J982" t="inlineStr"/>
       <c r="K982" t="n">
@@ -48333,10 +48331,8 @@
         </is>
       </c>
       <c r="H983" t="inlineStr"/>
-      <c r="I983" t="inlineStr">
-        <is>
-          <t>556196138793</t>
-        </is>
+      <c r="I983" t="n">
+        <v>556196138793</v>
       </c>
       <c r="J983" t="inlineStr"/>
       <c r="K983" t="n">
@@ -48433,10 +48429,8 @@
         </is>
       </c>
       <c r="H985" t="inlineStr"/>
-      <c r="I985" t="inlineStr">
-        <is>
-          <t>5561992112177</t>
-        </is>
+      <c r="I985" t="n">
+        <v>5561992112177</v>
       </c>
       <c r="J985" t="inlineStr"/>
       <c r="K985" t="n">
@@ -48485,10 +48479,8 @@
         </is>
       </c>
       <c r="H986" t="inlineStr"/>
-      <c r="I986" t="inlineStr">
-        <is>
-          <t>5515981224202</t>
-        </is>
+      <c r="I986" t="n">
+        <v>5515981224202</v>
       </c>
       <c r="J986" t="inlineStr"/>
       <c r="K986" t="n">
@@ -48777,10 +48769,8 @@
         </is>
       </c>
       <c r="H992" t="inlineStr"/>
-      <c r="I992" t="inlineStr">
-        <is>
-          <t>5561999963898</t>
-        </is>
+      <c r="I992" t="n">
+        <v>5561999963898</v>
       </c>
       <c r="J992" t="inlineStr"/>
       <c r="K992" t="n">
@@ -48829,10 +48819,8 @@
         </is>
       </c>
       <c r="H993" t="inlineStr"/>
-      <c r="I993" t="inlineStr">
-        <is>
-          <t>5562998228647</t>
-        </is>
+      <c r="I993" t="n">
+        <v>5562998228647</v>
       </c>
       <c r="J993" t="inlineStr"/>
       <c r="K993" t="n">
@@ -49025,10 +49013,8 @@
         </is>
       </c>
       <c r="H997" t="inlineStr"/>
-      <c r="I997" t="inlineStr">
-        <is>
-          <t>5562996768223</t>
-        </is>
+      <c r="I997" t="n">
+        <v>5562996768223</v>
       </c>
       <c r="J997" t="inlineStr"/>
       <c r="K997" t="n">
@@ -49088,6 +49074,1010 @@
         </is>
       </c>
     </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>Victoria Medicina: Victória Medicina e Diagnóstico</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>https://victoriamedicina.com.br</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr"/>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>552730270100</t>
+        </is>
+      </c>
+      <c r="J999" t="inlineStr"/>
+      <c r="K999" t="n">
+        <v>82</v>
+      </c>
+      <c r="L999" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>MedLive Centro Médico em Vitória-ES</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>https://medlive-es.com.br</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr"/>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>5527998004211</t>
+        </is>
+      </c>
+      <c r="J1000" t="inlineStr"/>
+      <c r="K1000" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1000" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>Padilha Odontologia</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>https://institutopadilha.com.br</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr"/>
+      <c r="I1001" t="inlineStr"/>
+      <c r="J1001" t="inlineStr"/>
+      <c r="K1001" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1001" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>Maxxi Dental</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>https://maxxidental.com.br</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr"/>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>552733253038</t>
+        </is>
+      </c>
+      <c r="J1002" t="inlineStr"/>
+      <c r="K1002" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1002" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>Clínica Kamilla Scalzer: Dentista em Vitória ES</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>https://clinicakamillascalzer.com.br</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr"/>
+      <c r="I1003" t="inlineStr"/>
+      <c r="J1003" t="inlineStr"/>
+      <c r="K1003" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1003" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>Um Estudo na Academia Popular de Santo Antônio em Vitória-ES</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>https://periodicos.ufmg.br</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr"/>
+      <c r="I1004" t="inlineStr"/>
+      <c r="J1004" t="inlineStr"/>
+      <c r="K1004" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1004" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>Kit Para Montar Academia in Vitória, ES</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>https://powerrun.com.br</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr"/>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>5514982191126</t>
+        </is>
+      </c>
+      <c r="J1005" t="inlineStr"/>
+      <c r="K1005" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1005" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>Policlínica Salud</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>https://www.policlinicasalud.com.br</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr"/>
+      <c r="I1006" t="inlineStr"/>
+      <c r="J1006" t="inlineStr"/>
+      <c r="K1006" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1006" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>Centro Médico MaterMed - 50 Anos cuidando de você!</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>https://www.matermed.com.br</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr"/>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>5531998784777</t>
+        </is>
+      </c>
+      <c r="J1007" t="inlineStr"/>
+      <c r="K1007" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1007" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>consulta com médico clínico geral valor r$100,00</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>https://www.bhcentrodiagnostico.com</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr"/>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>5531996022782</t>
+        </is>
+      </c>
+      <c r="J1008" t="inlineStr"/>
+      <c r="K1008" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1008" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>Hospital Evangélico de Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>https://he.org.br</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr"/>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>553121388355</t>
+        </is>
+      </c>
+      <c r="J1009" t="inlineStr"/>
+      <c r="K1009" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1009" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>Dentista</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>https://www.odontosaudevida.com.br</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr"/>
+      <c r="I1010" t="inlineStr"/>
+      <c r="J1010" t="inlineStr"/>
+      <c r="K1010" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1010" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>Marcos Santos</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>https://msantosodonto.com</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr"/>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>5531993519143</t>
+        </is>
+      </c>
+      <c r="J1011" t="inlineStr"/>
+      <c r="K1011" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1011" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>Contextualmente</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>https://www.contextualmente.com</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr"/>
+      <c r="I1012" t="inlineStr"/>
+      <c r="J1012" t="inlineStr"/>
+      <c r="K1012" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1012" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>Terapia Clínica</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>https://terapiaclinica.com.br</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr"/>
+      <c r="I1013" t="inlineStr"/>
+      <c r="J1013" t="inlineStr"/>
+      <c r="K1013" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1013" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>Dr. Sérgio Antonio</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>https://www.sergioantonioadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr"/>
+      <c r="I1014" t="inlineStr"/>
+      <c r="J1014" t="inlineStr"/>
+      <c r="K1014" t="n">
+        <v>55</v>
+      </c>
+      <c r="L1014" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>Advogado Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>https://cleidesobreira.com.br</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr"/>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>5511988078120</t>
+        </is>
+      </c>
+      <c r="J1015" t="inlineStr"/>
+      <c r="K1015" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1015" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta em Belo Horizonte - MG</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>https://www.paularezendefisio.com.br</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr"/>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>5531999731985</t>
+        </is>
+      </c>
+      <c r="J1016" t="inlineStr"/>
+      <c r="K1016" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1016" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>Consulta Carioca</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>https://www.consultacarioca.com.br</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr"/>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>5521969162030</t>
+        </is>
+      </c>
+      <c r="J1017" t="inlineStr"/>
+      <c r="K1017" t="n">
+        <v>76</v>
+      </c>
+      <c r="L1017" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>Clínicas Prosaúde</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>https://prosaude.com.br</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr"/>
+      <c r="I1018" t="inlineStr"/>
+      <c r="J1018" t="inlineStr"/>
+      <c r="K1018" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1018" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1018"/>
+  <dimension ref="A1:L1042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49111,10 +49111,8 @@
         </is>
       </c>
       <c r="H999" t="inlineStr"/>
-      <c r="I999" t="inlineStr">
-        <is>
-          <t>552730270100</t>
-        </is>
+      <c r="I999" t="n">
+        <v>552730270100</v>
       </c>
       <c r="J999" t="inlineStr"/>
       <c r="K999" t="n">
@@ -49163,10 +49161,8 @@
         </is>
       </c>
       <c r="H1000" t="inlineStr"/>
-      <c r="I1000" t="inlineStr">
-        <is>
-          <t>5527998004211</t>
-        </is>
+      <c r="I1000" t="n">
+        <v>5527998004211</v>
       </c>
       <c r="J1000" t="inlineStr"/>
       <c r="K1000" t="n">
@@ -49263,10 +49259,8 @@
         </is>
       </c>
       <c r="H1002" t="inlineStr"/>
-      <c r="I1002" t="inlineStr">
-        <is>
-          <t>552733253038</t>
-        </is>
+      <c r="I1002" t="n">
+        <v>552733253038</v>
       </c>
       <c r="J1002" t="inlineStr"/>
       <c r="K1002" t="n">
@@ -49411,10 +49405,8 @@
         </is>
       </c>
       <c r="H1005" t="inlineStr"/>
-      <c r="I1005" t="inlineStr">
-        <is>
-          <t>5514982191126</t>
-        </is>
+      <c r="I1005" t="n">
+        <v>5514982191126</v>
       </c>
       <c r="J1005" t="inlineStr"/>
       <c r="K1005" t="n">
@@ -49511,10 +49503,8 @@
         </is>
       </c>
       <c r="H1007" t="inlineStr"/>
-      <c r="I1007" t="inlineStr">
-        <is>
-          <t>5531998784777</t>
-        </is>
+      <c r="I1007" t="n">
+        <v>5531998784777</v>
       </c>
       <c r="J1007" t="inlineStr"/>
       <c r="K1007" t="n">
@@ -49563,10 +49553,8 @@
         </is>
       </c>
       <c r="H1008" t="inlineStr"/>
-      <c r="I1008" t="inlineStr">
-        <is>
-          <t>5531996022782</t>
-        </is>
+      <c r="I1008" t="n">
+        <v>5531996022782</v>
       </c>
       <c r="J1008" t="inlineStr"/>
       <c r="K1008" t="n">
@@ -49615,10 +49603,8 @@
         </is>
       </c>
       <c r="H1009" t="inlineStr"/>
-      <c r="I1009" t="inlineStr">
-        <is>
-          <t>553121388355</t>
-        </is>
+      <c r="I1009" t="n">
+        <v>553121388355</v>
       </c>
       <c r="J1009" t="inlineStr"/>
       <c r="K1009" t="n">
@@ -49715,10 +49701,8 @@
         </is>
       </c>
       <c r="H1011" t="inlineStr"/>
-      <c r="I1011" t="inlineStr">
-        <is>
-          <t>5531993519143</t>
-        </is>
+      <c r="I1011" t="n">
+        <v>5531993519143</v>
       </c>
       <c r="J1011" t="inlineStr"/>
       <c r="K1011" t="n">
@@ -49911,10 +49895,8 @@
         </is>
       </c>
       <c r="H1015" t="inlineStr"/>
-      <c r="I1015" t="inlineStr">
-        <is>
-          <t>5511988078120</t>
-        </is>
+      <c r="I1015" t="n">
+        <v>5511988078120</v>
       </c>
       <c r="J1015" t="inlineStr"/>
       <c r="K1015" t="n">
@@ -49963,10 +49945,8 @@
         </is>
       </c>
       <c r="H1016" t="inlineStr"/>
-      <c r="I1016" t="inlineStr">
-        <is>
-          <t>5531999731985</t>
-        </is>
+      <c r="I1016" t="n">
+        <v>5531999731985</v>
       </c>
       <c r="J1016" t="inlineStr"/>
       <c r="K1016" t="n">
@@ -50015,10 +49995,8 @@
         </is>
       </c>
       <c r="H1017" t="inlineStr"/>
-      <c r="I1017" t="inlineStr">
-        <is>
-          <t>5521969162030</t>
-        </is>
+      <c r="I1017" t="n">
+        <v>5521969162030</v>
       </c>
       <c r="J1017" t="inlineStr"/>
       <c r="K1017" t="n">
@@ -50078,6 +50056,1198 @@
         </is>
       </c>
     </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>Clinicar</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>https://clinicarpr.com.br</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr"/>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>5541988666344</t>
+        </is>
+      </c>
+      <c r="J1019" t="inlineStr"/>
+      <c r="K1019" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1019" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>Policlínica Sítio Cercado</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>https://policlinicasitiocercado.com.br</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr"/>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>554132582000</t>
+        </is>
+      </c>
+      <c r="J1020" t="inlineStr"/>
+      <c r="K1020" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1020" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>Clinica Médica</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>https://hospital.mackenzie.br</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr"/>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>556332365340</t>
+        </is>
+      </c>
+      <c r="J1021" t="inlineStr"/>
+      <c r="K1021" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1021" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>Departamento de Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>https://saude.ufpr.br</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr"/>
+      <c r="I1022" t="inlineStr"/>
+      <c r="J1022" t="inlineStr"/>
+      <c r="K1022" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1022" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>MEDICINA DO TRABALHO CURITIBA</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>https://idealmed.med.br</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr"/>
+      <c r="I1023" t="inlineStr"/>
+      <c r="J1023" t="inlineStr"/>
+      <c r="K1023" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1023" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>https://www.utfpr.edu.br</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr"/>
+      <c r="I1024" t="inlineStr"/>
+      <c r="J1024" t="inlineStr"/>
+      <c r="K1024" t="n">
+        <v>78</v>
+      </c>
+      <c r="L1024" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>Educação Física (Curitiba)</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>https://agendamento.universoufpr.com.br</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr"/>
+      <c r="I1025" t="inlineStr"/>
+      <c r="J1025" t="inlineStr"/>
+      <c r="K1025" t="n">
+        <v>65</v>
+      </c>
+      <c r="L1025" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>Departamento de Educação Física</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>https://bio.ufpr.br</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr"/>
+      <c r="I1026" t="inlineStr"/>
+      <c r="J1026" t="inlineStr"/>
+      <c r="K1026" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1026" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>13 Fisioterapeutas mais recomendados em Curitiba, PR</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>https://www.drbuska.com.br</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr"/>
+      <c r="I1027" t="inlineStr"/>
+      <c r="J1027" t="inlineStr"/>
+      <c r="K1027" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1027" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>Clínica Wallig</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>https://www.ccgsaude.com.br</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr"/>
+      <c r="I1028" t="inlineStr"/>
+      <c r="J1028" t="inlineStr"/>
+      <c r="K1028" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1028" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>Dentista</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>https://www.odontomaffei.com.br</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr"/>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>5551999750636</t>
+        </is>
+      </c>
+      <c r="J1029" t="inlineStr"/>
+      <c r="K1029" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1029" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>Psicóloga em Porto Alegre Luísa Ciulla Psicólogo Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>https://www.psicologaportoalegre.com.br</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr"/>
+      <c r="I1030" t="inlineStr"/>
+      <c r="J1030" t="inlineStr"/>
+      <c r="K1030" t="n">
+        <v>53</v>
+      </c>
+      <c r="L1030" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>Manoel Felipe Terapeuta</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>https://www.manoelfelipemd.com.br</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr"/>
+      <c r="I1031" t="inlineStr"/>
+      <c r="J1031" t="inlineStr"/>
+      <c r="K1031" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1031" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>Psicóloga Priscilla Fernandes</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>https://www.psicologapriscillafernandes.com</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr"/>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>5551996207702</t>
+        </is>
+      </c>
+      <c r="J1032" t="inlineStr"/>
+      <c r="K1032" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1032" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>Larissa Ferreira</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>https://www.larissaferreirapsicologa.com.br</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr"/>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>5551999927414</t>
+        </is>
+      </c>
+      <c r="J1033" t="inlineStr"/>
+      <c r="K1033" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1033" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>Assis Brasil – Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>https://usinadocorpoacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr"/>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>5551989894461</t>
+        </is>
+      </c>
+      <c r="J1034" t="inlineStr"/>
+      <c r="K1034" t="n">
+        <v>90</v>
+      </c>
+      <c r="L1034" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>https://www.sesc-rs.com.br</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr"/>
+      <c r="I1035" t="inlineStr"/>
+      <c r="J1035" t="inlineStr"/>
+      <c r="K1035" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1035" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>Academia Ph.D Sports Assis Brasil</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>https://www.academiaphdsports.com.br</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr"/>
+      <c r="I1036" t="inlineStr"/>
+      <c r="J1036" t="inlineStr"/>
+      <c r="K1036" t="n">
+        <v>40</v>
+      </c>
+      <c r="L1036" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>https://www.ipanemasports.com.br</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr"/>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>5505132469000</t>
+        </is>
+      </c>
+      <c r="J1037" t="inlineStr"/>
+      <c r="K1037" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1037" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>Bourbon Carlos Gomes - Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>http://www.bioritmo.com.br</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr"/>
+      <c r="I1038" t="inlineStr"/>
+      <c r="J1038" t="inlineStr"/>
+      <c r="K1038" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1038" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>Jardim Lindóia/Grand Park</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>https://engenhariadocorpo.com.br</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr"/>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>555493087752</t>
+        </is>
+      </c>
+      <c r="J1039" t="inlineStr"/>
+      <c r="K1039" t="n">
+        <v>70</v>
+      </c>
+      <c r="L1039" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta Lucas Pinheiro</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>https://www.fisiolucaspinheiro.com.br</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr"/>
+      <c r="I1040" t="inlineStr"/>
+      <c r="J1040" t="inlineStr"/>
+      <c r="K1040" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1040" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>Congresso Sul-Brasileiro de Clínica Médica 2026</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>https://sulbraclinicamedica.com.br</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr"/>
+      <c r="I1041" t="inlineStr"/>
+      <c r="J1041" t="inlineStr"/>
+      <c r="K1041" t="n">
+        <v>50</v>
+      </c>
+      <c r="L1041" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Florianópolis</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>Clínica Médica Capoeiras</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>https://clinicamedicacapoeiras.com.br</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr"/>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>5548999470288</t>
+        </is>
+      </c>
+      <c r="J1042" t="inlineStr"/>
+      <c r="K1042" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1042" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1042"/>
+  <dimension ref="A1:L1060"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50093,10 +50093,8 @@
         </is>
       </c>
       <c r="H1019" t="inlineStr"/>
-      <c r="I1019" t="inlineStr">
-        <is>
-          <t>5541988666344</t>
-        </is>
+      <c r="I1019" t="n">
+        <v>5541988666344</v>
       </c>
       <c r="J1019" t="inlineStr"/>
       <c r="K1019" t="n">
@@ -50145,10 +50143,8 @@
         </is>
       </c>
       <c r="H1020" t="inlineStr"/>
-      <c r="I1020" t="inlineStr">
-        <is>
-          <t>554132582000</t>
-        </is>
+      <c r="I1020" t="n">
+        <v>554132582000</v>
       </c>
       <c r="J1020" t="inlineStr"/>
       <c r="K1020" t="n">
@@ -50197,10 +50193,8 @@
         </is>
       </c>
       <c r="H1021" t="inlineStr"/>
-      <c r="I1021" t="inlineStr">
-        <is>
-          <t>556332365340</t>
-        </is>
+      <c r="I1021" t="n">
+        <v>556332365340</v>
       </c>
       <c r="J1021" t="inlineStr"/>
       <c r="K1021" t="n">
@@ -50585,10 +50579,8 @@
         </is>
       </c>
       <c r="H1029" t="inlineStr"/>
-      <c r="I1029" t="inlineStr">
-        <is>
-          <t>5551999750636</t>
-        </is>
+      <c r="I1029" t="n">
+        <v>5551999750636</v>
       </c>
       <c r="J1029" t="inlineStr"/>
       <c r="K1029" t="n">
@@ -50733,10 +50725,8 @@
         </is>
       </c>
       <c r="H1032" t="inlineStr"/>
-      <c r="I1032" t="inlineStr">
-        <is>
-          <t>5551996207702</t>
-        </is>
+      <c r="I1032" t="n">
+        <v>5551996207702</v>
       </c>
       <c r="J1032" t="inlineStr"/>
       <c r="K1032" t="n">
@@ -50785,10 +50775,8 @@
         </is>
       </c>
       <c r="H1033" t="inlineStr"/>
-      <c r="I1033" t="inlineStr">
-        <is>
-          <t>5551999927414</t>
-        </is>
+      <c r="I1033" t="n">
+        <v>5551999927414</v>
       </c>
       <c r="J1033" t="inlineStr"/>
       <c r="K1033" t="n">
@@ -50837,10 +50825,8 @@
         </is>
       </c>
       <c r="H1034" t="inlineStr"/>
-      <c r="I1034" t="inlineStr">
-        <is>
-          <t>5551989894461</t>
-        </is>
+      <c r="I1034" t="n">
+        <v>5551989894461</v>
       </c>
       <c r="J1034" t="inlineStr"/>
       <c r="K1034" t="n">
@@ -50985,10 +50971,8 @@
         </is>
       </c>
       <c r="H1037" t="inlineStr"/>
-      <c r="I1037" t="inlineStr">
-        <is>
-          <t>5505132469000</t>
-        </is>
+      <c r="I1037" t="n">
+        <v>5505132469000</v>
       </c>
       <c r="J1037" t="inlineStr"/>
       <c r="K1037" t="n">
@@ -51085,10 +51069,8 @@
         </is>
       </c>
       <c r="H1039" t="inlineStr"/>
-      <c r="I1039" t="inlineStr">
-        <is>
-          <t>555493087752</t>
-        </is>
+      <c r="I1039" t="n">
+        <v>555493087752</v>
       </c>
       <c r="J1039" t="inlineStr"/>
       <c r="K1039" t="n">
@@ -51233,16 +51215,894 @@
         </is>
       </c>
       <c r="H1042" t="inlineStr"/>
-      <c r="I1042" t="inlineStr">
-        <is>
-          <t>5548999470288</t>
-        </is>
+      <c r="I1042" t="n">
+        <v>5548999470288</v>
       </c>
       <c r="J1042" t="inlineStr"/>
       <c r="K1042" t="n">
         <v>69</v>
       </c>
       <c r="L1042" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>Preventiva Engenharia e Medicina do Trabalho: Clínica do ...</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>https://preventivabrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr"/>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>556899355105</t>
+        </is>
+      </c>
+      <c r="J1043" t="inlineStr"/>
+      <c r="K1043" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1043" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>Plano de Saúde Select Rio Branco</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>https://selectoperadora.com.br</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr"/>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>5508002242808</t>
+        </is>
+      </c>
+      <c r="J1044" t="inlineStr"/>
+      <c r="K1044" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1044" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>VITALCLIN</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>https://www.vitalclinac.uniexames.com.br</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr"/>
+      <c r="I1045" t="inlineStr"/>
+      <c r="J1045" t="inlineStr"/>
+      <c r="K1045" t="n">
+        <v>76</v>
+      </c>
+      <c r="L1045" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>LABCLIN SAÚDE CLINICA MÉDICA &amp; LABORATÓRIO DE ...</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>https://labclinsaudeac.com.br</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr"/>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>5568999670789</t>
+        </is>
+      </c>
+      <c r="J1046" t="inlineStr"/>
+      <c r="K1046" t="n">
+        <v>71</v>
+      </c>
+      <c r="L1046" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>Teramoto Odontologia</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>https://teramotoodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr"/>
+      <c r="I1047" t="inlineStr"/>
+      <c r="J1047" t="inlineStr"/>
+      <c r="K1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1047" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>Os 35 Psicologos mais Indicados em Rio Branco AC</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>https://docsite.app.br</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr"/>
+      <c r="I1048" t="inlineStr"/>
+      <c r="J1048" t="inlineStr"/>
+      <c r="K1048" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1048" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>[PDF] CRP 2</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>https://transparencia.cfp.org.br</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr"/>
+      <c r="I1049" t="inlineStr"/>
+      <c r="J1049" t="inlineStr"/>
+      <c r="K1049" t="n">
+        <v>94</v>
+      </c>
+      <c r="L1049" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>GISLEYANE MELO "GIGI" TERAPEUTA CORPORAL em Rio Branco</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>https://www.psicologas.biz</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr"/>
+      <c r="I1050" t="inlineStr"/>
+      <c r="J1050" t="inlineStr"/>
+      <c r="K1050" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1050" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>Clínico em Macapá - AP: 531 médicos</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>https://bula.com.br</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr"/>
+      <c r="I1051" t="inlineStr"/>
+      <c r="J1051" t="inlineStr"/>
+      <c r="K1051" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1051" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>Vista do Interações medicamentosas e consequentes ...</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>https://visaemdebate.incqs.fiocruz.br</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr"/>
+      <c r="I1052" t="inlineStr"/>
+      <c r="J1052" t="inlineStr"/>
+      <c r="K1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1052" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>REATIVA ACADEMIA TERAPEUTICA LTDA</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>https://monitorcnpj.com.br</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr"/>
+      <c r="I1053" t="inlineStr"/>
+      <c r="J1053" t="inlineStr"/>
+      <c r="K1053" t="n">
+        <v>76</v>
+      </c>
+      <c r="L1053" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>[PDF] COSTA, Robson Antonio. SOUZA, Michel Assunção Vale de. A ...</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>https://portaldeperiodicos.animaeducacao.com.br</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr"/>
+      <c r="I1054" t="inlineStr"/>
+      <c r="J1054" t="inlineStr"/>
+      <c r="K1054" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1054" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>Efeito placebo no desempenho da força muscular em homens ...</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>http://www.rbne.com.br</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr"/>
+      <c r="I1055" t="inlineStr"/>
+      <c r="J1055" t="inlineStr"/>
+      <c r="K1055" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1055" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>Vista do Ortotanásia na formação médica: tabus e desvelamentos</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>https://revistabioetica.cfm.org.br</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr"/>
+      <c r="I1056" t="inlineStr"/>
+      <c r="J1056" t="inlineStr"/>
+      <c r="K1056" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1056" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>CMM Medical Center Manoa, Av. Francisco Queiroz, 56</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>https://brasillocais.com</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr"/>
+      <c r="I1057" t="inlineStr"/>
+      <c r="J1057" t="inlineStr"/>
+      <c r="K1057" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1057" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>Busca por médicos</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>https://cremam.org.br</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr"/>
+      <c r="I1058" t="inlineStr"/>
+      <c r="J1058" t="inlineStr"/>
+      <c r="K1058" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1058" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>Psicóloga Amanda Araújo/ Manaus</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>https://psicologoemmanaus.com</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr"/>
+      <c r="I1059" t="inlineStr"/>
+      <c r="J1059" t="inlineStr"/>
+      <c r="K1059" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1059" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>OAB Amazonas</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>https://www.oabam.org.br</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr"/>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>5592992863958</t>
+        </is>
+      </c>
+      <c r="J1060" t="inlineStr"/>
+      <c r="K1060" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1060" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1060"/>
+  <dimension ref="A1:L1072"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51265,10 +51265,8 @@
         </is>
       </c>
       <c r="H1043" t="inlineStr"/>
-      <c r="I1043" t="inlineStr">
-        <is>
-          <t>556899355105</t>
-        </is>
+      <c r="I1043" t="n">
+        <v>556899355105</v>
       </c>
       <c r="J1043" t="inlineStr"/>
       <c r="K1043" t="n">
@@ -51317,10 +51315,8 @@
         </is>
       </c>
       <c r="H1044" t="inlineStr"/>
-      <c r="I1044" t="inlineStr">
-        <is>
-          <t>5508002242808</t>
-        </is>
+      <c r="I1044" t="n">
+        <v>5508002242808</v>
       </c>
       <c r="J1044" t="inlineStr"/>
       <c r="K1044" t="n">
@@ -51417,10 +51413,8 @@
         </is>
       </c>
       <c r="H1046" t="inlineStr"/>
-      <c r="I1046" t="inlineStr">
-        <is>
-          <t>5568999670789</t>
-        </is>
+      <c r="I1046" t="n">
+        <v>5568999670789</v>
       </c>
       <c r="J1046" t="inlineStr"/>
       <c r="K1046" t="n">
@@ -52093,16 +52087,618 @@
         </is>
       </c>
       <c r="H1060" t="inlineStr"/>
-      <c r="I1060" t="inlineStr">
-        <is>
-          <t>5592992863958</t>
-        </is>
+      <c r="I1060" t="n">
+        <v>5592992863958</v>
       </c>
       <c r="J1060" t="inlineStr"/>
       <c r="K1060" t="n">
         <v>73</v>
       </c>
       <c r="L1060" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>Comac Material Médico</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>https://www.comacmaterialmedico.com.br</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr"/>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>558299981468</t>
+        </is>
+      </c>
+      <c r="J1061" t="inlineStr"/>
+      <c r="K1061" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1061" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>PERFIL DA MORTALIDADE POR ASFIXIAS NO INSTITUTO ...</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>https://www.perspectivas.med.br</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr"/>
+      <c r="I1062" t="inlineStr"/>
+      <c r="J1062" t="inlineStr"/>
+      <c r="K1062" t="n">
+        <v>65</v>
+      </c>
+      <c r="L1062" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>Clínica ADS</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>https://clinicaads.com.br</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr"/>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>557199237237</t>
+        </is>
+      </c>
+      <c r="J1063" t="inlineStr"/>
+      <c r="K1063" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1063" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>Clínica da Família: HOME</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>https://www.clinicamedicadafamilia.com.br</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr"/>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>5571994180003</t>
+        </is>
+      </c>
+      <c r="J1064" t="inlineStr"/>
+      <c r="K1064" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1064" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica Vilasboas</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>https://www.clinicavilasboas.com.br</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr"/>
+      <c r="I1065" t="inlineStr"/>
+      <c r="J1065" t="inlineStr"/>
+      <c r="K1065" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1065" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>Dental Mac Salvador</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>https://dentalmacssa.com.br</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr"/>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>557133599096</t>
+        </is>
+      </c>
+      <c r="J1066" t="inlineStr"/>
+      <c r="K1066" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1066" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>Oral Clean Odontologia Digital</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>https://www.adoromeusorriso.com.br</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr"/>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>5571999668851</t>
+        </is>
+      </c>
+      <c r="J1067" t="inlineStr"/>
+      <c r="K1067" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1067" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>Climil Odontologia Moderna</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>https://climilodontologiamoderna.com.br</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr"/>
+      <c r="I1068" t="inlineStr"/>
+      <c r="J1068" t="inlineStr"/>
+      <c r="K1068" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1068" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>Encontre um especialista</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>https://croba.org.br</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr"/>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>5507131142525</t>
+        </is>
+      </c>
+      <c r="J1069" t="inlineStr"/>
+      <c r="K1069" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1069" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>Louise Diná</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>https://www.psicologalouise.com.br</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr"/>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>5571983631000</t>
+        </is>
+      </c>
+      <c r="J1070" t="inlineStr"/>
+      <c r="K1070" t="n">
+        <v>93</v>
+      </c>
+      <c r="L1070" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>Psicólogo em Salvador BA: como encontrar o profissional certo</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>https://lumusterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr"/>
+      <c r="I1071" t="inlineStr"/>
+      <c r="J1071" t="inlineStr"/>
+      <c r="K1071" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1071" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>Terapeutas para Ansiedade</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>https://vitrine.terapiaacolher.com.br</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr"/>
+      <c r="I1072" t="inlineStr"/>
+      <c r="J1072" t="inlineStr"/>
+      <c r="K1072" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1072" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1072"/>
+  <dimension ref="A1:L1089"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52137,10 +52137,8 @@
         </is>
       </c>
       <c r="H1061" t="inlineStr"/>
-      <c r="I1061" t="inlineStr">
-        <is>
-          <t>558299981468</t>
-        </is>
+      <c r="I1061" t="n">
+        <v>558299981468</v>
       </c>
       <c r="J1061" t="inlineStr"/>
       <c r="K1061" t="n">
@@ -52237,10 +52235,8 @@
         </is>
       </c>
       <c r="H1063" t="inlineStr"/>
-      <c r="I1063" t="inlineStr">
-        <is>
-          <t>557199237237</t>
-        </is>
+      <c r="I1063" t="n">
+        <v>557199237237</v>
       </c>
       <c r="J1063" t="inlineStr"/>
       <c r="K1063" t="n">
@@ -52289,10 +52285,8 @@
         </is>
       </c>
       <c r="H1064" t="inlineStr"/>
-      <c r="I1064" t="inlineStr">
-        <is>
-          <t>5571994180003</t>
-        </is>
+      <c r="I1064" t="n">
+        <v>5571994180003</v>
       </c>
       <c r="J1064" t="inlineStr"/>
       <c r="K1064" t="n">
@@ -52389,10 +52383,8 @@
         </is>
       </c>
       <c r="H1066" t="inlineStr"/>
-      <c r="I1066" t="inlineStr">
-        <is>
-          <t>557133599096</t>
-        </is>
+      <c r="I1066" t="n">
+        <v>557133599096</v>
       </c>
       <c r="J1066" t="inlineStr"/>
       <c r="K1066" t="n">
@@ -52441,10 +52433,8 @@
         </is>
       </c>
       <c r="H1067" t="inlineStr"/>
-      <c r="I1067" t="inlineStr">
-        <is>
-          <t>5571999668851</t>
-        </is>
+      <c r="I1067" t="n">
+        <v>5571999668851</v>
       </c>
       <c r="J1067" t="inlineStr"/>
       <c r="K1067" t="n">
@@ -52541,10 +52531,8 @@
         </is>
       </c>
       <c r="H1069" t="inlineStr"/>
-      <c r="I1069" t="inlineStr">
-        <is>
-          <t>5507131142525</t>
-        </is>
+      <c r="I1069" t="n">
+        <v>5507131142525</v>
       </c>
       <c r="J1069" t="inlineStr"/>
       <c r="K1069" t="n">
@@ -52593,10 +52581,8 @@
         </is>
       </c>
       <c r="H1070" t="inlineStr"/>
-      <c r="I1070" t="inlineStr">
-        <is>
-          <t>5571983631000</t>
-        </is>
+      <c r="I1070" t="n">
+        <v>5571983631000</v>
       </c>
       <c r="J1070" t="inlineStr"/>
       <c r="K1070" t="n">
@@ -52704,6 +52690,858 @@
         </is>
       </c>
     </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>Davida Medicina Especializada · Brasília-DF</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>https://www.davidamedicina.com.br</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr"/>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>556130201981</t>
+        </is>
+      </c>
+      <c r="J1073" t="inlineStr"/>
+      <c r="K1073" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1073" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>Agende Seu Médico DF • Consultas em Brasília</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>https://agendeseumedico.com.br</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr"/>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>5561982863837</t>
+        </is>
+      </c>
+      <c r="J1074" t="inlineStr"/>
+      <c r="K1074" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1074" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>Seidler Odontologia</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>https://seidlerodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr"/>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>556199878534</t>
+        </is>
+      </c>
+      <c r="J1075" t="inlineStr"/>
+      <c r="K1075" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1075" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>Centro Interescolar de Educação Física (CIEF)</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>https://br.todosnegocios.com</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr"/>
+      <c r="I1076" t="inlineStr"/>
+      <c r="J1076" t="inlineStr"/>
+      <c r="K1076" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1076" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>Fisioterapia Domiciliar em Brasília-DF</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>https://www.vibefisio.com.br</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr"/>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>5561993564242</t>
+        </is>
+      </c>
+      <c r="J1077" t="inlineStr"/>
+      <c r="K1077" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1077" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>Clínica Médica Goiás Saúde e Odontologia</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>https://clinicagoias.com</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr"/>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>5562982223100</t>
+        </is>
+      </c>
+      <c r="J1078" t="inlineStr"/>
+      <c r="K1078" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1078" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>Clínica MKN</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>https://mknservicos.com.br</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr"/>
+      <c r="I1079" t="inlineStr"/>
+      <c r="J1079" t="inlineStr"/>
+      <c r="K1079" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1079" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>clínica cmd on WhatsApp</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>https://wa.me</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr"/>
+      <c r="I1080" t="inlineStr"/>
+      <c r="J1080" t="inlineStr"/>
+      <c r="K1080" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1080" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>Clínica São Matheus</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>https://www.clinicasaomatheusgo.com.br</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr"/>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>5562985169032</t>
+        </is>
+      </c>
+      <c r="J1081" t="inlineStr"/>
+      <c r="K1081" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1081" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>Doutor Everton Neres</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>https://evertonneres.com.br</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr"/>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>5562985478937</t>
+        </is>
+      </c>
+      <c r="J1082" t="inlineStr"/>
+      <c r="K1082" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1082" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>Dentista em Goiânia</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>https://www.drgunnarguimaraes.com</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr"/>
+      <c r="I1083" t="inlineStr"/>
+      <c r="J1083" t="inlineStr"/>
+      <c r="K1083" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1083" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>Terapeuta</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>https://marciagoncalvesconstelacao.com.br</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr"/>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>5562985995444</t>
+        </is>
+      </c>
+      <c r="J1084" t="inlineStr"/>
+      <c r="K1084" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1084" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>Patrícia Neri</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>https://patricianeri.com.br</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr"/>
+      <c r="I1085" t="inlineStr"/>
+      <c r="J1085" t="inlineStr"/>
+      <c r="K1085" t="n">
+        <v>44</v>
+      </c>
+      <c r="L1085" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>Negócios de Terapeuta em GoiâNia</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>https://paginasamarelas.cybo.com</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr"/>
+      <c r="I1086" t="inlineStr"/>
+      <c r="J1086" t="inlineStr"/>
+      <c r="K1086" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1086" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>Advogado em Goiânia</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>https://advogadoemgoiania.adv.br</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr"/>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>5562999999999</t>
+        </is>
+      </c>
+      <c r="J1087" t="inlineStr"/>
+      <c r="K1087" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1087" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>Advogado em Goiânia</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>https://erickferrazadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr"/>
+      <c r="I1088" t="inlineStr"/>
+      <c r="J1088" t="inlineStr"/>
+      <c r="K1088" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1088" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>https://guiagoianiago.com.br</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr"/>
+      <c r="I1089" t="inlineStr"/>
+      <c r="J1089" t="inlineStr"/>
+      <c r="K1089" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1089" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1089"/>
+  <dimension ref="A1:L1107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52727,10 +52727,8 @@
         </is>
       </c>
       <c r="H1073" t="inlineStr"/>
-      <c r="I1073" t="inlineStr">
-        <is>
-          <t>556130201981</t>
-        </is>
+      <c r="I1073" t="n">
+        <v>556130201981</v>
       </c>
       <c r="J1073" t="inlineStr"/>
       <c r="K1073" t="n">
@@ -52779,10 +52777,8 @@
         </is>
       </c>
       <c r="H1074" t="inlineStr"/>
-      <c r="I1074" t="inlineStr">
-        <is>
-          <t>5561982863837</t>
-        </is>
+      <c r="I1074" t="n">
+        <v>5561982863837</v>
       </c>
       <c r="J1074" t="inlineStr"/>
       <c r="K1074" t="n">
@@ -52831,10 +52827,8 @@
         </is>
       </c>
       <c r="H1075" t="inlineStr"/>
-      <c r="I1075" t="inlineStr">
-        <is>
-          <t>556199878534</t>
-        </is>
+      <c r="I1075" t="n">
+        <v>556199878534</v>
       </c>
       <c r="J1075" t="inlineStr"/>
       <c r="K1075" t="n">
@@ -52931,10 +52925,8 @@
         </is>
       </c>
       <c r="H1077" t="inlineStr"/>
-      <c r="I1077" t="inlineStr">
-        <is>
-          <t>5561993564242</t>
-        </is>
+      <c r="I1077" t="n">
+        <v>5561993564242</v>
       </c>
       <c r="J1077" t="inlineStr"/>
       <c r="K1077" t="n">
@@ -52983,10 +52975,8 @@
         </is>
       </c>
       <c r="H1078" t="inlineStr"/>
-      <c r="I1078" t="inlineStr">
-        <is>
-          <t>5562982223100</t>
-        </is>
+      <c r="I1078" t="n">
+        <v>5562982223100</v>
       </c>
       <c r="J1078" t="inlineStr"/>
       <c r="K1078" t="n">
@@ -53131,10 +53121,8 @@
         </is>
       </c>
       <c r="H1081" t="inlineStr"/>
-      <c r="I1081" t="inlineStr">
-        <is>
-          <t>5562985169032</t>
-        </is>
+      <c r="I1081" t="n">
+        <v>5562985169032</v>
       </c>
       <c r="J1081" t="inlineStr"/>
       <c r="K1081" t="n">
@@ -53183,10 +53171,8 @@
         </is>
       </c>
       <c r="H1082" t="inlineStr"/>
-      <c r="I1082" t="inlineStr">
-        <is>
-          <t>5562985478937</t>
-        </is>
+      <c r="I1082" t="n">
+        <v>5562985478937</v>
       </c>
       <c r="J1082" t="inlineStr"/>
       <c r="K1082" t="n">
@@ -53283,10 +53269,8 @@
         </is>
       </c>
       <c r="H1084" t="inlineStr"/>
-      <c r="I1084" t="inlineStr">
-        <is>
-          <t>5562985995444</t>
-        </is>
+      <c r="I1084" t="n">
+        <v>5562985995444</v>
       </c>
       <c r="J1084" t="inlineStr"/>
       <c r="K1084" t="n">
@@ -53431,10 +53415,8 @@
         </is>
       </c>
       <c r="H1087" t="inlineStr"/>
-      <c r="I1087" t="inlineStr">
-        <is>
-          <t>5562999999999</t>
-        </is>
+      <c r="I1087" t="n">
+        <v>5562999999999</v>
       </c>
       <c r="J1087" t="inlineStr"/>
       <c r="K1087" t="n">
@@ -53542,6 +53524,906 @@
         </is>
       </c>
     </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>Articular Clínica Médica em Vitória</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>https://articularclinica.com.br</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr"/>
+      <c r="I1090" t="inlineStr"/>
+      <c r="J1090" t="inlineStr"/>
+      <c r="K1090" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1090" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>Clínica Médica</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>https://vitoriaguialocal.com.br</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr"/>
+      <c r="I1091" t="inlineStr"/>
+      <c r="J1091" t="inlineStr"/>
+      <c r="K1091" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1091" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>Centro Médico Shopping Vitoria</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>https://www.cmsv.com.br</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr"/>
+      <c r="I1092" t="inlineStr"/>
+      <c r="J1092" t="inlineStr"/>
+      <c r="K1092" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1092" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>Programa Mais Médicos e a medicina científica na perspectiva de ...</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>https://rbmfc.org.br</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr"/>
+      <c r="I1093" t="inlineStr"/>
+      <c r="J1093" t="inlineStr"/>
+      <c r="K1093" t="n">
+        <v>62</v>
+      </c>
+      <c r="L1093" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>Meridional Vitória</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>https://redemeridional.com.br</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr"/>
+      <c r="I1094" t="inlineStr"/>
+      <c r="J1094" t="inlineStr"/>
+      <c r="K1094" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1094" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>Santi Medicina Diagnóstica</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>https://santidiagnostico.com.br</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr"/>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>552734415700</t>
+        </is>
+      </c>
+      <c r="J1095" t="inlineStr"/>
+      <c r="K1095" t="n">
+        <v>76</v>
+      </c>
+      <c r="L1095" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>Super Dentista</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>https://superdentista.com.br</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr"/>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>5527992321325</t>
+        </is>
+      </c>
+      <c r="J1096" t="inlineStr"/>
+      <c r="K1096" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1096" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>Atuação do(a) psicólogo(a) na atenção básica</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>https://seer.unisc.br</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr"/>
+      <c r="I1097" t="inlineStr"/>
+      <c r="J1097" t="inlineStr"/>
+      <c r="K1097" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1097" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>Terapeuta Jéssica Paz</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>https://terapeuta5.site2.com.br</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr"/>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>5527998362472</t>
+        </is>
+      </c>
+      <c r="J1098" t="inlineStr"/>
+      <c r="K1098" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1098" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>Academia Vittoria</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>https://www.academiavittoria.com.br</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr"/>
+      <c r="I1099" t="inlineStr"/>
+      <c r="J1099" t="inlineStr"/>
+      <c r="K1099" t="n">
+        <v>50</v>
+      </c>
+      <c r="L1099" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>Instituto de Odontologia</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>https://www.institutodeodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr"/>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>5531987658699</t>
+        </is>
+      </c>
+      <c r="J1100" t="inlineStr"/>
+      <c r="K1100" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1100" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>Dentista Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>https://nosodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr"/>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>5531998077342</t>
+        </is>
+      </c>
+      <c r="J1101" t="inlineStr"/>
+      <c r="K1101" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1101" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>Dental Shalon</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>https://dentalshalon.com.br</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr"/>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>553132719430</t>
+        </is>
+      </c>
+      <c r="J1102" t="inlineStr"/>
+      <c r="K1102" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1102" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>Psicoterapeutas</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>https://tfebrasil.com.br</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr"/>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>5521992307496</t>
+        </is>
+      </c>
+      <c r="J1103" t="inlineStr"/>
+      <c r="K1103" t="n">
+        <v>59</v>
+      </c>
+      <c r="L1103" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>Advogado trabalhista BH</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>https://advogadatrabalhistabh.com.br</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr"/>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>5531981127997</t>
+        </is>
+      </c>
+      <c r="J1104" t="inlineStr"/>
+      <c r="K1104" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1104" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>Educação Física (Bacharelado)</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>https://www.facemg.edu.br</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr"/>
+      <c r="I1105" t="inlineStr"/>
+      <c r="J1105" t="inlineStr"/>
+      <c r="K1105" t="n">
+        <v>78</v>
+      </c>
+      <c r="L1105" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>15 Academias em Belo Horizonte: Veja aqui as Melhores!</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>https://prefirobh.com.br</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr"/>
+      <c r="I1106" t="inlineStr"/>
+      <c r="J1106" t="inlineStr"/>
+      <c r="K1106" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1106" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>Amare Fisioterapia</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>https://www.amarefisioterapia.com.br</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr"/>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>5531996365815</t>
+        </is>
+      </c>
+      <c r="J1107" t="inlineStr"/>
+      <c r="K1107" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1107" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1107"/>
+  <dimension ref="A1:L1118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53801,10 +53801,8 @@
         </is>
       </c>
       <c r="H1095" t="inlineStr"/>
-      <c r="I1095" t="inlineStr">
-        <is>
-          <t>552734415700</t>
-        </is>
+      <c r="I1095" t="n">
+        <v>552734415700</v>
       </c>
       <c r="J1095" t="inlineStr"/>
       <c r="K1095" t="n">
@@ -53853,10 +53851,8 @@
         </is>
       </c>
       <c r="H1096" t="inlineStr"/>
-      <c r="I1096" t="inlineStr">
-        <is>
-          <t>5527992321325</t>
-        </is>
+      <c r="I1096" t="n">
+        <v>5527992321325</v>
       </c>
       <c r="J1096" t="inlineStr"/>
       <c r="K1096" t="n">
@@ -53953,10 +53949,8 @@
         </is>
       </c>
       <c r="H1098" t="inlineStr"/>
-      <c r="I1098" t="inlineStr">
-        <is>
-          <t>5527998362472</t>
-        </is>
+      <c r="I1098" t="n">
+        <v>5527998362472</v>
       </c>
       <c r="J1098" t="inlineStr"/>
       <c r="K1098" t="n">
@@ -54053,10 +54047,8 @@
         </is>
       </c>
       <c r="H1100" t="inlineStr"/>
-      <c r="I1100" t="inlineStr">
-        <is>
-          <t>5531987658699</t>
-        </is>
+      <c r="I1100" t="n">
+        <v>5531987658699</v>
       </c>
       <c r="J1100" t="inlineStr"/>
       <c r="K1100" t="n">
@@ -54105,10 +54097,8 @@
         </is>
       </c>
       <c r="H1101" t="inlineStr"/>
-      <c r="I1101" t="inlineStr">
-        <is>
-          <t>5531998077342</t>
-        </is>
+      <c r="I1101" t="n">
+        <v>5531998077342</v>
       </c>
       <c r="J1101" t="inlineStr"/>
       <c r="K1101" t="n">
@@ -54157,10 +54147,8 @@
         </is>
       </c>
       <c r="H1102" t="inlineStr"/>
-      <c r="I1102" t="inlineStr">
-        <is>
-          <t>553132719430</t>
-        </is>
+      <c r="I1102" t="n">
+        <v>553132719430</v>
       </c>
       <c r="J1102" t="inlineStr"/>
       <c r="K1102" t="n">
@@ -54209,10 +54197,8 @@
         </is>
       </c>
       <c r="H1103" t="inlineStr"/>
-      <c r="I1103" t="inlineStr">
-        <is>
-          <t>5521992307496</t>
-        </is>
+      <c r="I1103" t="n">
+        <v>5521992307496</v>
       </c>
       <c r="J1103" t="inlineStr"/>
       <c r="K1103" t="n">
@@ -54261,10 +54247,8 @@
         </is>
       </c>
       <c r="H1104" t="inlineStr"/>
-      <c r="I1104" t="inlineStr">
-        <is>
-          <t>5531981127997</t>
-        </is>
+      <c r="I1104" t="n">
+        <v>5531981127997</v>
       </c>
       <c r="J1104" t="inlineStr"/>
       <c r="K1104" t="n">
@@ -54409,10 +54393,8 @@
         </is>
       </c>
       <c r="H1107" t="inlineStr"/>
-      <c r="I1107" t="inlineStr">
-        <is>
-          <t>5531996365815</t>
-        </is>
+      <c r="I1107" t="n">
+        <v>5531996365815</v>
       </c>
       <c r="J1107" t="inlineStr"/>
       <c r="K1107" t="n">
@@ -54421,6 +54403,554 @@
       <c r="L1107" t="inlineStr">
         <is>
           <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>Advogados de Direito de Família em Curitiba</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>https://aot.adv.br</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr"/>
+      <c r="I1108" t="inlineStr"/>
+      <c r="J1108" t="inlineStr"/>
+      <c r="K1108" t="n">
+        <v>82</v>
+      </c>
+      <c r="L1108" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>EDUCAÇÃO FÍSICA</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>https://www.prppg.ufpr.br</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr"/>
+      <c r="I1109" t="inlineStr"/>
+      <c r="J1109" t="inlineStr"/>
+      <c r="K1109" t="n">
+        <v>76</v>
+      </c>
+      <c r="L1109" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>Harmos Academia</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>https://harmosacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr"/>
+      <c r="I1110" t="inlineStr"/>
+      <c r="J1110" t="inlineStr"/>
+      <c r="K1110" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1110" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>Clínica Mirabile</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>https://www.clinicamirabile.com.br</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr"/>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>555199054701</t>
+        </is>
+      </c>
+      <c r="J1111" t="inlineStr"/>
+      <c r="K1111" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1111" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>Lazaroto Odontologia</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>https://www.lazarotoodontologia.com.br</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr"/>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>5551992499027</t>
+        </is>
+      </c>
+      <c r="J1112" t="inlineStr"/>
+      <c r="K1112" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1112" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>Dentista Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>https://www.clinicadacostaodontoeestetica.com</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr"/>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>5551997410114</t>
+        </is>
+      </c>
+      <c r="J1113" t="inlineStr"/>
+      <c r="K1113" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1113" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>BAGGIO Advogados Associados</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>https://baggioadvogados.com</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr"/>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>5551999441039</t>
+        </is>
+      </c>
+      <c r="J1114" t="inlineStr"/>
+      <c r="K1114" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1114" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>Dias e Paim Advogados: Advogado Trabalhista Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>https://www.diasepaimadvogados.com.br</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr"/>
+      <c r="I1115" t="inlineStr"/>
+      <c r="J1115" t="inlineStr"/>
+      <c r="K1115" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1115" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>Fernanda Ramalho Advogada Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>https://fernandaramalho.adv.br</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr"/>
+      <c r="I1116" t="inlineStr"/>
+      <c r="J1116" t="inlineStr"/>
+      <c r="K1116" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1116" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>UFRGS</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>https://www.ufrgs.br</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr"/>
+      <c r="I1117" t="inlineStr"/>
+      <c r="J1117" t="inlineStr"/>
+      <c r="K1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1117" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Sul</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>Top One Academia em Porto Alegre</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>https://www.toponeacademia.com.br</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr"/>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>555193024049</t>
+        </is>
+      </c>
+      <c r="J1118" t="inlineStr"/>
+      <c r="K1118" t="n">
+        <v>100</v>
+      </c>
+      <c r="L1118" t="inlineStr">
+        <is>
+          <t>Baixo</t>
         </is>
       </c>
     </row>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1118"/>
+  <dimension ref="A1:L1135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54587,10 +54587,8 @@
         </is>
       </c>
       <c r="H1111" t="inlineStr"/>
-      <c r="I1111" t="inlineStr">
-        <is>
-          <t>555199054701</t>
-        </is>
+      <c r="I1111" t="n">
+        <v>555199054701</v>
       </c>
       <c r="J1111" t="inlineStr"/>
       <c r="K1111" t="n">
@@ -54639,10 +54637,8 @@
         </is>
       </c>
       <c r="H1112" t="inlineStr"/>
-      <c r="I1112" t="inlineStr">
-        <is>
-          <t>5551992499027</t>
-        </is>
+      <c r="I1112" t="n">
+        <v>5551992499027</v>
       </c>
       <c r="J1112" t="inlineStr"/>
       <c r="K1112" t="n">
@@ -54691,10 +54687,8 @@
         </is>
       </c>
       <c r="H1113" t="inlineStr"/>
-      <c r="I1113" t="inlineStr">
-        <is>
-          <t>5551997410114</t>
-        </is>
+      <c r="I1113" t="n">
+        <v>5551997410114</v>
       </c>
       <c r="J1113" t="inlineStr"/>
       <c r="K1113" t="n">
@@ -54743,10 +54737,8 @@
         </is>
       </c>
       <c r="H1114" t="inlineStr"/>
-      <c r="I1114" t="inlineStr">
-        <is>
-          <t>5551999441039</t>
-        </is>
+      <c r="I1114" t="n">
+        <v>5551999441039</v>
       </c>
       <c r="J1114" t="inlineStr"/>
       <c r="K1114" t="n">
@@ -54939,10 +54931,8 @@
         </is>
       </c>
       <c r="H1118" t="inlineStr"/>
-      <c r="I1118" t="inlineStr">
-        <is>
-          <t>555193024049</t>
-        </is>
+      <c r="I1118" t="n">
+        <v>555193024049</v>
       </c>
       <c r="J1118" t="inlineStr"/>
       <c r="K1118" t="n">
@@ -54951,6 +54941,842 @@
       <c r="L1118" t="inlineStr">
         <is>
           <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>I Fórum Acreano de Direito Médico em Rio Branco</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>https://www.sympla.com.br</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr"/>
+      <c r="I1119" t="inlineStr"/>
+      <c r="J1119" t="inlineStr"/>
+      <c r="K1119" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1119" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>Legisla-e</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>https://app.al.ac.leg.br</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr"/>
+      <c r="I1120" t="inlineStr"/>
+      <c r="J1120" t="inlineStr"/>
+      <c r="K1120" t="n">
+        <v>89</v>
+      </c>
+      <c r="L1120" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>Infecção endoparasitária entre primatas de estimação no Acre ...</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>https://www.revistamvez-crmvsp.com.br</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr"/>
+      <c r="I1121" t="inlineStr"/>
+      <c r="J1121" t="inlineStr"/>
+      <c r="K1121" t="n">
+        <v>65</v>
+      </c>
+      <c r="L1121" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>Dentista Rio Branco</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>https://dentistariobranco.ac.gd</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr"/>
+      <c r="I1122" t="inlineStr"/>
+      <c r="J1122" t="inlineStr"/>
+      <c r="K1122" t="n">
+        <v>53</v>
+      </c>
+      <c r="L1122" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>Poersch &amp; Poersch Advogados</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>https://poersch.adv.br</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr"/>
+      <c r="I1123" t="inlineStr"/>
+      <c r="J1123" t="inlineStr"/>
+      <c r="K1123" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1123" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>Emerson Costa Advocacia</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>https://www.emersoncostaadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr"/>
+      <c r="I1124" t="inlineStr"/>
+      <c r="J1124" t="inlineStr"/>
+      <c r="K1124" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1124" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>Araújo e Braga Advocacia e Assessoria</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>https://araujoebragaadvocacia.com.br</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr"/>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>5568992266725</t>
+        </is>
+      </c>
+      <c r="J1125" t="inlineStr"/>
+      <c r="K1125" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1125" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>Advogado em Rio Branco-AC</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>https://sennamartins.com.br</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr"/>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>551940421216</t>
+        </is>
+      </c>
+      <c r="J1126" t="inlineStr"/>
+      <c r="K1126" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1126" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>Atividades físicas</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>https://sesiac.org.br</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr"/>
+      <c r="I1127" t="inlineStr"/>
+      <c r="J1127" t="inlineStr"/>
+      <c r="K1127" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1127" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>▷ Melhores Academias Em Rio Branco 《 2024 》</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>https://academiasbrasil.online</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr"/>
+      <c r="I1128" t="inlineStr"/>
+      <c r="J1128" t="inlineStr"/>
+      <c r="K1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1128" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>Educação Física (Bacharelado)</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>https://castelobranco.br</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr"/>
+      <c r="I1129" t="inlineStr"/>
+      <c r="J1129" t="inlineStr"/>
+      <c r="K1129" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1129" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>Software Para Dentista Macapá Ap</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>https://dentalsolutionweb.com.br</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr"/>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>5521999877076</t>
+        </is>
+      </c>
+      <c r="J1130" t="inlineStr"/>
+      <c r="K1130" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1130" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>Mapa do Site</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>https://brclinmacapa.com.br</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr"/>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>5596981463313</t>
+        </is>
+      </c>
+      <c r="J1131" t="inlineStr"/>
+      <c r="K1131" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1131" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>ABO pelo Brasil</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>https://abonacional.com.br</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr"/>
+      <c r="I1132" t="inlineStr"/>
+      <c r="J1132" t="inlineStr"/>
+      <c r="K1132" t="n">
+        <v>67</v>
+      </c>
+      <c r="L1132" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Macapá</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>Academias no Macapá, Amapá, ap</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>https://amapa.net.br</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr"/>
+      <c r="I1133" t="inlineStr"/>
+      <c r="J1133" t="inlineStr"/>
+      <c r="K1133" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1133" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>COOPERCLIM</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>https://socios.cooperclim.com.br</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr"/>
+      <c r="I1134" t="inlineStr"/>
+      <c r="J1134" t="inlineStr"/>
+      <c r="K1134" t="n">
+        <v>50</v>
+      </c>
+      <c r="L1134" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>Inicio</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>https://dentistaemmanaus.com.br</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr"/>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>5592984294317</t>
+        </is>
+      </c>
+      <c r="J1135" t="inlineStr"/>
+      <c r="K1135" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1135" t="inlineStr">
+        <is>
+          <t>Crítico</t>
         </is>
       </c>
     </row>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1135"/>
+  <dimension ref="A1:L1145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55269,10 +55269,8 @@
         </is>
       </c>
       <c r="H1125" t="inlineStr"/>
-      <c r="I1125" t="inlineStr">
-        <is>
-          <t>5568992266725</t>
-        </is>
+      <c r="I1125" t="n">
+        <v>5568992266725</v>
       </c>
       <c r="J1125" t="inlineStr"/>
       <c r="K1125" t="n">
@@ -55321,10 +55319,8 @@
         </is>
       </c>
       <c r="H1126" t="inlineStr"/>
-      <c r="I1126" t="inlineStr">
-        <is>
-          <t>551940421216</t>
-        </is>
+      <c r="I1126" t="n">
+        <v>551940421216</v>
       </c>
       <c r="J1126" t="inlineStr"/>
       <c r="K1126" t="n">
@@ -55517,10 +55513,8 @@
         </is>
       </c>
       <c r="H1130" t="inlineStr"/>
-      <c r="I1130" t="inlineStr">
-        <is>
-          <t>5521999877076</t>
-        </is>
+      <c r="I1130" t="n">
+        <v>5521999877076</v>
       </c>
       <c r="J1130" t="inlineStr"/>
       <c r="K1130" t="n">
@@ -55569,10 +55563,8 @@
         </is>
       </c>
       <c r="H1131" t="inlineStr"/>
-      <c r="I1131" t="inlineStr">
-        <is>
-          <t>5596981463313</t>
-        </is>
+      <c r="I1131" t="n">
+        <v>5596981463313</v>
       </c>
       <c r="J1131" t="inlineStr"/>
       <c r="K1131" t="n">
@@ -55765,16 +55757,510 @@
         </is>
       </c>
       <c r="H1135" t="inlineStr"/>
-      <c r="I1135" t="inlineStr">
-        <is>
-          <t>5592984294317</t>
-        </is>
+      <c r="I1135" t="n">
+        <v>5592984294317</v>
       </c>
       <c r="J1135" t="inlineStr"/>
       <c r="K1135" t="n">
         <v>73</v>
       </c>
       <c r="L1135" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>Médica</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>https://deusamendes.com.br</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr"/>
+      <c r="I1136" t="inlineStr"/>
+      <c r="J1136" t="inlineStr"/>
+      <c r="K1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1136" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>Clínica Médica em Maceió</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>https://mbprimesaude.com</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr"/>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>5582993230900</t>
+        </is>
+      </c>
+      <c r="J1137" t="inlineStr"/>
+      <c r="K1137" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1137" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>Dental Mac Maceió</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>https://dentalmac.com.br</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr"/>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>5582998260123</t>
+        </is>
+      </c>
+      <c r="J1138" t="inlineStr"/>
+      <c r="K1138" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1138" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>Luciana Gomes — Psicóloga Clínica em Maceió/AL</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>https://lucianagomespsicologa.com.br</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr"/>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>5582991442003</t>
+        </is>
+      </c>
+      <c r="J1139" t="inlineStr"/>
+      <c r="K1139" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1139" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>Academia Maceió</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>https://br.top10place.com</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr"/>
+      <c r="I1140" t="inlineStr"/>
+      <c r="J1140" t="inlineStr"/>
+      <c r="K1140" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1140" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>Maceió</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Academia Maceió,</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>https://wanderlog.com</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr"/>
+      <c r="I1141" t="inlineStr"/>
+      <c r="J1141" t="inlineStr"/>
+      <c r="K1141" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1141" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>CLINICA MÉDICA DA FAMÍLIA</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>https://sindhosba.org.br</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr"/>
+      <c r="I1142" t="inlineStr"/>
+      <c r="J1142" t="inlineStr"/>
+      <c r="K1142" t="n">
+        <v>78</v>
+      </c>
+      <c r="L1142" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>Advogado em Salvador</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>https://advogalia.com</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr"/>
+      <c r="I1143" t="inlineStr"/>
+      <c r="J1143" t="inlineStr"/>
+      <c r="K1143" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1143" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>Marinho Bastos Advogados</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>https://marinhobastos.com.br</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr"/>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>5571987803521</t>
+        </is>
+      </c>
+      <c r="J1144" t="inlineStr"/>
+      <c r="K1144" t="n">
+        <v>91</v>
+      </c>
+      <c r="L1144" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Advogado em Salvador, BA</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>https://michelrocha.adv.br</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr"/>
+      <c r="I1145" t="inlineStr"/>
+      <c r="J1145" t="inlineStr"/>
+      <c r="K1145" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1145" t="inlineStr">
         <is>
           <t>Crítico</t>
         </is>

--- a/leads_automation/data/leads_conformidade_brasil.xlsx
+++ b/leads_automation/data/leads_conformidade_brasil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1145"/>
+  <dimension ref="A1:L1167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55855,10 +55855,8 @@
         </is>
       </c>
       <c r="H1137" t="inlineStr"/>
-      <c r="I1137" t="inlineStr">
-        <is>
-          <t>5582993230900</t>
-        </is>
+      <c r="I1137" t="n">
+        <v>5582993230900</v>
       </c>
       <c r="J1137" t="inlineStr"/>
       <c r="K1137" t="n">
@@ -55907,10 +55905,8 @@
         </is>
       </c>
       <c r="H1138" t="inlineStr"/>
-      <c r="I1138" t="inlineStr">
-        <is>
-          <t>5582998260123</t>
-        </is>
+      <c r="I1138" t="n">
+        <v>5582998260123</v>
       </c>
       <c r="J1138" t="inlineStr"/>
       <c r="K1138" t="n">
@@ -55959,10 +55955,8 @@
         </is>
       </c>
       <c r="H1139" t="inlineStr"/>
-      <c r="I1139" t="inlineStr">
-        <is>
-          <t>5582991442003</t>
-        </is>
+      <c r="I1139" t="n">
+        <v>5582991442003</v>
       </c>
       <c r="J1139" t="inlineStr"/>
       <c r="K1139" t="n">
@@ -56203,10 +56197,8 @@
         </is>
       </c>
       <c r="H1144" t="inlineStr"/>
-      <c r="I1144" t="inlineStr">
-        <is>
-          <t>5571987803521</t>
-        </is>
+      <c r="I1144" t="n">
+        <v>5571987803521</v>
       </c>
       <c r="J1144" t="inlineStr"/>
       <c r="K1144" t="n">
@@ -56266,6 +56258,1102 @@
         </is>
       </c>
     </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>Sigmavita</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>https://www.sigmavita.com.br</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr"/>
+      <c r="I1146" t="inlineStr"/>
+      <c r="J1146" t="inlineStr"/>
+      <c r="K1146" t="n">
+        <v>56</v>
+      </c>
+      <c r="L1146" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>Kypy Saúde - Clínica Médica em Brasília</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>https://kypysaude.com.br</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr"/>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>556193656589</t>
+        </is>
+      </c>
+      <c r="J1147" t="inlineStr"/>
+      <c r="K1147" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1147" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>Clínica Médica no Guará</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>https://centroclinicoportoclaro.com.br</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr"/>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>5561993041166</t>
+        </is>
+      </c>
+      <c r="J1148" t="inlineStr"/>
+      <c r="K1148" t="n">
+        <v>87</v>
+      </c>
+      <c r="L1148" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>Início - Clínica Odontológica em Brasília</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>https://cobodontologiabrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr"/>
+      <c r="I1149" t="inlineStr"/>
+      <c r="J1149" t="inlineStr"/>
+      <c r="K1149" t="n">
+        <v>22</v>
+      </c>
+      <c r="L1149" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>dentista</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>Clínica Oral Concept</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>https://clinicaoralconcept.com.br</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr"/>
+      <c r="I1150" t="inlineStr"/>
+      <c r="J1150" t="inlineStr"/>
+      <c r="K1150" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1150" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>Lucas Bezerra: Psicólogo em Brasília e Online</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>https://psicologobrasilia.com.br</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr"/>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>5561984048581</t>
+        </is>
+      </c>
+      <c r="J1151" t="inlineStr"/>
+      <c r="K1151" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1151" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>Fabíola Freitas</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>https://www.conexasaude.com.br</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr"/>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>5511976396153</t>
+        </is>
+      </c>
+      <c r="J1152" t="inlineStr"/>
+      <c r="K1152" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1152" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>CRP DF: Conselho Regional de Psicologia do DF</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>https://www.crp-01.org.br</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr"/>
+      <c r="I1153" t="inlineStr"/>
+      <c r="J1153" t="inlineStr"/>
+      <c r="K1153" t="n">
+        <v>75</v>
+      </c>
+      <c r="L1153" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>Terappia</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>https://www.terappia.com.br</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr"/>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>5521999850091</t>
+        </is>
+      </c>
+      <c r="J1154" t="inlineStr"/>
+      <c r="K1154" t="n">
+        <v>88</v>
+      </c>
+      <c r="L1154" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>CLÍNICA HOLLOS</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>https://www.clinicahollos.com.br</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr"/>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>5561992926161</t>
+        </is>
+      </c>
+      <c r="J1155" t="inlineStr"/>
+      <c r="K1155" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1155" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Psicóloga em Brasília: Terapia Cognitiva Online</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>https://mariacarolinacolombo.com.br</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr"/>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>556196811386</t>
+        </is>
+      </c>
+      <c r="J1156" t="inlineStr"/>
+      <c r="K1156" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1156" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>Elias Daher Psicanalista</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>https://eliasdaherpsicanalista.com.br</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr"/>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>5561992541042</t>
+        </is>
+      </c>
+      <c r="J1157" t="inlineStr"/>
+      <c r="K1157" t="n">
+        <v>81</v>
+      </c>
+      <c r="L1157" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>academia</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>Melhores Academias em Brasilia</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>https://academiasbr.com.br</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr"/>
+      <c r="I1158" t="inlineStr"/>
+      <c r="J1158" t="inlineStr"/>
+      <c r="K1158" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1158" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>Fisioterapeuta no DF</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>https://fisioterapeutaingrid.com</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr"/>
+      <c r="I1159" t="inlineStr"/>
+      <c r="J1159" t="inlineStr"/>
+      <c r="K1159" t="n">
+        <v>60</v>
+      </c>
+      <c r="L1159" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>clínica médica</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>Clínica Médica de Alto Padrão em Goiânia</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>https://clinicasaudeagora.com.br</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr"/>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>5562981942470</t>
+        </is>
+      </c>
+      <c r="J1160" t="inlineStr"/>
+      <c r="K1160" t="n">
+        <v>80</v>
+      </c>
+      <c r="L1160" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>Einstein Hospital Israelita em Goiânia</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>https://www.einstein.br</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr"/>
+      <c r="I1161" t="inlineStr"/>
+      <c r="J1161" t="inlineStr"/>
+      <c r="K1161" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1161" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>médico</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Santa Casa de Misericórdia de Goiânia</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>https://www.santacasago.org.br</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr"/>
+      <c r="I1162" t="inlineStr"/>
+      <c r="J1162" t="inlineStr"/>
+      <c r="K1162" t="n">
+        <v>44</v>
+      </c>
+      <c r="L1162" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>psicólogo</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>Thiago Valadares</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>https://thiagovaladarespsi.com.br</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr"/>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>5562982254507</t>
+        </is>
+      </c>
+      <c r="J1163" t="inlineStr"/>
+      <c r="K1163" t="n">
+        <v>73</v>
+      </c>
+      <c r="L1163" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>terapeuta</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>A VIVÊNCIA DO AQUI-E-AGORA NA RELAÇÃO TERAPÊUTICA NA ...</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>https://seer.pucgoias.edu.br</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr"/>
+      <c r="I1164" t="inlineStr"/>
+      <c r="J1164" t="inlineStr"/>
+      <c r="K1164" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1164" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>advogado</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>Advogado Goiânia</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>https://goianiaadvogado.com.br</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr"/>
+      <c r="I1165" t="inlineStr"/>
+      <c r="J1165" t="inlineStr"/>
+      <c r="K1165" t="n">
+        <v>64</v>
+      </c>
+      <c r="L1165" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Educação Física</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>https://www.institutodesaudeassistida.com.br</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr"/>
+      <c r="I1166" t="inlineStr"/>
+      <c r="J1166" t="inlineStr"/>
+      <c r="K1166" t="n">
+        <v>69</v>
+      </c>
+      <c r="L1166" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>educação física</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Daniel Alves Personal</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>https://www.clikofertas.com</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr"/>
+      <c r="I1167" t="inlineStr"/>
+      <c r="J1167" t="inlineStr"/>
+      <c r="K1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1167" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
